--- a/input/ES/reg_fertility.xlsx
+++ b/input/ES/reg_fertility.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="91" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="93" uniqueCount="59">
   <si>
     <t>Description</t>
   </si>
@@ -140,10 +140,13 @@
     <t>Ydses_c5_Q5_L1</t>
   </si>
   <si>
-    <t>Dnc_L1</t>
-  </si>
-  <si>
-    <t>Dnc02_L1</t>
+    <t>Dnc1_L1</t>
+  </si>
+  <si>
+    <t>Dnc2_plus_L1</t>
+  </si>
+  <si>
+    <t>Dnc02_yes_L1</t>
   </si>
   <si>
     <t>Deh_c4_Low</t>
@@ -374,7 +377,7 @@
         <v>14</v>
       </c>
       <c r="B11">
-        <v>0.21241176194806766</v>
+        <v>0.22583240468467514</v>
       </c>
       <c r="C11"/>
       <c r="D11"/>
@@ -382,7 +385,7 @@
         <v>20</v>
       </c>
       <c r="F11">
-        <v>1077.7230887536318</v>
+        <v>1110.9526961824765</v>
       </c>
     </row>
     <row r="12">
@@ -398,7 +401,7 @@
         <v>21</v>
       </c>
       <c r="F12">
-        <v>-10212250.615058184</v>
+        <v>-10038232.588347603</v>
       </c>
     </row>
   </sheetData>
@@ -407,7 +410,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AI34"/>
+  <dimension ref="A1:AJ35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -415,7 +418,7 @@
         <v>23</v>
       </c>
       <c r="B1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C1" t="s">
         <v>24</v>
@@ -515,6 +518,9 @@
       </c>
       <c r="AI1" t="s">
         <v>56</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="2">
@@ -522,106 +528,109 @@
         <v>24</v>
       </c>
       <c r="B2">
-        <v>11.711447280450107</v>
+        <v>10.28828366904478</v>
       </c>
       <c r="C2">
-        <v>4.2343793880865173</v>
+        <v>4.0264820492458382</v>
       </c>
       <c r="D2">
-        <v>0.016804877743496878</v>
+        <v>0.016511847314585056</v>
       </c>
       <c r="E2">
-        <v>-0.00022494547014773069</v>
+        <v>-0.00021891562602621467</v>
       </c>
       <c r="F2">
-        <v>-0.0020299719301921648</v>
+        <v>-0.0019806546731783448</v>
       </c>
       <c r="G2">
-        <v>0.005378909669715326</v>
+        <v>0.0069914406088493475</v>
       </c>
       <c r="H2">
-        <v>0.0047083300805478845</v>
+        <v>0.0053225052952228513</v>
       </c>
       <c r="I2">
-        <v>0.0056948946196553885</v>
+        <v>0.0066617728859940939</v>
       </c>
       <c r="J2">
-        <v>0.0089088725539483229</v>
+        <v>0.0068401309091116634</v>
       </c>
       <c r="K2">
-        <v>-0.0045807759269763867</v>
+        <v>-0.0044960599519654615</v>
       </c>
       <c r="L2">
-        <v>-0.13666820742910732</v>
+        <v>-0.12910664187354523</v>
       </c>
       <c r="M2">
-        <v>-0.70314136262784777</v>
+        <v>-0.67873172975765528</v>
       </c>
       <c r="N2">
-        <v>-0.80687831594874504</v>
+        <v>-0.78093632353149845</v>
       </c>
       <c r="O2">
-        <v>-0.45248467586004876</v>
+        <v>-0.41699609051896836</v>
       </c>
       <c r="P2">
-        <v>0.012482120185884406</v>
+        <v>0.009134840529856178</v>
       </c>
       <c r="Q2">
-        <v>-0.011911167082071045</v>
+        <v>-0.012497257666346708</v>
       </c>
       <c r="R2">
-        <v>-0.015062334207493481</v>
+        <v>-0.016531622865446738</v>
       </c>
       <c r="S2">
-        <v>-0.019174804078569224</v>
+        <v>-0.021052870742490106</v>
       </c>
       <c r="T2">
-        <v>-0.0068540292196371238</v>
+        <v>-0.01403103509017159</v>
       </c>
       <c r="U2">
-        <v>0.0038910469223367161</v>
+        <v>-0.014861015372463846</v>
       </c>
       <c r="V2">
-        <v>0.0010978054264662307</v>
+        <v>0.0051318929565080541</v>
       </c>
       <c r="W2">
-        <v>-0.00025410340911616487</v>
+        <v>0.0019271813196352072</v>
       </c>
       <c r="X2">
-        <v>0.0022790960136856511</v>
+        <v>-0.00056765398063500158</v>
       </c>
       <c r="Y2">
-        <v>-0.039403594306083645</v>
+        <v>0.0016190650379425339</v>
       </c>
       <c r="Z2">
-        <v>-0.0063408707682034299</v>
+        <v>-0.036502196669909948</v>
       </c>
       <c r="AA2">
-        <v>-0.00034062264106876627</v>
+        <v>-0.0067386622581028372</v>
       </c>
       <c r="AB2">
-        <v>5.2232044968119652e-05</v>
+        <v>0.00061525010395119262</v>
       </c>
       <c r="AC2">
-        <v>0.013289755297482164</v>
+        <v>1.2232335546196772e-05</v>
       </c>
       <c r="AD2">
-        <v>0.010614052731393764</v>
+        <v>0.012352768684668003</v>
       </c>
       <c r="AE2">
-        <v>0.013802604640571599</v>
+        <v>0.0094684639002704241</v>
       </c>
       <c r="AF2">
-        <v>0.013342535415184625</v>
+        <v>0.013109054646122054</v>
       </c>
       <c r="AG2">
-        <v>0.013547676971519824</v>
+        <v>0.011757120176712266</v>
       </c>
       <c r="AH2">
-        <v>0.010977371294658339</v>
+        <v>0.012178381634644971</v>
       </c>
       <c r="AI2">
-        <v>-0.40253927747843399</v>
+        <v>0.009746672677643467</v>
+      </c>
+      <c r="AJ2">
+        <v>-0.37311892966451871</v>
       </c>
     </row>
     <row r="3">
@@ -629,106 +638,109 @@
         <v>25</v>
       </c>
       <c r="B3">
-        <v>0.37385108913203652</v>
+        <v>0.3765273314776737</v>
       </c>
       <c r="C3">
-        <v>0.016804877743496878</v>
+        <v>0.016511847314585056</v>
       </c>
       <c r="D3">
-        <v>0.0012589612359229594</v>
+        <v>0.0012601148983745845</v>
       </c>
       <c r="E3">
-        <v>-1.7440054465121916e-05</v>
+        <v>-1.750413119638845e-05</v>
       </c>
       <c r="F3">
-        <v>-0.00012518344544707079</v>
+        <v>-0.00025903859447572869</v>
       </c>
       <c r="G3">
-        <v>0.00038556538267762314</v>
+        <v>0.00037875841799748199</v>
       </c>
       <c r="H3">
-        <v>0.00019624820830609763</v>
+        <v>0.00019802447148850773</v>
       </c>
       <c r="I3">
-        <v>0.0003550627913427775</v>
+        <v>0.00035183995322166616</v>
       </c>
       <c r="J3">
-        <v>0.00051379937646650327</v>
+        <v>0.0004770352383460663</v>
       </c>
       <c r="K3">
-        <v>1.2034036398811659e-05</v>
+        <v>2.8523648163845863e-05</v>
       </c>
       <c r="L3">
-        <v>-0.00061560548759721236</v>
+        <v>-0.00060590155380684484</v>
       </c>
       <c r="M3">
-        <v>-0.00069946551586146349</v>
+        <v>-0.00066020688256818356</v>
       </c>
       <c r="N3">
-        <v>-0.00018631616516383764</v>
+        <v>-0.00019717856783842006</v>
       </c>
       <c r="O3">
-        <v>0.00010528952368784802</v>
+        <v>0.00010327853045473748</v>
       </c>
       <c r="P3">
-        <v>-9.3205184014845529e-05</v>
+        <v>-8.0230439460864545e-05</v>
       </c>
       <c r="Q3">
-        <v>-0.00030290424234959037</v>
+        <v>-0.00030388784763747917</v>
       </c>
       <c r="R3">
-        <v>-0.00030588844955861357</v>
+        <v>-0.00030995834585633819</v>
       </c>
       <c r="S3">
-        <v>-0.00039006962747682858</v>
+        <v>-0.00038970639162901912</v>
       </c>
       <c r="T3">
-        <v>-6.0547268984937177e-05</v>
+        <v>-3.3615211987328593e-05</v>
       </c>
       <c r="U3">
-        <v>-0.00019444007135821029</v>
+        <v>-0.00011066982474565619</v>
       </c>
       <c r="V3">
-        <v>-3.6469958510562065e-05</v>
+        <v>-0.00023393056887593858</v>
       </c>
       <c r="W3">
-        <v>-0.00015624355756860579</v>
+        <v>-4.0250667569825295e-05</v>
       </c>
       <c r="X3">
-        <v>6.3939760231571975e-06</v>
+        <v>-0.00015939846490364926</v>
       </c>
       <c r="Y3">
-        <v>-0.00052942195573361646</v>
+        <v>2.7557411350635948e-06</v>
       </c>
       <c r="Z3">
-        <v>-6.2911593248133908e-05</v>
+        <v>-0.00044795679051351251</v>
       </c>
       <c r="AA3">
-        <v>4.6010239909438644e-05</v>
+        <v>-4.4919305012504005e-05</v>
       </c>
       <c r="AB3">
-        <v>-1.1521360416434775e-06</v>
+        <v>5.0034921853884043e-05</v>
       </c>
       <c r="AC3">
-        <v>-0.00024188602674922975</v>
+        <v>-1.3201437961548549e-06</v>
       </c>
       <c r="AD3">
-        <v>-0.00030942367085952556</v>
+        <v>-0.00025913318481369033</v>
       </c>
       <c r="AE3">
-        <v>-0.00018723769281027642</v>
+        <v>-0.00031972678353795608</v>
       </c>
       <c r="AF3">
-        <v>-0.00020488777842849783</v>
+        <v>-0.0001902478692502492</v>
       </c>
       <c r="AG3">
-        <v>-0.00018763163193530764</v>
+        <v>-0.0002336475160176453</v>
       </c>
       <c r="AH3">
-        <v>-0.00026767623432941926</v>
+        <v>-0.0002131261504103284</v>
       </c>
       <c r="AI3">
-        <v>-0.022425967133208467</v>
+        <v>-0.00028790444598063986</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.022249251698617419</v>
       </c>
     </row>
     <row r="4">
@@ -736,106 +748,109 @@
         <v>26</v>
       </c>
       <c r="B4">
-        <v>-0.0061494401935123077</v>
+        <v>-0.0062212832590872276</v>
       </c>
       <c r="C4">
-        <v>-0.00022494547014773069</v>
+        <v>-0.00021891562602621467</v>
       </c>
       <c r="D4">
-        <v>-1.7440054465121916e-05</v>
+        <v>-1.750413119638845e-05</v>
       </c>
       <c r="E4">
-        <v>2.4402441957767835e-07</v>
+        <v>2.4584741848218557e-07</v>
       </c>
       <c r="F4">
-        <v>1.1863473408743228e-06</v>
+        <v>3.0440925414201175e-06</v>
       </c>
       <c r="G4">
-        <v>-5.1005778139603768e-06</v>
+        <v>-4.8806396285952004e-06</v>
       </c>
       <c r="H4">
-        <v>-2.4011107857440425e-06</v>
+        <v>-2.3491670395210911e-06</v>
       </c>
       <c r="I4">
-        <v>-4.4720301458506533e-06</v>
+        <v>-4.3174216617076317e-06</v>
       </c>
       <c r="J4">
-        <v>-6.2407736092217277e-06</v>
+        <v>-5.755835934742876e-06</v>
       </c>
       <c r="K4">
-        <v>-3.8194073036045386e-08</v>
+        <v>-3.2318630677959114e-07</v>
       </c>
       <c r="L4">
-        <v>8.2467636077627966e-06</v>
+        <v>8.0168792119224057e-06</v>
       </c>
       <c r="M4">
-        <v>8.6886523741590954e-06</v>
+        <v>8.1691724576419637e-06</v>
       </c>
       <c r="N4">
-        <v>2.2151028291856893e-06</v>
+        <v>2.3262631773805615e-06</v>
       </c>
       <c r="O4">
-        <v>-1.2251503745399576e-06</v>
+        <v>-1.1290501425161248e-06</v>
       </c>
       <c r="P4">
-        <v>1.2213958656446713e-06</v>
+        <v>1.0375098014718678e-06</v>
       </c>
       <c r="Q4">
-        <v>4.2853634019152227e-06</v>
+        <v>4.3844932218281975e-06</v>
       </c>
       <c r="R4">
-        <v>4.2131304416566235e-06</v>
+        <v>4.3193194425701289e-06</v>
       </c>
       <c r="S4">
-        <v>5.2050590231725682e-06</v>
+        <v>5.2133472251351553e-06</v>
       </c>
       <c r="T4">
-        <v>3.9192315423521632e-07</v>
+        <v>-5.8623768479945204e-07</v>
       </c>
       <c r="U4">
-        <v>3.3471710671157277e-06</v>
+        <v>4.7953007317183202e-07</v>
       </c>
       <c r="V4">
-        <v>7.9392659110029943e-07</v>
+        <v>4.1757462749229513e-06</v>
       </c>
       <c r="W4">
-        <v>2.2385276561586834e-06</v>
+        <v>9.0305587337487751e-07</v>
       </c>
       <c r="X4">
-        <v>-5.0764350912784796e-08</v>
+        <v>2.2494239875276752e-06</v>
       </c>
       <c r="Y4">
-        <v>7.5598983291268453e-06</v>
+        <v>-4.0966235322160223e-09</v>
       </c>
       <c r="Z4">
-        <v>9.5968162963645088e-07</v>
+        <v>6.4749595984658732e-06</v>
       </c>
       <c r="AA4">
-        <v>-6.2298458975221238e-07</v>
+        <v>6.7845143132435861e-07</v>
       </c>
       <c r="AB4">
-        <v>1.6337636712074235e-08</v>
+        <v>-6.4226139312095949e-07</v>
       </c>
       <c r="AC4">
-        <v>3.6451992819760764e-06</v>
+        <v>1.7554184113501017e-08</v>
       </c>
       <c r="AD4">
-        <v>4.4418989474176646e-06</v>
+        <v>3.8559943109072196e-06</v>
       </c>
       <c r="AE4">
-        <v>2.7680291872209567e-06</v>
+        <v>4.5446123549131305e-06</v>
       </c>
       <c r="AF4">
-        <v>3.0622265848598892e-06</v>
+        <v>2.8008612660330339e-06</v>
       </c>
       <c r="AG4">
-        <v>2.8186374644986398e-06</v>
+        <v>3.4113027974215341e-06</v>
       </c>
       <c r="AH4">
-        <v>3.9839162319782326e-06</v>
+        <v>3.1354343175727539e-06</v>
       </c>
       <c r="AI4">
-        <v>0.00030522568860010516</v>
+        <v>4.2500031558900272e-06</v>
+      </c>
+      <c r="AJ4">
+        <v>0.00030329743687748336</v>
       </c>
     </row>
     <row r="5">
@@ -843,106 +858,109 @@
         <v>27</v>
       </c>
       <c r="B5">
-        <v>0.38499667568016122</v>
+        <v>0.35718175015469528</v>
       </c>
       <c r="C5">
-        <v>-0.0020299719301921648</v>
+        <v>-0.0019806546731783448</v>
       </c>
       <c r="D5">
-        <v>-0.00012518344544707079</v>
+        <v>-0.00025903859447572869</v>
       </c>
       <c r="E5">
-        <v>1.1863473408743228e-06</v>
+        <v>3.0440925414201175e-06</v>
       </c>
       <c r="F5">
-        <v>0.10906113185334199</v>
+        <v>0.11090863563757386</v>
       </c>
       <c r="G5">
-        <v>0.069184452689582288</v>
+        <v>0.070991138447904223</v>
       </c>
       <c r="H5">
-        <v>0.069106870033010581</v>
+        <v>0.07091228232359098</v>
       </c>
       <c r="I5">
-        <v>0.069085625942935658</v>
+        <v>0.07088579238361431</v>
       </c>
       <c r="J5">
-        <v>0.00046318587085100033</v>
+        <v>0.00033937413316854036</v>
       </c>
       <c r="K5">
-        <v>-0.00063637500247866463</v>
+        <v>-0.00063051999708914341</v>
       </c>
       <c r="L5">
-        <v>9.8029129708569751e-05</v>
+        <v>9.7337037995151587e-05</v>
       </c>
       <c r="M5">
-        <v>-0.00055796006698365097</v>
+        <v>-0.00057109175587347419</v>
       </c>
       <c r="N5">
-        <v>0.00051419327264094761</v>
+        <v>0.00036570032321804613</v>
       </c>
       <c r="O5">
-        <v>-0.00078818304856614896</v>
+        <v>-0.00090412420021965256</v>
       </c>
       <c r="P5">
-        <v>-0.00080702049760759606</v>
+        <v>-0.0011370334412190777</v>
       </c>
       <c r="Q5">
-        <v>-0.00096483382860985956</v>
+        <v>-0.0013232822363664666</v>
       </c>
       <c r="R5">
-        <v>-0.00055598828177176422</v>
+        <v>-0.00095340245750266672</v>
       </c>
       <c r="S5">
-        <v>-0.00056296117222746911</v>
+        <v>-0.00090716218822905342</v>
       </c>
       <c r="T5">
-        <v>0.00019283274636152509</v>
+        <v>6.7708413812345159e-05</v>
       </c>
       <c r="U5">
-        <v>-4.4131606317131256e-05</v>
+        <v>0.0005884381129871788</v>
       </c>
       <c r="V5">
-        <v>-0.00056880340337257113</v>
+        <v>6.8978488783139752e-05</v>
       </c>
       <c r="W5">
-        <v>-0.00034499406447835099</v>
+        <v>-0.00043960912064326674</v>
       </c>
       <c r="X5">
-        <v>-6.1679006406176184e-05</v>
+        <v>-0.00019561891786943827</v>
       </c>
       <c r="Y5">
-        <v>-0.00059552817936721694</v>
+        <v>-8.9249421394238526e-05</v>
       </c>
       <c r="Z5">
-        <v>0.00035352782538422556</v>
+        <v>-0.00078604493774756673</v>
       </c>
       <c r="AA5">
-        <v>-0.00019073705750968784</v>
+        <v>0.0002541317112012137</v>
       </c>
       <c r="AB5">
-        <v>3.7792907982159979e-06</v>
+        <v>-6.2917903985659773e-05</v>
       </c>
       <c r="AC5">
-        <v>-0.00019699754339597142</v>
+        <v>-6.4020514655219185e-08</v>
       </c>
       <c r="AD5">
-        <v>-0.00020824551216924725</v>
+        <v>-0.00026963384057465678</v>
       </c>
       <c r="AE5">
-        <v>0.00017468720633960488</v>
+        <v>-0.00030229303508072514</v>
       </c>
       <c r="AF5">
-        <v>3.2859136858631732e-05</v>
+        <v>5.1111423175653759e-05</v>
       </c>
       <c r="AG5">
-        <v>0.0004373057883380882</v>
+        <v>-5.3124251327252292e-05</v>
       </c>
       <c r="AH5">
-        <v>-2.6705380407290868e-05</v>
+        <v>0.00030951872868142938</v>
       </c>
       <c r="AI5">
-        <v>-0.061142915903919799</v>
+        <v>-0.00010427112488800572</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.060133749086610844</v>
       </c>
     </row>
     <row r="6">
@@ -950,106 +968,109 @@
         <v>28</v>
       </c>
       <c r="B6">
-        <v>0.53344567751760852</v>
+        <v>0.50179381713219884</v>
       </c>
       <c r="C6">
-        <v>0.005378909669715326</v>
+        <v>0.0069914406088493475</v>
       </c>
       <c r="D6">
-        <v>0.00038556538267762314</v>
+        <v>0.00037875841799748199</v>
       </c>
       <c r="E6">
-        <v>-5.1005778139603768e-06</v>
+        <v>-4.8806396285952004e-06</v>
       </c>
       <c r="F6">
-        <v>0.069184452689582288</v>
+        <v>0.070991138447904223</v>
       </c>
       <c r="G6">
-        <v>0.073655487976724943</v>
+        <v>0.075658980542603005</v>
       </c>
       <c r="H6">
-        <v>0.069401254303500304</v>
+        <v>0.071252633349476957</v>
       </c>
       <c r="I6">
-        <v>0.069454023696750356</v>
+        <v>0.07131270814220203</v>
       </c>
       <c r="J6">
-        <v>0.00068148746686867365</v>
+        <v>0.00066850949550915223</v>
       </c>
       <c r="K6">
-        <v>6.8733378816729362e-05</v>
+        <v>4.6905579984810042e-05</v>
       </c>
       <c r="L6">
-        <v>-0.00018403135429036731</v>
+        <v>-0.00025743881702642441</v>
       </c>
       <c r="M6">
-        <v>-0.00076727986982561697</v>
+        <v>-0.00076439992084379946</v>
       </c>
       <c r="N6">
-        <v>-8.3041837271702335e-05</v>
+        <v>-0.00016569136548562347</v>
       </c>
       <c r="O6">
-        <v>-0.00047856715377456172</v>
+        <v>-0.00048266061529286808</v>
       </c>
       <c r="P6">
-        <v>-0.00033352061314261342</v>
+        <v>-0.00046196326867928988</v>
       </c>
       <c r="Q6">
-        <v>-0.00022244512247700937</v>
+        <v>-0.00030498902773365422</v>
       </c>
       <c r="R6">
-        <v>-0.000308577150588513</v>
+        <v>-0.00037504183842230338</v>
       </c>
       <c r="S6">
-        <v>-0.00034958377009881164</v>
+        <v>-0.00045033030282543019</v>
       </c>
       <c r="T6">
-        <v>1.9760103432454185e-05</v>
+        <v>-0.00031849112729133433</v>
       </c>
       <c r="U6">
-        <v>-6.5531235964380596e-06</v>
+        <v>8.3216341128927729e-05</v>
       </c>
       <c r="V6">
-        <v>-6.7591148885701169e-05</v>
+        <v>0.00012280573773625764</v>
       </c>
       <c r="W6">
-        <v>-0.00018649824329965495</v>
+        <v>-1.9161969688527569e-05</v>
       </c>
       <c r="X6">
-        <v>4.6842525336376895e-05</v>
+        <v>-0.00015887896411250629</v>
       </c>
       <c r="Y6">
-        <v>-6.578249448698989e-05</v>
+        <v>3.0230494891259063e-06</v>
       </c>
       <c r="Z6">
-        <v>0.00010995260095963966</v>
+        <v>-3.9762688375737099e-05</v>
       </c>
       <c r="AA6">
-        <v>-0.0001160488282910821</v>
+        <v>8.5140332353350612e-05</v>
       </c>
       <c r="AB6">
-        <v>3.6596137237276949e-06</v>
+        <v>-4.8323662136001699e-05</v>
       </c>
       <c r="AC6">
-        <v>6.8786265495446308e-05</v>
+        <v>1.0138052308726608e-06</v>
       </c>
       <c r="AD6">
-        <v>-0.00036735892814038218</v>
+        <v>-2.722479090172536e-05</v>
       </c>
       <c r="AE6">
-        <v>-0.00014678654306091166</v>
+        <v>-0.00050747929637179334</v>
       </c>
       <c r="AF6">
-        <v>-0.00037585828223651863</v>
+        <v>-0.00028813322742500536</v>
       </c>
       <c r="AG6">
-        <v>-0.00035559774632820673</v>
+        <v>-0.00052548304366584198</v>
       </c>
       <c r="AH6">
-        <v>-0.00054884068747695913</v>
+        <v>-0.0004638058761665953</v>
       </c>
       <c r="AI6">
-        <v>-0.07692951241091886</v>
+        <v>-0.00073041362526063414</v>
+      </c>
+      <c r="AJ6">
+        <v>-0.077140312484265283</v>
       </c>
     </row>
     <row r="7">
@@ -1057,106 +1078,109 @@
         <v>29</v>
       </c>
       <c r="B7">
-        <v>0.82166551148836897</v>
+        <v>0.79271785610069712</v>
       </c>
       <c r="C7">
-        <v>0.0047083300805478845</v>
+        <v>0.0053225052952228513</v>
       </c>
       <c r="D7">
-        <v>0.00019624820830609763</v>
+        <v>0.00019802447148850773</v>
       </c>
       <c r="E7">
-        <v>-2.4011107857440425e-06</v>
+        <v>-2.3491670395210911e-06</v>
       </c>
       <c r="F7">
-        <v>0.069106870033010581</v>
+        <v>0.07091228232359098</v>
       </c>
       <c r="G7">
-        <v>0.069401254303500304</v>
+        <v>0.071252633349476957</v>
       </c>
       <c r="H7">
-        <v>0.069834806542772909</v>
+        <v>0.071708815946861126</v>
       </c>
       <c r="I7">
-        <v>0.069491254259767099</v>
+        <v>0.071362761722253198</v>
       </c>
       <c r="J7">
-        <v>0.00053017393119329792</v>
+        <v>0.00048336547520136733</v>
       </c>
       <c r="K7">
-        <v>-0.00036795225818450628</v>
+        <v>-0.00036510867326244867</v>
       </c>
       <c r="L7">
-        <v>-0.00017267346607024482</v>
+        <v>-0.00020253263807616662</v>
       </c>
       <c r="M7">
-        <v>-0.00065481860902761799</v>
+        <v>-0.00056979834011672628</v>
       </c>
       <c r="N7">
-        <v>0.00024388790725282661</v>
+        <v>0.00022825039166399219</v>
       </c>
       <c r="O7">
-        <v>-0.00086604277735241597</v>
+        <v>-0.000874177638921253</v>
       </c>
       <c r="P7">
-        <v>-4.5917754549970602e-06</v>
+        <v>-0.00013551497840506854</v>
       </c>
       <c r="Q7">
-        <v>-0.00025683700062710535</v>
+        <v>-0.0002990901207749197</v>
       </c>
       <c r="R7">
-        <v>-0.00024948015868723507</v>
+        <v>-0.00029724317080510702</v>
       </c>
       <c r="S7">
-        <v>-0.00028649373855649252</v>
+        <v>-0.00033049685513933391</v>
       </c>
       <c r="T7">
-        <v>-9.0255950355010856e-05</v>
+        <v>-0.00029751787683207631</v>
       </c>
       <c r="U7">
-        <v>-0.00014735224089427318</v>
+        <v>-0.00013730376260434607</v>
       </c>
       <c r="V7">
-        <v>0.00011914232424628524</v>
+        <v>-0.00016360283807634671</v>
       </c>
       <c r="W7">
-        <v>-4.5488267761299023e-05</v>
+        <v>0.00013719780070220455</v>
       </c>
       <c r="X7">
-        <v>2.850674282510457e-05</v>
+        <v>-1.7749614095067395e-05</v>
       </c>
       <c r="Y7">
-        <v>-9.4500699416515122e-05</v>
+        <v>-1.2587281779413706e-05</v>
       </c>
       <c r="Z7">
-        <v>0.0002903765424918936</v>
+        <v>-2.5785282258307396e-05</v>
       </c>
       <c r="AA7">
-        <v>-0.00013474179715905477</v>
+        <v>0.00032559139890397937</v>
       </c>
       <c r="AB7">
-        <v>4.2256210295629065e-06</v>
+        <v>-8.9351585151747903e-05</v>
       </c>
       <c r="AC7">
-        <v>-0.00042780656961566299</v>
+        <v>2.2603731803256394e-06</v>
       </c>
       <c r="AD7">
-        <v>-0.0005574749959784131</v>
+        <v>-0.0005194671027988762</v>
       </c>
       <c r="AE7">
-        <v>-0.00017287982960645376</v>
+        <v>-0.00065521853583794254</v>
       </c>
       <c r="AF7">
-        <v>-0.00038913928229977746</v>
+        <v>-0.00030694086771507201</v>
       </c>
       <c r="AG7">
-        <v>-0.00032075966531550093</v>
+        <v>-0.00049800624425511142</v>
       </c>
       <c r="AH7">
-        <v>-0.00049815122937303669</v>
+        <v>-0.00039600732195300969</v>
       </c>
       <c r="AI7">
-        <v>-0.072827229016091288</v>
+        <v>-0.00060407156948102947</v>
+      </c>
+      <c r="AJ7">
+        <v>-0.073182202790631645</v>
       </c>
     </row>
     <row r="8">
@@ -1164,106 +1188,109 @@
         <v>30</v>
       </c>
       <c r="B8">
-        <v>0.89559071669836277</v>
+        <v>0.87029489645335634</v>
       </c>
       <c r="C8">
-        <v>0.0056948946196553885</v>
+        <v>0.0066617728859940939</v>
       </c>
       <c r="D8">
-        <v>0.0003550627913427775</v>
+        <v>0.00035183995322166616</v>
       </c>
       <c r="E8">
-        <v>-4.4720301458506533e-06</v>
+        <v>-4.3174216617076317e-06</v>
       </c>
       <c r="F8">
-        <v>0.069085625942935658</v>
+        <v>0.07088579238361431</v>
       </c>
       <c r="G8">
-        <v>0.069454023696750356</v>
+        <v>0.07131270814220203</v>
       </c>
       <c r="H8">
-        <v>0.069491254259767099</v>
+        <v>0.071362761722253198</v>
       </c>
       <c r="I8">
-        <v>0.070550391188018868</v>
+        <v>0.072459843746936259</v>
       </c>
       <c r="J8">
-        <v>0.00053158351885719893</v>
+        <v>0.00048444045465258386</v>
       </c>
       <c r="K8">
-        <v>-0.00035830875664774609</v>
+        <v>-0.00038324045358537062</v>
       </c>
       <c r="L8">
-        <v>-0.00023296121209230407</v>
+        <v>-0.00028134456924309298</v>
       </c>
       <c r="M8">
-        <v>-0.00063072935757853624</v>
+        <v>-0.00056589372103480959</v>
       </c>
       <c r="N8">
-        <v>0.00020394082927492618</v>
+        <v>0.00018671209149849488</v>
       </c>
       <c r="O8">
-        <v>0.0005771642808234112</v>
+        <v>0.00061533691292992021</v>
       </c>
       <c r="P8">
-        <v>2.400955892626136e-05</v>
+        <v>-6.7238298140141761e-05</v>
       </c>
       <c r="Q8">
-        <v>-0.00016388516025710176</v>
+        <v>-0.00016598741552827784</v>
       </c>
       <c r="R8">
-        <v>-0.00022128813635778275</v>
+        <v>-0.00025988306405460779</v>
       </c>
       <c r="S8">
-        <v>-0.0002261463912025391</v>
+        <v>-0.00025563365540589092</v>
       </c>
       <c r="T8">
-        <v>-6.3366177249980782e-05</v>
+        <v>-0.00032930967045939619</v>
       </c>
       <c r="U8">
-        <v>-0.00021581421589400573</v>
+        <v>-0.00016425396908717471</v>
       </c>
       <c r="V8">
-        <v>0.00022908159705351677</v>
+        <v>-0.0001847887030670646</v>
       </c>
       <c r="W8">
-        <v>-0.00017955549617110211</v>
+        <v>0.00025257432929338963</v>
       </c>
       <c r="X8">
-        <v>-2.3004726905070938e-05</v>
+        <v>-0.00015263677111317792</v>
       </c>
       <c r="Y8">
-        <v>-0.000254042385207702</v>
+        <v>-5.8344592110820548e-05</v>
       </c>
       <c r="Z8">
-        <v>0.00028627843108514073</v>
+        <v>-0.00016863984768275553</v>
       </c>
       <c r="AA8">
-        <v>1.38021883758499e-05</v>
+        <v>0.000337733709171395</v>
       </c>
       <c r="AB8">
-        <v>-5.7753898192840214e-07</v>
+        <v>7.1281580288184987e-05</v>
       </c>
       <c r="AC8">
-        <v>-0.000324765342721689</v>
+        <v>-2.7577286006042617e-06</v>
       </c>
       <c r="AD8">
-        <v>-0.00057493221463100763</v>
+        <v>-0.00042836153031172719</v>
       </c>
       <c r="AE8">
-        <v>-0.0002283139001940937</v>
+        <v>-0.00068299009515571108</v>
       </c>
       <c r="AF8">
-        <v>-0.00039250915359423377</v>
+        <v>-0.00036555191390709452</v>
       </c>
       <c r="AG8">
-        <v>-0.00031641590305528378</v>
+        <v>-0.00051092846576128448</v>
       </c>
       <c r="AH8">
-        <v>-0.00059871869722495641</v>
+        <v>-0.00040214909048520708</v>
       </c>
       <c r="AI8">
-        <v>-0.074902994544512672</v>
+        <v>-0.00072643168811993564</v>
+      </c>
+      <c r="AJ8">
+        <v>-0.075567392646664261</v>
       </c>
     </row>
     <row r="9">
@@ -1271,106 +1298,109 @@
         <v>31</v>
       </c>
       <c r="B9">
-        <v>-1.2342576096501659</v>
+        <v>-1.2288194217681772</v>
       </c>
       <c r="C9">
-        <v>0.0089088725539483229</v>
+        <v>0.0068401309091116634</v>
       </c>
       <c r="D9">
-        <v>0.00051379937646650327</v>
+        <v>0.0004770352383460663</v>
       </c>
       <c r="E9">
-        <v>-6.2407736092217277e-06</v>
+        <v>-5.755835934742876e-06</v>
       </c>
       <c r="F9">
-        <v>0.00046318587085100033</v>
+        <v>0.00033937413316854036</v>
       </c>
       <c r="G9">
-        <v>0.00068148746686867365</v>
+        <v>0.00066850949550915223</v>
       </c>
       <c r="H9">
-        <v>0.00053017393119329792</v>
+        <v>0.00048336547520136733</v>
       </c>
       <c r="I9">
-        <v>0.00053158351885719893</v>
+        <v>0.00048444045465258386</v>
       </c>
       <c r="J9">
-        <v>0.018440542691919269</v>
+        <v>0.01826703213828787</v>
       </c>
       <c r="K9">
-        <v>-0.015527798183874167</v>
+        <v>-0.015322354560187542</v>
       </c>
       <c r="L9">
-        <v>-0.00029371599958073627</v>
+        <v>-0.00020147815729475724</v>
       </c>
       <c r="M9">
-        <v>-0.018585341319077121</v>
+        <v>-0.018358693628204966</v>
       </c>
       <c r="N9">
-        <v>0.015575517732869392</v>
+        <v>0.015490124812957137</v>
       </c>
       <c r="O9">
-        <v>0.00013625228455299912</v>
+        <v>0.00016721877051585664</v>
       </c>
       <c r="P9">
-        <v>-0.00020478891571190378</v>
+        <v>-0.00025645949140334901</v>
       </c>
       <c r="Q9">
-        <v>-0.00023398721957393646</v>
+        <v>-0.00024036252563609069</v>
       </c>
       <c r="R9">
-        <v>9.239123820556247e-05</v>
+        <v>6.2522710901730368e-05</v>
       </c>
       <c r="S9">
-        <v>-0.0001399048814895523</v>
+        <v>-0.0001319750251310505</v>
       </c>
       <c r="T9">
-        <v>5.311176028970565e-06</v>
+        <v>0.00027584060762993363</v>
       </c>
       <c r="U9">
-        <v>0.00018387983840504436</v>
+        <v>7.7532943543886525e-05</v>
       </c>
       <c r="V9">
-        <v>0.0004354975253703261</v>
+        <v>0.00015610081180726291</v>
       </c>
       <c r="W9">
-        <v>3.4900043021665313e-05</v>
+        <v>0.00040864141282163187</v>
       </c>
       <c r="X9">
-        <v>0.00018738626967574907</v>
+        <v>5.8354328227125781e-05</v>
       </c>
       <c r="Y9">
-        <v>-0.00043014663693432057</v>
+        <v>0.00020320250088897319</v>
       </c>
       <c r="Z9">
-        <v>-4.8485918077898231e-05</v>
+        <v>-0.00042162893040731755</v>
       </c>
       <c r="AA9">
-        <v>-0.00040578728455636102</v>
+        <v>-5.1104846317391985e-05</v>
       </c>
       <c r="AB9">
-        <v>1.4950737462750193e-05</v>
+        <v>-0.00044264654520438434</v>
       </c>
       <c r="AC9">
-        <v>0.00064035711923646601</v>
+        <v>1.6187036676253573e-05</v>
       </c>
       <c r="AD9">
-        <v>0.00026474484208860016</v>
+        <v>0.00071167103031875151</v>
       </c>
       <c r="AE9">
-        <v>0.00039196167911758251</v>
+        <v>0.0002955191502173873</v>
       </c>
       <c r="AF9">
-        <v>0.00041074118580697013</v>
+        <v>0.00043743257823449259</v>
       </c>
       <c r="AG9">
-        <v>0.00067096704356365915</v>
+        <v>0.00046058125842611715</v>
       </c>
       <c r="AH9">
-        <v>0.00026785724039906636</v>
+        <v>0.00070204836502050323</v>
       </c>
       <c r="AI9">
-        <v>-0.016273479518709041</v>
+        <v>0.00032291640328157949</v>
+      </c>
+      <c r="AJ9">
+        <v>-0.016078198363168674</v>
       </c>
     </row>
     <row r="10">
@@ -1378,106 +1408,109 @@
         <v>32</v>
       </c>
       <c r="B10">
-        <v>0.05701392036583415</v>
+        <v>0.1053999587401252</v>
       </c>
       <c r="C10">
-        <v>-0.0045807759269763867</v>
+        <v>-0.0044960599519654615</v>
       </c>
       <c r="D10">
-        <v>1.2034036398811659e-05</v>
+        <v>2.8523648163845863e-05</v>
       </c>
       <c r="E10">
-        <v>-3.8194073036045386e-08</v>
+        <v>-3.2318630677959114e-07</v>
       </c>
       <c r="F10">
-        <v>-0.00063637500247866463</v>
+        <v>-0.00063051999708914341</v>
       </c>
       <c r="G10">
-        <v>6.8733378816729362e-05</v>
+        <v>4.6905579984810042e-05</v>
       </c>
       <c r="H10">
-        <v>-0.00036795225818450628</v>
+        <v>-0.00036510867326244867</v>
       </c>
       <c r="I10">
-        <v>-0.00035830875664774609</v>
+        <v>-0.00038324045358537062</v>
       </c>
       <c r="J10">
-        <v>-0.015527798183874167</v>
+        <v>-0.015322354560187542</v>
       </c>
       <c r="K10">
-        <v>0.01627178381924119</v>
+        <v>0.016142930743019788</v>
       </c>
       <c r="L10">
-        <v>0.00023715665163024627</v>
+        <v>0.00023917861658259267</v>
       </c>
       <c r="M10">
-        <v>0.015746111099338378</v>
+        <v>0.015487012597818088</v>
       </c>
       <c r="N10">
-        <v>-0.015802946564907074</v>
+        <v>-0.015728458695750677</v>
       </c>
       <c r="O10">
-        <v>0.00010486296452688333</v>
+        <v>1.2557975438453272e-05</v>
       </c>
       <c r="P10">
-        <v>0.00051816736153950985</v>
+        <v>0.00059879255969465424</v>
       </c>
       <c r="Q10">
-        <v>0.00083369776744187112</v>
+        <v>0.00084987130572135945</v>
       </c>
       <c r="R10">
-        <v>0.00083696292260326268</v>
+        <v>0.00091244289669354241</v>
       </c>
       <c r="S10">
-        <v>0.0011922595443167273</v>
+        <v>0.0012465220329281651</v>
       </c>
       <c r="T10">
-        <v>0.00031968392404982014</v>
+        <v>0.00044434752343775667</v>
       </c>
       <c r="U10">
-        <v>5.2026151820094765e-05</v>
+        <v>0.0007299781743081771</v>
       </c>
       <c r="V10">
-        <v>-3.18799757991028e-05</v>
+        <v>8.4228112378104903e-05</v>
       </c>
       <c r="W10">
-        <v>-0.00027995311683873936</v>
+        <v>-7.4718561288690018e-05</v>
       </c>
       <c r="X10">
-        <v>4.2639279417184834e-07</v>
+        <v>-0.00026887173349688135</v>
       </c>
       <c r="Y10">
-        <v>0.00022887317678900478</v>
+        <v>-5.2089042598708478e-06</v>
       </c>
       <c r="Z10">
-        <v>0.00023670175134485455</v>
+        <v>0.00015690793646992561</v>
       </c>
       <c r="AA10">
-        <v>0.00020889845789145924</v>
+        <v>0.00025335319509769689</v>
       </c>
       <c r="AB10">
-        <v>-5.842763345124245e-06</v>
+        <v>0.00021272869895610613</v>
       </c>
       <c r="AC10">
-        <v>-0.00040729115004866496</v>
+        <v>-5.9608906500921002e-06</v>
       </c>
       <c r="AD10">
-        <v>-0.00027490264218683988</v>
+        <v>-0.0004843125908789755</v>
       </c>
       <c r="AE10">
-        <v>-0.00046727857092587012</v>
+        <v>-0.0003101845513583145</v>
       </c>
       <c r="AF10">
-        <v>-0.00048629489875235505</v>
+        <v>-0.00050411556076881427</v>
       </c>
       <c r="AG10">
-        <v>-0.00062927862323973265</v>
+        <v>-0.00055116890330128305</v>
       </c>
       <c r="AH10">
-        <v>-0.00042034453788511125</v>
+        <v>-0.00068720238313065441</v>
       </c>
       <c r="AI10">
-        <v>-0.0028706581611771622</v>
+        <v>-0.00047989350412604924</v>
+      </c>
+      <c r="AJ10">
+        <v>-0.0029590583490347162</v>
       </c>
     </row>
     <row r="11">
@@ -1485,106 +1518,109 @@
         <v>33</v>
       </c>
       <c r="B11">
-        <v>-0.46011090467005311</v>
+        <v>-0.39439438984358721</v>
       </c>
       <c r="C11">
-        <v>-0.13666820742910732</v>
+        <v>-0.12910664187354523</v>
       </c>
       <c r="D11">
-        <v>-0.00061560548759721236</v>
+        <v>-0.00060590155380684484</v>
       </c>
       <c r="E11">
-        <v>8.2467636077627966e-06</v>
+        <v>8.0168792119224057e-06</v>
       </c>
       <c r="F11">
-        <v>9.8029129708569751e-05</v>
+        <v>9.7337037995151587e-05</v>
       </c>
       <c r="G11">
-        <v>-0.00018403135429036731</v>
+        <v>-0.00025743881702642441</v>
       </c>
       <c r="H11">
-        <v>-0.00017267346607024482</v>
+        <v>-0.00020253263807616662</v>
       </c>
       <c r="I11">
-        <v>-0.00023296121209230407</v>
+        <v>-0.00028134456924309298</v>
       </c>
       <c r="J11">
-        <v>-0.00029371599958073627</v>
+        <v>-0.00020147815729475724</v>
       </c>
       <c r="K11">
-        <v>0.00023715665163024627</v>
+        <v>0.00023917861658259267</v>
       </c>
       <c r="L11">
-        <v>0.0047327264839605475</v>
+        <v>0.004466257423477323</v>
       </c>
       <c r="M11">
-        <v>0.02024407020460053</v>
+        <v>0.01930338745606433</v>
       </c>
       <c r="N11">
-        <v>0.023638017442305884</v>
+        <v>0.02270165458918429</v>
       </c>
       <c r="O11">
-        <v>0.012232323890196826</v>
+        <v>0.010925551780011766</v>
       </c>
       <c r="P11">
-        <v>-0.00043967793782724455</v>
+        <v>-0.00029330910579033987</v>
       </c>
       <c r="Q11">
-        <v>0.00048770695089095714</v>
+        <v>0.00050280877392754964</v>
       </c>
       <c r="R11">
-        <v>0.00060797376783038536</v>
+        <v>0.00066389538491095224</v>
       </c>
       <c r="S11">
-        <v>0.00078436264105729518</v>
+        <v>0.00086106661336901613</v>
       </c>
       <c r="T11">
-        <v>0.00029040440175441616</v>
+        <v>0.00063214033868301978</v>
       </c>
       <c r="U11">
-        <v>-0.00015136464462205124</v>
+        <v>0.00064658426680226384</v>
       </c>
       <c r="V11">
-        <v>3.3006796986939473e-06</v>
+        <v>-0.00021087268036293675</v>
       </c>
       <c r="W11">
-        <v>5.6735932334623274e-05</v>
+        <v>-3.4955021206470316e-05</v>
       </c>
       <c r="X11">
-        <v>-8.518967574418332e-05</v>
+        <v>7.4104563116129593e-05</v>
       </c>
       <c r="Y11">
-        <v>0.0009364478418040249</v>
+        <v>-5.8032315052613083e-05</v>
       </c>
       <c r="Z11">
-        <v>0.00026691023006594674</v>
+        <v>0.00081496363643340482</v>
       </c>
       <c r="AA11">
-        <v>3.9509382272978969e-06</v>
+        <v>0.00028145696276422947</v>
       </c>
       <c r="AB11">
-        <v>-1.657848064615374e-06</v>
+        <v>-3.8646629756339777e-05</v>
       </c>
       <c r="AC11">
-        <v>-0.00053456493072570437</v>
+        <v>9.1034956044077709e-08</v>
       </c>
       <c r="AD11">
-        <v>-0.00043824622233876957</v>
+        <v>-0.00048968528688025491</v>
       </c>
       <c r="AE11">
-        <v>-0.00053827432424176087</v>
+        <v>-0.00038332998564618616</v>
       </c>
       <c r="AF11">
-        <v>-0.00054105770059326673</v>
+        <v>-0.00050383865992559848</v>
       </c>
       <c r="AG11">
-        <v>-0.00054505874245996846</v>
+        <v>-0.00047085365539634855</v>
       </c>
       <c r="AH11">
-        <v>-0.00045213393508005024</v>
+        <v>-0.00048319697802431711</v>
       </c>
       <c r="AI11">
-        <v>0.014770115678727103</v>
+        <v>-0.00039388708121651864</v>
+      </c>
+      <c r="AJ11">
+        <v>0.013623117641510661</v>
       </c>
     </row>
     <row r="12">
@@ -1592,106 +1628,109 @@
         <v>34</v>
       </c>
       <c r="B12">
-        <v>-0.46591409422087526</v>
+        <v>-0.42703433964403537</v>
       </c>
       <c r="C12">
-        <v>-0.70314136262784777</v>
+        <v>-0.67873172975765528</v>
       </c>
       <c r="D12">
-        <v>-0.00069946551586146349</v>
+        <v>-0.00066020688256818356</v>
       </c>
       <c r="E12">
-        <v>8.6886523741590954e-06</v>
+        <v>8.1691724576419637e-06</v>
       </c>
       <c r="F12">
-        <v>-0.00055796006698365097</v>
+        <v>-0.00057109175587347419</v>
       </c>
       <c r="G12">
-        <v>-0.00076727986982561697</v>
+        <v>-0.00076439992084379946</v>
       </c>
       <c r="H12">
-        <v>-0.00065481860902761799</v>
+        <v>-0.00056979834011672628</v>
       </c>
       <c r="I12">
-        <v>-0.00063072935757853624</v>
+        <v>-0.00056589372103480959</v>
       </c>
       <c r="J12">
-        <v>-0.018585341319077121</v>
+        <v>-0.018358693628204966</v>
       </c>
       <c r="K12">
-        <v>0.015746111099338378</v>
+        <v>0.015487012597818088</v>
       </c>
       <c r="L12">
-        <v>0.02024407020460053</v>
+        <v>0.01930338745606433</v>
       </c>
       <c r="M12">
-        <v>0.34387877184465354</v>
+        <v>0.32072921119788811</v>
       </c>
       <c r="N12">
-        <v>-0.022581924545659833</v>
+        <v>-0.0039080193918140885</v>
       </c>
       <c r="O12">
-        <v>0.090293161016446535</v>
+        <v>0.084623594331150673</v>
       </c>
       <c r="P12">
-        <v>-0.00026102498947001753</v>
+        <v>0.00010427264004039295</v>
       </c>
       <c r="Q12">
-        <v>0.00081646922040840789</v>
+        <v>0.00087249091734782505</v>
       </c>
       <c r="R12">
-        <v>0.00082569221420482472</v>
+        <v>0.00092592678077957195</v>
       </c>
       <c r="S12">
-        <v>0.0010245123342594415</v>
+        <v>0.0010688269352444844</v>
       </c>
       <c r="T12">
-        <v>0.00017714193772328381</v>
+        <v>-9.3899970209110686e-05</v>
       </c>
       <c r="U12">
-        <v>-0.00035532925225286761</v>
+        <v>0.00021857877783650536</v>
       </c>
       <c r="V12">
-        <v>-0.00041984523326343186</v>
+        <v>-0.00026539830497367828</v>
       </c>
       <c r="W12">
-        <v>2.2198636438916942e-05</v>
+        <v>-0.00039125422590610692</v>
       </c>
       <c r="X12">
-        <v>-0.00070603229604999668</v>
+        <v>2.2294010395177517e-06</v>
       </c>
       <c r="Y12">
-        <v>0.0016025197754252654</v>
+        <v>-0.00068362442644818999</v>
       </c>
       <c r="Z12">
-        <v>0.00043602477581287198</v>
+        <v>0.0014404235926219118</v>
       </c>
       <c r="AA12">
-        <v>0.0005563956985397446</v>
+        <v>0.00043404234164555553</v>
       </c>
       <c r="AB12">
-        <v>-2.8122226782190736e-05</v>
+        <v>0.00055623889438208632</v>
       </c>
       <c r="AC12">
-        <v>-0.0027004584629066221</v>
+        <v>-2.7567916788975833e-05</v>
       </c>
       <c r="AD12">
-        <v>-0.0022746277761699369</v>
+        <v>-0.0027267800837532923</v>
       </c>
       <c r="AE12">
-        <v>-0.0026229122312671298</v>
+        <v>-0.0022728772854662006</v>
       </c>
       <c r="AF12">
-        <v>-0.0025877187412414633</v>
+        <v>-0.0026334675305861605</v>
       </c>
       <c r="AG12">
-        <v>-0.0026887852341772166</v>
+        <v>-0.0025787895997136084</v>
       </c>
       <c r="AH12">
-        <v>-0.0019966838962494384</v>
+        <v>-0.0026695457881824917</v>
       </c>
       <c r="AI12">
-        <v>0.042560118928667803</v>
+        <v>-0.0020049185779722851</v>
+      </c>
+      <c r="AJ12">
+        <v>0.040768146586417725</v>
       </c>
     </row>
     <row r="13">
@@ -1699,106 +1738,109 @@
         <v>35</v>
       </c>
       <c r="B13">
-        <v>-2.0861015762383079</v>
+        <v>-2.0375665761706494</v>
       </c>
       <c r="C13">
-        <v>-0.80687831594874504</v>
+        <v>-0.78093632353149845</v>
       </c>
       <c r="D13">
-        <v>-0.00018631616516383764</v>
+        <v>-0.00019717856783842006</v>
       </c>
       <c r="E13">
-        <v>2.2151028291856893e-06</v>
+        <v>2.3262631773805615e-06</v>
       </c>
       <c r="F13">
-        <v>0.00051419327264094761</v>
+        <v>0.00036570032321804613</v>
       </c>
       <c r="G13">
-        <v>-8.3041837271702335e-05</v>
+        <v>-0.00016569136548562347</v>
       </c>
       <c r="H13">
-        <v>0.00024388790725282661</v>
+        <v>0.00022825039166399219</v>
       </c>
       <c r="I13">
-        <v>0.00020394082927492618</v>
+        <v>0.00018671209149849488</v>
       </c>
       <c r="J13">
-        <v>0.015575517732869392</v>
+        <v>0.015490124812957137</v>
       </c>
       <c r="K13">
-        <v>-0.015802946564907074</v>
+        <v>-0.015728458695750677</v>
       </c>
       <c r="L13">
-        <v>0.023638017442305884</v>
+        <v>0.02270165458918429</v>
       </c>
       <c r="M13">
-        <v>-0.022581924545659833</v>
+        <v>-0.0039080193918140885</v>
       </c>
       <c r="N13">
-        <v>0.3834746515043867</v>
+        <v>0.35907189827393537</v>
       </c>
       <c r="O13">
-        <v>0.094411557125440693</v>
+        <v>0.087468024927459046</v>
       </c>
       <c r="P13">
-        <v>-0.0018734686406386872</v>
+        <v>-0.0015907037189158693</v>
       </c>
       <c r="Q13">
-        <v>0.00011095190473632956</v>
+        <v>0.00017763740548221412</v>
       </c>
       <c r="R13">
-        <v>0.00056805737817451911</v>
+        <v>0.00063089198112702323</v>
       </c>
       <c r="S13">
-        <v>0.00035696248834257748</v>
+        <v>0.0004309180960626224</v>
       </c>
       <c r="T13">
-        <v>2.1820022286023807e-06</v>
+        <v>0.00016979418664173074</v>
       </c>
       <c r="U13">
-        <v>-0.00032145828896990025</v>
+        <v>-0.00015313543304103011</v>
       </c>
       <c r="V13">
-        <v>-3.6257538513338131e-05</v>
+        <v>-0.0003581395822996519</v>
       </c>
       <c r="W13">
-        <v>0.00029290227026215548</v>
+        <v>-5.6167694535051629e-05</v>
       </c>
       <c r="X13">
-        <v>0.00021311126627596936</v>
+        <v>0.00028967592560371014</v>
       </c>
       <c r="Y13">
-        <v>0.0015295178590606713</v>
+        <v>0.00028383393650210421</v>
       </c>
       <c r="Z13">
-        <v>0.00042056884597566459</v>
+        <v>0.0014164015979874316</v>
       </c>
       <c r="AA13">
-        <v>-0.00074013702914473879</v>
+        <v>0.0004236524433265164</v>
       </c>
       <c r="AB13">
-        <v>2.4285900913136223e-05</v>
+        <v>-0.00082985883371058337</v>
       </c>
       <c r="AC13">
-        <v>-0.0031388737448439976</v>
+        <v>2.809492346334829e-05</v>
       </c>
       <c r="AD13">
-        <v>-0.0028889668244260315</v>
+        <v>-0.0032160436069721549</v>
       </c>
       <c r="AE13">
-        <v>-0.0029990878132675714</v>
+        <v>-0.0029662849096437887</v>
       </c>
       <c r="AF13">
-        <v>-0.0026889008674822988</v>
+        <v>-0.0030931317431023672</v>
       </c>
       <c r="AG13">
-        <v>-0.0025676868395537837</v>
+        <v>-0.0026919974458402222</v>
       </c>
       <c r="AH13">
-        <v>-0.0024149540736188501</v>
+        <v>-0.0026112751116294107</v>
       </c>
       <c r="AI13">
-        <v>0.002806812868468702</v>
+        <v>-0.0024664750228936597</v>
+      </c>
+      <c r="AJ13">
+        <v>0.00059993195604187387</v>
       </c>
     </row>
     <row r="14">
@@ -1806,106 +1848,109 @@
         <v>36</v>
       </c>
       <c r="B14">
-        <v>-0.17083255963818656</v>
+        <v>-0.14259751298740955</v>
       </c>
       <c r="C14">
-        <v>-0.45248467586004876</v>
+        <v>-0.41699609051896836</v>
       </c>
       <c r="D14">
-        <v>0.00010528952368784802</v>
+        <v>0.00010327853045473748</v>
       </c>
       <c r="E14">
-        <v>-1.2251503745399576e-06</v>
+        <v>-1.1290501425161248e-06</v>
       </c>
       <c r="F14">
-        <v>-0.00078818304856614896</v>
+        <v>-0.00090412420021965256</v>
       </c>
       <c r="G14">
-        <v>-0.00047856715377456172</v>
+        <v>-0.00048266061529286808</v>
       </c>
       <c r="H14">
-        <v>-0.00086604277735241597</v>
+        <v>-0.000874177638921253</v>
       </c>
       <c r="I14">
-        <v>0.0005771642808234112</v>
+        <v>0.00061533691292992021</v>
       </c>
       <c r="J14">
-        <v>0.00013625228455299912</v>
+        <v>0.00016721877051585664</v>
       </c>
       <c r="K14">
-        <v>0.00010486296452688333</v>
+        <v>1.2557975438453272e-05</v>
       </c>
       <c r="L14">
-        <v>0.012232323890196826</v>
+        <v>0.010925551780011766</v>
       </c>
       <c r="M14">
-        <v>0.090293161016446535</v>
+        <v>0.084623594331150673</v>
       </c>
       <c r="N14">
-        <v>0.094411557125440693</v>
+        <v>0.087468024927459046</v>
       </c>
       <c r="O14">
-        <v>0.21180222105007734</v>
+        <v>0.20670950888052622</v>
       </c>
       <c r="P14">
-        <v>-0.0043562186576778517</v>
+        <v>-0.0045623256792363676</v>
       </c>
       <c r="Q14">
-        <v>-0.0013059776244100708</v>
+        <v>-0.0014310986859956227</v>
       </c>
       <c r="R14">
-        <v>-0.0013661564690591974</v>
+        <v>-0.0015205795057833492</v>
       </c>
       <c r="S14">
-        <v>-0.001469704443685811</v>
+        <v>-0.0016614669860702488</v>
       </c>
       <c r="T14">
-        <v>1.45053698995525e-05</v>
+        <v>-0.00010614781652158278</v>
       </c>
       <c r="U14">
-        <v>-9.1541199989701445e-05</v>
+        <v>-0.00018504432776530262</v>
       </c>
       <c r="V14">
-        <v>-9.1041326933832801e-05</v>
+        <v>1.8281861557667423e-06</v>
       </c>
       <c r="W14">
-        <v>-1.1656873372409087e-05</v>
+        <v>-0.00015270748867635738</v>
       </c>
       <c r="X14">
-        <v>-0.00055978453092549684</v>
+        <v>-1.5004678771510509e-05</v>
       </c>
       <c r="Y14">
-        <v>0.0002030203746463498</v>
+        <v>-0.00056476726495756965</v>
       </c>
       <c r="Z14">
-        <v>-7.5305778971812196e-05</v>
+        <v>0.00016533698653648356</v>
       </c>
       <c r="AA14">
-        <v>0.00096850812848046225</v>
+        <v>-0.00010190239538112656</v>
       </c>
       <c r="AB14">
-        <v>-3.9376425907337837e-05</v>
+        <v>0.0010368197386893077</v>
       </c>
       <c r="AC14">
-        <v>0.0029590099578440327</v>
+        <v>-4.1639116238285435e-05</v>
       </c>
       <c r="AD14">
-        <v>0.0029566608918253469</v>
+        <v>0.002879560547387707</v>
       </c>
       <c r="AE14">
-        <v>0.0030715942386580044</v>
+        <v>0.0028818244746878227</v>
       </c>
       <c r="AF14">
-        <v>0.0030454467097911979</v>
+        <v>0.0029994411987923036</v>
       </c>
       <c r="AG14">
-        <v>0.0033657017644494608</v>
+        <v>0.0030099481208004171</v>
       </c>
       <c r="AH14">
-        <v>0.0038604514672349322</v>
+        <v>0.0033101054896326402</v>
       </c>
       <c r="AI14">
-        <v>0.014040958222916164</v>
+        <v>0.0038467197948812825</v>
+      </c>
+      <c r="AJ14">
+        <v>0.014009909190098795</v>
       </c>
     </row>
     <row r="15">
@@ -1913,106 +1958,109 @@
         <v>37</v>
       </c>
       <c r="B15">
-        <v>-0.097753112696575564</v>
+        <v>-0.096489722387074789</v>
       </c>
       <c r="C15">
-        <v>0.012482120185884406</v>
+        <v>0.009134840529856178</v>
       </c>
       <c r="D15">
-        <v>-9.3205184014845529e-05</v>
+        <v>-8.0230439460864545e-05</v>
       </c>
       <c r="E15">
-        <v>1.2213958656446713e-06</v>
+        <v>1.0375098014718678e-06</v>
       </c>
       <c r="F15">
-        <v>-0.00080702049760759606</v>
+        <v>-0.0011370334412190777</v>
       </c>
       <c r="G15">
-        <v>-0.00033352061314261342</v>
+        <v>-0.00046196326867928988</v>
       </c>
       <c r="H15">
-        <v>-4.5917754549970602e-06</v>
+        <v>-0.00013551497840506854</v>
       </c>
       <c r="I15">
-        <v>2.400955892626136e-05</v>
+        <v>-6.7238298140141761e-05</v>
       </c>
       <c r="J15">
-        <v>-0.00020478891571190378</v>
+        <v>-0.00025645949140334901</v>
       </c>
       <c r="K15">
-        <v>0.00051816736153950985</v>
+        <v>0.00059879255969465424</v>
       </c>
       <c r="L15">
-        <v>-0.00043967793782724455</v>
+        <v>-0.00029330910579033987</v>
       </c>
       <c r="M15">
-        <v>-0.00026102498947001753</v>
+        <v>0.00010427264004039295</v>
       </c>
       <c r="N15">
-        <v>-0.0018734686406386872</v>
+        <v>-0.0015907037189158693</v>
       </c>
       <c r="O15">
-        <v>-0.0043562186576778517</v>
+        <v>-0.0045623256792363676</v>
       </c>
       <c r="P15">
-        <v>0.0093124994897508182</v>
+        <v>0.0095715622421395918</v>
       </c>
       <c r="Q15">
-        <v>0.0039868794960410316</v>
+        <v>0.0042179827040229392</v>
       </c>
       <c r="R15">
-        <v>0.004070603899566462</v>
+        <v>0.0042767080761080632</v>
       </c>
       <c r="S15">
-        <v>0.004172197890873963</v>
+        <v>0.0043785573649136956</v>
       </c>
       <c r="T15">
-        <v>1.7717544523059082e-05</v>
+        <v>0.00027163932199897149</v>
       </c>
       <c r="U15">
-        <v>0.0002279950416981211</v>
+        <v>-5.3730124025124252e-05</v>
       </c>
       <c r="V15">
-        <v>6.9907300788436984e-05</v>
+        <v>0.00019828021468279883</v>
       </c>
       <c r="W15">
-        <v>-0.00018483160940569886</v>
+        <v>4.4097899605850311e-05</v>
       </c>
       <c r="X15">
-        <v>0.00023788874191294339</v>
+        <v>-0.00017165198668459938</v>
       </c>
       <c r="Y15">
-        <v>-0.0013197311307299891</v>
+        <v>0.00027468526501003626</v>
       </c>
       <c r="Z15">
-        <v>0.00028589000806486867</v>
+        <v>-0.0012330503170501729</v>
       </c>
       <c r="AA15">
-        <v>-0.0002948472675332063</v>
+        <v>0.00029866345080838911</v>
       </c>
       <c r="AB15">
-        <v>1.2566200672554834e-05</v>
+        <v>-0.00033334425671132577</v>
       </c>
       <c r="AC15">
-        <v>-0.00042413028890383965</v>
+        <v>1.4322448704067536e-05</v>
       </c>
       <c r="AD15">
-        <v>-0.00026961053484948327</v>
+        <v>-0.00044987536369928095</v>
       </c>
       <c r="AE15">
-        <v>0.00011916511678051035</v>
+        <v>-0.00026898932976012358</v>
       </c>
       <c r="AF15">
-        <v>-0.00029816000897347865</v>
+        <v>0.00014406173637961735</v>
       </c>
       <c r="AG15">
-        <v>-0.00021161917505449338</v>
+        <v>-0.00028189896236239511</v>
       </c>
       <c r="AH15">
-        <v>-0.00038891201818296961</v>
+        <v>-0.00022195308815425895</v>
       </c>
       <c r="AI15">
-        <v>-0.010335785793734951</v>
+        <v>-0.00042738192690495026</v>
+      </c>
+      <c r="AJ15">
+        <v>-0.012054322743333104</v>
       </c>
     </row>
     <row r="16">
@@ -2020,106 +2068,109 @@
         <v>38</v>
       </c>
       <c r="B16">
-        <v>-0.074380214357748178</v>
+        <v>-0.078037203077631678</v>
       </c>
       <c r="C16">
-        <v>-0.011911167082071045</v>
+        <v>-0.012497257666346708</v>
       </c>
       <c r="D16">
-        <v>-0.00030290424234959037</v>
+        <v>-0.00030388784763747917</v>
       </c>
       <c r="E16">
-        <v>4.2853634019152227e-06</v>
+        <v>4.3844932218281975e-06</v>
       </c>
       <c r="F16">
-        <v>-0.00096483382860985956</v>
+        <v>-0.0013232822363664666</v>
       </c>
       <c r="G16">
-        <v>-0.00022244512247700937</v>
+        <v>-0.00030498902773365422</v>
       </c>
       <c r="H16">
-        <v>-0.00025683700062710535</v>
+        <v>-0.0002990901207749197</v>
       </c>
       <c r="I16">
-        <v>-0.00016388516025710176</v>
+        <v>-0.00016598741552827784</v>
       </c>
       <c r="J16">
-        <v>-0.00023398721957393646</v>
+        <v>-0.00024036252563609069</v>
       </c>
       <c r="K16">
-        <v>0.00083369776744187112</v>
+        <v>0.00084987130572135945</v>
       </c>
       <c r="L16">
-        <v>0.00048770695089095714</v>
+        <v>0.00050280877392754964</v>
       </c>
       <c r="M16">
-        <v>0.00081646922040840789</v>
+        <v>0.00087249091734782505</v>
       </c>
       <c r="N16">
-        <v>0.00011095190473632956</v>
+        <v>0.00017763740548221412</v>
       </c>
       <c r="O16">
-        <v>-0.0013059776244100708</v>
+        <v>-0.0014310986859956227</v>
       </c>
       <c r="P16">
-        <v>0.0039868794960410316</v>
+        <v>0.0042179827040229392</v>
       </c>
       <c r="Q16">
-        <v>0.006225463567535566</v>
+        <v>0.0066427545339064025</v>
       </c>
       <c r="R16">
-        <v>0.0051662515601290952</v>
+        <v>0.0054884559762355513</v>
       </c>
       <c r="S16">
-        <v>0.0053827370206308064</v>
+        <v>0.0056967766446109833</v>
       </c>
       <c r="T16">
-        <v>-4.8428316187823921e-05</v>
+        <v>-0.00018358907131377949</v>
       </c>
       <c r="U16">
-        <v>8.1070460528308557e-06</v>
+        <v>-0.00039805674930032772</v>
       </c>
       <c r="V16">
-        <v>0.00017978052309439705</v>
+        <v>0.00012506127557443988</v>
       </c>
       <c r="W16">
-        <v>9.0134234588109207e-06</v>
+        <v>0.00020451535826646186</v>
       </c>
       <c r="X16">
-        <v>0.00017202891810156324</v>
+        <v>-9.2782878564031036e-06</v>
       </c>
       <c r="Y16">
-        <v>0.0020020150381360371</v>
+        <v>0.00020875287162149911</v>
       </c>
       <c r="Z16">
-        <v>0.0012672959499446077</v>
+        <v>0.0020889980527941578</v>
       </c>
       <c r="AA16">
-        <v>-6.0846605364108051e-05</v>
+        <v>0.0013545005116211185</v>
       </c>
       <c r="AB16">
-        <v>4.5494006807156369e-06</v>
+        <v>-9.1039749237398476e-05</v>
       </c>
       <c r="AC16">
-        <v>-0.0007873479153950693</v>
+        <v>6.06305458166338e-06</v>
       </c>
       <c r="AD16">
-        <v>-0.00049846813573303046</v>
+        <v>-0.00095422260525676291</v>
       </c>
       <c r="AE16">
-        <v>-0.00052890627267357393</v>
+        <v>-0.00064572875638472778</v>
       </c>
       <c r="AF16">
-        <v>-0.00060330102428831191</v>
+        <v>-0.00065807909882752743</v>
       </c>
       <c r="AG16">
-        <v>-0.000391806544723773</v>
+        <v>-0.00073458664625755351</v>
       </c>
       <c r="AH16">
-        <v>-0.0007169162807663486</v>
+        <v>-0.00052804773378511049</v>
       </c>
       <c r="AI16">
-        <v>-0.0066607958970502489</v>
+        <v>-0.00090346517113689567</v>
+      </c>
+      <c r="AJ16">
+        <v>-0.0082232343440501853</v>
       </c>
     </row>
     <row r="17">
@@ -2127,106 +2178,109 @@
         <v>39</v>
       </c>
       <c r="B17">
-        <v>-0.16410573577474163</v>
+        <v>-0.17138816476305416</v>
       </c>
       <c r="C17">
-        <v>-0.015062334207493481</v>
+        <v>-0.016531622865446738</v>
       </c>
       <c r="D17">
-        <v>-0.00030588844955861357</v>
+        <v>-0.00030995834585633819</v>
       </c>
       <c r="E17">
-        <v>4.2131304416566235e-06</v>
+        <v>4.3193194425701289e-06</v>
       </c>
       <c r="F17">
-        <v>-0.00055598828177176422</v>
+        <v>-0.00095340245750266672</v>
       </c>
       <c r="G17">
-        <v>-0.000308577150588513</v>
+        <v>-0.00037504183842230338</v>
       </c>
       <c r="H17">
-        <v>-0.00024948015868723507</v>
+        <v>-0.00029724317080510702</v>
       </c>
       <c r="I17">
-        <v>-0.00022128813635778275</v>
+        <v>-0.00025988306405460779</v>
       </c>
       <c r="J17">
-        <v>9.239123820556247e-05</v>
+        <v>6.2522710901730368e-05</v>
       </c>
       <c r="K17">
-        <v>0.00083696292260326268</v>
+        <v>0.00091244289669354241</v>
       </c>
       <c r="L17">
-        <v>0.00060797376783038536</v>
+        <v>0.00066389538491095224</v>
       </c>
       <c r="M17">
-        <v>0.00082569221420482472</v>
+        <v>0.00092592678077957195</v>
       </c>
       <c r="N17">
-        <v>0.00056805737817451911</v>
+        <v>0.00063089198112702323</v>
       </c>
       <c r="O17">
-        <v>-0.0013661564690591974</v>
+        <v>-0.0015205795057833492</v>
       </c>
       <c r="P17">
-        <v>0.004070603899566462</v>
+        <v>0.0042767080761080632</v>
       </c>
       <c r="Q17">
-        <v>0.0051662515601290952</v>
+        <v>0.0054884559762355513</v>
       </c>
       <c r="R17">
-        <v>0.0063094127971984292</v>
+        <v>0.0066259169428012927</v>
       </c>
       <c r="S17">
-        <v>0.0058338596772272936</v>
+        <v>0.0061152854490815704</v>
       </c>
       <c r="T17">
-        <v>4.2300388717626824e-05</v>
+        <v>7.4298031779859329e-05</v>
       </c>
       <c r="U17">
-        <v>-2.5702197459364891e-05</v>
+        <v>-0.00017839259747063263</v>
       </c>
       <c r="V17">
-        <v>0.00027595956769282991</v>
+        <v>4.9928818852626324e-05</v>
       </c>
       <c r="W17">
-        <v>-6.9855781273491148e-05</v>
+        <v>0.00029139915720181344</v>
       </c>
       <c r="X17">
-        <v>0.00019322281495221536</v>
+        <v>-5.5637592460253786e-05</v>
       </c>
       <c r="Y17">
-        <v>0.0024311774690057636</v>
+        <v>0.00022468899698518369</v>
       </c>
       <c r="Z17">
-        <v>0.0015189687489016006</v>
+        <v>0.0024942953067278147</v>
       </c>
       <c r="AA17">
-        <v>-0.00024942500821564925</v>
+        <v>0.0015822343450867596</v>
       </c>
       <c r="AB17">
-        <v>1.0288745233226539e-05</v>
+        <v>-0.00030852253138595443</v>
       </c>
       <c r="AC17">
-        <v>-0.0010825205005590996</v>
+        <v>1.2459774472939184e-05</v>
       </c>
       <c r="AD17">
-        <v>-0.00084236937991497224</v>
+        <v>-0.0013242211544942004</v>
       </c>
       <c r="AE17">
-        <v>-0.00087550261182786659</v>
+        <v>-0.0010593619085024497</v>
       </c>
       <c r="AF17">
-        <v>-0.00075900176349736844</v>
+        <v>-0.0010565806993199794</v>
       </c>
       <c r="AG17">
-        <v>-0.00070737302321325323</v>
+        <v>-0.00094538972593384216</v>
       </c>
       <c r="AH17">
-        <v>-0.00086428267837278337</v>
+        <v>-0.00093948473387639757</v>
       </c>
       <c r="AI17">
-        <v>-0.0060576403963884546</v>
+        <v>-0.0010926162612756923</v>
+      </c>
+      <c r="AJ17">
+        <v>-0.0069895405356792942</v>
       </c>
     </row>
     <row r="18">
@@ -2234,106 +2288,109 @@
         <v>40</v>
       </c>
       <c r="B18">
-        <v>-0.0020643717861995726</v>
+        <v>0.0081702981228509337</v>
       </c>
       <c r="C18">
-        <v>-0.019174804078569224</v>
+        <v>-0.021052870742490106</v>
       </c>
       <c r="D18">
-        <v>-0.00039006962747682858</v>
+        <v>-0.00038970639162901912</v>
       </c>
       <c r="E18">
-        <v>5.2050590231725682e-06</v>
+        <v>5.2133472251351553e-06</v>
       </c>
       <c r="F18">
-        <v>-0.00056296117222746911</v>
+        <v>-0.00090716218822905342</v>
       </c>
       <c r="G18">
-        <v>-0.00034958377009881164</v>
+        <v>-0.00045033030282543019</v>
       </c>
       <c r="H18">
-        <v>-0.00028649373855649252</v>
+        <v>-0.00033049685513933391</v>
       </c>
       <c r="I18">
-        <v>-0.0002261463912025391</v>
+        <v>-0.00025563365540589092</v>
       </c>
       <c r="J18">
-        <v>-0.0001399048814895523</v>
+        <v>-0.0001319750251310505</v>
       </c>
       <c r="K18">
-        <v>0.0011922595443167273</v>
+        <v>0.0012465220329281651</v>
       </c>
       <c r="L18">
-        <v>0.00078436264105729518</v>
+        <v>0.00086106661336901613</v>
       </c>
       <c r="M18">
-        <v>0.0010245123342594415</v>
+        <v>0.0010688269352444844</v>
       </c>
       <c r="N18">
-        <v>0.00035696248834257748</v>
+        <v>0.0004309180960626224</v>
       </c>
       <c r="O18">
-        <v>-0.001469704443685811</v>
+        <v>-0.0016614669860702488</v>
       </c>
       <c r="P18">
-        <v>0.004172197890873963</v>
+        <v>0.0043785573649136956</v>
       </c>
       <c r="Q18">
-        <v>0.0053827370206308064</v>
+        <v>0.0056967766446109833</v>
       </c>
       <c r="R18">
-        <v>0.0058338596772272936</v>
+        <v>0.0061152854490815704</v>
       </c>
       <c r="S18">
-        <v>0.0071631590393610566</v>
+        <v>0.0074479468105875541</v>
       </c>
       <c r="T18">
-        <v>0.00015586461585498251</v>
+        <v>0.00033198545501881909</v>
       </c>
       <c r="U18">
-        <v>-2.456073161708367e-05</v>
+        <v>5.62391154889445e-05</v>
       </c>
       <c r="V18">
-        <v>0.00030368635488680197</v>
+        <v>-3.4646826263611913e-06</v>
       </c>
       <c r="W18">
-        <v>-0.00047385341626837989</v>
+        <v>0.00030307597494647857</v>
       </c>
       <c r="X18">
-        <v>0.00023269591664152887</v>
+        <v>-0.00045639232404741061</v>
       </c>
       <c r="Y18">
-        <v>0.0027268461161591515</v>
+        <v>0.00026102181448338894</v>
       </c>
       <c r="Z18">
-        <v>0.0017974066457881158</v>
+        <v>0.0027588843300405119</v>
       </c>
       <c r="AA18">
-        <v>-0.00017428270326453211</v>
+        <v>0.0018856896139226563</v>
       </c>
       <c r="AB18">
-        <v>9.1764553226018826e-06</v>
+        <v>-0.00022172316541170729</v>
       </c>
       <c r="AC18">
-        <v>-0.00093168661198174277</v>
+        <v>1.101674702892644e-05</v>
       </c>
       <c r="AD18">
-        <v>-0.00077782163662643445</v>
+        <v>-0.0011505919882662924</v>
       </c>
       <c r="AE18">
-        <v>-0.00085792086063237144</v>
+        <v>-0.00098074851741361286</v>
       </c>
       <c r="AF18">
-        <v>-0.00058126274490196859</v>
+        <v>-0.001045777108736315</v>
       </c>
       <c r="AG18">
-        <v>-0.00061193036376472202</v>
+        <v>-0.00074984388122480237</v>
       </c>
       <c r="AH18">
-        <v>-0.00067139522295163641</v>
+        <v>-0.00081647293075966839</v>
       </c>
       <c r="AI18">
-        <v>-0.0072893218727677657</v>
+        <v>-0.00090545178776167495</v>
+      </c>
+      <c r="AJ18">
+        <v>-0.008289191437113182</v>
       </c>
     </row>
     <row r="19">
@@ -2341,106 +2398,109 @@
         <v>41</v>
       </c>
       <c r="B19">
-        <v>-0.2114446296438196</v>
+        <v>0.11946047387921112</v>
       </c>
       <c r="C19">
-        <v>-0.0068540292196371238</v>
+        <v>-0.01403103509017159</v>
       </c>
       <c r="D19">
-        <v>-6.0547268984937177e-05</v>
+        <v>-3.3615211987328593e-05</v>
       </c>
       <c r="E19">
-        <v>3.9192315423521632e-07</v>
+        <v>-5.8623768479945204e-07</v>
       </c>
       <c r="F19">
-        <v>0.00019283274636152509</v>
+        <v>6.7708413812345159e-05</v>
       </c>
       <c r="G19">
-        <v>1.9760103432454185e-05</v>
+        <v>-0.00031849112729133433</v>
       </c>
       <c r="H19">
-        <v>-9.0255950355010856e-05</v>
+        <v>-0.00029751787683207631</v>
       </c>
       <c r="I19">
-        <v>-6.3366177249980782e-05</v>
+        <v>-0.00032930967045939619</v>
       </c>
       <c r="J19">
-        <v>5.311176028970565e-06</v>
+        <v>0.00027584060762993363</v>
       </c>
       <c r="K19">
-        <v>0.00031968392404982014</v>
+        <v>0.00044434752343775667</v>
       </c>
       <c r="L19">
-        <v>0.00029040440175441616</v>
+        <v>0.00063214033868301978</v>
       </c>
       <c r="M19">
-        <v>0.00017714193772328381</v>
+        <v>-9.3899970209110686e-05</v>
       </c>
       <c r="N19">
-        <v>2.1820022286023807e-06</v>
+        <v>0.00016979418664173074</v>
       </c>
       <c r="O19">
-        <v>1.45053698995525e-05</v>
+        <v>-0.00010614781652158278</v>
       </c>
       <c r="P19">
-        <v>1.7717544523059082e-05</v>
+        <v>0.00027163932199897149</v>
       </c>
       <c r="Q19">
-        <v>-4.8428316187823921e-05</v>
+        <v>-0.00018358907131377949</v>
       </c>
       <c r="R19">
-        <v>4.2300388717626824e-05</v>
+        <v>7.4298031779859329e-05</v>
       </c>
       <c r="S19">
-        <v>0.00015586461585498251</v>
+        <v>0.00033198545501881909</v>
       </c>
       <c r="T19">
-        <v>0.00063266500779511278</v>
+        <v>0.0022992157998673372</v>
       </c>
       <c r="U19">
-        <v>-0.00051022052624054043</v>
+        <v>0.0018358555178688897</v>
       </c>
       <c r="V19">
-        <v>-3.4999073375507393e-05</v>
+        <v>-0.00098742050538569827</v>
       </c>
       <c r="W19">
-        <v>3.9941321754973538e-05</v>
+        <v>-0.00024728611842767846</v>
       </c>
       <c r="X19">
-        <v>-4.8039857728959051e-05</v>
+        <v>0.00011175747351413279</v>
       </c>
       <c r="Y19">
-        <v>0.0003182153416565808</v>
+        <v>-1.4717583511966059e-05</v>
       </c>
       <c r="Z19">
-        <v>7.3920928790712008e-06</v>
+        <v>0.00013118896940101168</v>
       </c>
       <c r="AA19">
-        <v>9.2430186825136315e-07</v>
+        <v>3.743680288836106e-05</v>
       </c>
       <c r="AB19">
-        <v>-7.7592997908764342e-07</v>
+        <v>-7.6367605385134772e-05</v>
       </c>
       <c r="AC19">
-        <v>-7.8903725190907094e-05</v>
+        <v>2.2401081404480074e-06</v>
       </c>
       <c r="AD19">
-        <v>-1.0264725569824229e-05</v>
+        <v>0.00013967521508012981</v>
       </c>
       <c r="AE19">
-        <v>-3.5954064999674292e-05</v>
+        <v>0.00028049044791821147</v>
       </c>
       <c r="AF19">
-        <v>-0.00011167788887903607</v>
+        <v>0.00017423587731126499</v>
       </c>
       <c r="AG19">
-        <v>-7.3799463098876971e-05</v>
+        <v>0.00016484563742359454</v>
       </c>
       <c r="AH19">
-        <v>-0.0001718781608681397</v>
+        <v>0.00018156420170203176</v>
       </c>
       <c r="AI19">
-        <v>0.0033492145023693997</v>
+        <v>9.5029596718553206e-05</v>
+      </c>
+      <c r="AJ19">
+        <v>0.0019189591195111224</v>
       </c>
     </row>
     <row r="20">
@@ -2448,106 +2508,109 @@
         <v>42</v>
       </c>
       <c r="B20">
-        <v>-0.070631382374817239</v>
+        <v>-0.54566835878240749</v>
       </c>
       <c r="C20">
-        <v>0.0038910469223367161</v>
+        <v>-0.014861015372463846</v>
       </c>
       <c r="D20">
-        <v>-0.00019444007135821029</v>
+        <v>-0.00011066982474565619</v>
       </c>
       <c r="E20">
-        <v>3.3471710671157277e-06</v>
+        <v>4.7953007317183202e-07</v>
       </c>
       <c r="F20">
-        <v>-4.4131606317131256e-05</v>
+        <v>0.0005884381129871788</v>
       </c>
       <c r="G20">
-        <v>-6.5531235964380596e-06</v>
+        <v>8.3216341128927729e-05</v>
       </c>
       <c r="H20">
-        <v>-0.00014735224089427318</v>
+        <v>-0.00013730376260434607</v>
       </c>
       <c r="I20">
-        <v>-0.00021581421589400573</v>
+        <v>-0.00016425396908717471</v>
       </c>
       <c r="J20">
-        <v>0.00018387983840504436</v>
+        <v>7.7532943543886525e-05</v>
       </c>
       <c r="K20">
-        <v>5.2026151820094765e-05</v>
+        <v>0.0007299781743081771</v>
       </c>
       <c r="L20">
-        <v>-0.00015136464462205124</v>
+        <v>0.00064658426680226384</v>
       </c>
       <c r="M20">
-        <v>-0.00035532925225286761</v>
+        <v>0.00021857877783650536</v>
       </c>
       <c r="N20">
-        <v>-0.00032145828896990025</v>
+        <v>-0.00015313543304103011</v>
       </c>
       <c r="O20">
-        <v>-9.1541199989701445e-05</v>
+        <v>-0.00018504432776530262</v>
       </c>
       <c r="P20">
-        <v>0.0002279950416981211</v>
+        <v>-5.3730124025124252e-05</v>
       </c>
       <c r="Q20">
-        <v>8.1070460528308557e-06</v>
+        <v>-0.00039805674930032772</v>
       </c>
       <c r="R20">
-        <v>-2.5702197459364891e-05</v>
+        <v>-0.00017839259747063263</v>
       </c>
       <c r="S20">
-        <v>-2.456073161708367e-05</v>
+        <v>5.62391154889445e-05</v>
       </c>
       <c r="T20">
-        <v>-0.00051022052624054043</v>
+        <v>0.0018358555178688897</v>
       </c>
       <c r="U20">
-        <v>0.0018064438621660074</v>
+        <v>0.0036844816496023522</v>
       </c>
       <c r="V20">
-        <v>0.00013067167557890847</v>
+        <v>-0.0012724305075856907</v>
       </c>
       <c r="W20">
-        <v>-1.2440082773223249e-05</v>
+        <v>-0.00010225588289816516</v>
       </c>
       <c r="X20">
-        <v>8.1435472208752117e-05</v>
+        <v>0.00018766665826012115</v>
       </c>
       <c r="Y20">
-        <v>-0.00036163553719518728</v>
+        <v>-0.00014500547791669079</v>
       </c>
       <c r="Z20">
-        <v>-0.00019137875722285654</v>
+        <v>0.00055842911266481242</v>
       </c>
       <c r="AA20">
-        <v>-0.00012226737999189669</v>
+        <v>6.1583968604455062e-05</v>
       </c>
       <c r="AB20">
-        <v>5.0793106254111995e-06</v>
+        <v>-3.9207991982039133e-05</v>
       </c>
       <c r="AC20">
-        <v>9.1711530249414001e-05</v>
+        <v>-1.5254212943521584e-06</v>
       </c>
       <c r="AD20">
-        <v>2.4608333511752902e-05</v>
+        <v>-0.00035916420322860401</v>
       </c>
       <c r="AE20">
-        <v>9.8761412541536575e-05</v>
+        <v>-0.00017647299743263735</v>
       </c>
       <c r="AF20">
-        <v>5.9025370231384922e-05</v>
+        <v>-0.00024732176697266772</v>
       </c>
       <c r="AG20">
-        <v>-1.8693498563849566e-05</v>
+        <v>-0.00039414874908908697</v>
       </c>
       <c r="AH20">
-        <v>0.00012872899156129742</v>
+        <v>-0.00033894208402273946</v>
       </c>
       <c r="AI20">
-        <v>5.7900964421969177e-05</v>
+        <v>-0.00049835162210639164</v>
+      </c>
+      <c r="AJ20">
+        <v>0.0093144568836014425</v>
       </c>
     </row>
     <row r="21">
@@ -2555,106 +2618,109 @@
         <v>43</v>
       </c>
       <c r="B21">
-        <v>0.06443357081193217</v>
+        <v>-0.15215207939100622</v>
       </c>
       <c r="C21">
-        <v>0.0010978054264662307</v>
+        <v>0.0051318929565080541</v>
       </c>
       <c r="D21">
-        <v>-3.6469958510562065e-05</v>
+        <v>-0.00023393056887593858</v>
       </c>
       <c r="E21">
-        <v>7.9392659110029943e-07</v>
+        <v>4.1757462749229513e-06</v>
       </c>
       <c r="F21">
-        <v>-0.00056880340337257113</v>
+        <v>6.8978488783139752e-05</v>
       </c>
       <c r="G21">
-        <v>-6.7591148885701169e-05</v>
+        <v>0.00012280573773625764</v>
       </c>
       <c r="H21">
-        <v>0.00011914232424628524</v>
+        <v>-0.00016360283807634671</v>
       </c>
       <c r="I21">
-        <v>0.00022908159705351677</v>
+        <v>-0.0001847887030670646</v>
       </c>
       <c r="J21">
-        <v>0.0004354975253703261</v>
+        <v>0.00015610081180726291</v>
       </c>
       <c r="K21">
-        <v>-3.18799757991028e-05</v>
+        <v>8.4228112378104903e-05</v>
       </c>
       <c r="L21">
-        <v>3.3006796986939473e-06</v>
+        <v>-0.00021087268036293675</v>
       </c>
       <c r="M21">
-        <v>-0.00041984523326343186</v>
+        <v>-0.00026539830497367828</v>
       </c>
       <c r="N21">
-        <v>-3.6257538513338131e-05</v>
+        <v>-0.0003581395822996519</v>
       </c>
       <c r="O21">
-        <v>-9.1041326933832801e-05</v>
+        <v>1.8281861557667423e-06</v>
       </c>
       <c r="P21">
-        <v>6.9907300788436984e-05</v>
+        <v>0.00019828021468279883</v>
       </c>
       <c r="Q21">
-        <v>0.00017978052309439705</v>
+        <v>0.00012506127557443988</v>
       </c>
       <c r="R21">
-        <v>0.00027595956769282991</v>
+        <v>4.9928818852626324e-05</v>
       </c>
       <c r="S21">
-        <v>0.00030368635488680197</v>
+        <v>-3.4646826263611913e-06</v>
       </c>
       <c r="T21">
-        <v>-3.4999073375507393e-05</v>
+        <v>-0.00098742050538569827</v>
       </c>
       <c r="U21">
-        <v>0.00013067167557890847</v>
+        <v>-0.0012724305075856907</v>
       </c>
       <c r="V21">
-        <v>0.0024808533844777872</v>
+        <v>0.0023550052516793114</v>
       </c>
       <c r="W21">
-        <v>0.0011764936305419563</v>
+        <v>0.00024174397356403472</v>
       </c>
       <c r="X21">
-        <v>-3.2146153439627473e-05</v>
+        <v>-4.6486864235604449e-05</v>
       </c>
       <c r="Y21">
-        <v>0.00037101644777601202</v>
+        <v>6.8050259825497273e-05</v>
       </c>
       <c r="Z21">
-        <v>-4.4882108429737081e-05</v>
+        <v>-0.00026222122066257988</v>
       </c>
       <c r="AA21">
-        <v>5.6183570867147405e-05</v>
+        <v>-0.00025066735290521513</v>
       </c>
       <c r="AB21">
-        <v>-1.7865352875426029e-06</v>
+        <v>-6.9794394013300044e-05</v>
       </c>
       <c r="AC21">
-        <v>0.00047686308164666068</v>
+        <v>3.3969857149139277e-06</v>
       </c>
       <c r="AD21">
-        <v>0.00037349392819110722</v>
+        <v>-2.1366953860633368e-05</v>
       </c>
       <c r="AE21">
-        <v>0.00040157710779500742</v>
+        <v>-0.00012252613807813982</v>
       </c>
       <c r="AF21">
-        <v>0.00017070913422620026</v>
+        <v>2.2211581000094126e-05</v>
       </c>
       <c r="AG21">
-        <v>0.00042331984530001208</v>
+        <v>-0.00010151274912743109</v>
       </c>
       <c r="AH21">
-        <v>0.00018568745674472096</v>
+        <v>-0.00013961506885963474</v>
       </c>
       <c r="AI21">
-        <v>-0.00083298470338044692</v>
+        <v>-1.9030236020144793e-05</v>
+      </c>
+      <c r="AJ21">
+        <v>0.00074799310333424022</v>
       </c>
     </row>
     <row r="22">
@@ -2662,106 +2728,109 @@
         <v>44</v>
       </c>
       <c r="B22">
-        <v>0.043798468480096109</v>
+        <v>0.067103961185812258</v>
       </c>
       <c r="C22">
-        <v>-0.00025410340911616487</v>
+        <v>0.0019271813196352072</v>
       </c>
       <c r="D22">
-        <v>-0.00015624355756860579</v>
+        <v>-4.0250667569825295e-05</v>
       </c>
       <c r="E22">
-        <v>2.2385276561586834e-06</v>
+        <v>9.0305587337487751e-07</v>
       </c>
       <c r="F22">
-        <v>-0.00034499406447835099</v>
+        <v>-0.00043960912064326674</v>
       </c>
       <c r="G22">
-        <v>-0.00018649824329965495</v>
+        <v>-1.9161969688527569e-05</v>
       </c>
       <c r="H22">
-        <v>-4.5488267761299023e-05</v>
+        <v>0.00013719780070220455</v>
       </c>
       <c r="I22">
-        <v>-0.00017955549617110211</v>
+        <v>0.00025257432929338963</v>
       </c>
       <c r="J22">
-        <v>3.4900043021665313e-05</v>
+        <v>0.00040864141282163187</v>
       </c>
       <c r="K22">
-        <v>-0.00027995311683873936</v>
+        <v>-7.4718561288690018e-05</v>
       </c>
       <c r="L22">
-        <v>5.6735932334623274e-05</v>
+        <v>-3.4955021206470316e-05</v>
       </c>
       <c r="M22">
-        <v>2.2198636438916942e-05</v>
+        <v>-0.00039125422590610692</v>
       </c>
       <c r="N22">
-        <v>0.00029290227026215548</v>
+        <v>-5.6167694535051629e-05</v>
       </c>
       <c r="O22">
-        <v>-1.1656873372409087e-05</v>
+        <v>-0.00015270748867635738</v>
       </c>
       <c r="P22">
-        <v>-0.00018483160940569886</v>
+        <v>4.4097899605850311e-05</v>
       </c>
       <c r="Q22">
-        <v>9.0134234588109207e-06</v>
+        <v>0.00020451535826646186</v>
       </c>
       <c r="R22">
-        <v>-6.9855781273491148e-05</v>
+        <v>0.00029139915720181344</v>
       </c>
       <c r="S22">
-        <v>-0.00047385341626837989</v>
+        <v>0.00030307597494647857</v>
       </c>
       <c r="T22">
-        <v>3.9941321754973538e-05</v>
+        <v>-0.00024728611842767846</v>
       </c>
       <c r="U22">
-        <v>-1.2440082773223249e-05</v>
+        <v>-0.00010225588289816516</v>
       </c>
       <c r="V22">
-        <v>0.0011764936305419563</v>
+        <v>0.00024174397356403472</v>
       </c>
       <c r="W22">
-        <v>0.0019305607124381131</v>
+        <v>0.002554766016668166</v>
       </c>
       <c r="X22">
-        <v>-2.9061194102584237e-06</v>
+        <v>0.0011854608161121075</v>
       </c>
       <c r="Y22">
-        <v>-6.0229127312111844e-05</v>
+        <v>-5.2370140322880853e-05</v>
       </c>
       <c r="Z22">
-        <v>0.00012372250538632501</v>
+        <v>0.00037810548105388672</v>
       </c>
       <c r="AA22">
-        <v>-0.00015947517016320082</v>
+        <v>-5.7858137315815661e-05</v>
       </c>
       <c r="AB22">
-        <v>4.1972335415238635e-06</v>
+        <v>7.0679743701248729e-05</v>
       </c>
       <c r="AC22">
-        <v>0.00011137459986377499</v>
+        <v>-2.5561372439502885e-06</v>
       </c>
       <c r="AD22">
-        <v>7.1193961384888251e-05</v>
+        <v>0.00048877945911205106</v>
       </c>
       <c r="AE22">
-        <v>3.697363353992446e-05</v>
+        <v>0.0003841513413991712</v>
       </c>
       <c r="AF22">
-        <v>4.2166999705862149e-05</v>
+        <v>0.00041072200204037641</v>
       </c>
       <c r="AG22">
-        <v>7.0035679735096039e-05</v>
+        <v>0.00017868472712351561</v>
       </c>
       <c r="AH22">
-        <v>3.7842730000199607e-05</v>
+        <v>0.00044821161996494967</v>
       </c>
       <c r="AI22">
-        <v>0.0030784277533595075</v>
+        <v>0.00021368823292435804</v>
+      </c>
+      <c r="AJ22">
+        <v>-4.0767698066891114e-05</v>
       </c>
     </row>
     <row r="23">
@@ -2769,106 +2838,109 @@
         <v>45</v>
       </c>
       <c r="B23">
-        <v>-0.012600017524180999</v>
+        <v>0.05943889776774814</v>
       </c>
       <c r="C23">
-        <v>0.0022790960136856511</v>
+        <v>-0.00056765398063500158</v>
       </c>
       <c r="D23">
-        <v>6.3939760231571975e-06</v>
+        <v>-0.00015939846490364926</v>
       </c>
       <c r="E23">
-        <v>-5.0764350912784796e-08</v>
+        <v>2.2494239875276752e-06</v>
       </c>
       <c r="F23">
-        <v>-6.1679006406176184e-05</v>
+        <v>-0.00019561891786943827</v>
       </c>
       <c r="G23">
-        <v>4.6842525336376895e-05</v>
+        <v>-0.00015887896411250629</v>
       </c>
       <c r="H23">
-        <v>2.850674282510457e-05</v>
+        <v>-1.7749614095067395e-05</v>
       </c>
       <c r="I23">
-        <v>-2.3004726905070938e-05</v>
+        <v>-0.00015263677111317792</v>
       </c>
       <c r="J23">
-        <v>0.00018738626967574907</v>
+        <v>5.8354328227125781e-05</v>
       </c>
       <c r="K23">
-        <v>4.2639279417184834e-07</v>
+        <v>-0.00026887173349688135</v>
       </c>
       <c r="L23">
-        <v>-8.518967574418332e-05</v>
+        <v>7.4104563116129593e-05</v>
       </c>
       <c r="M23">
-        <v>-0.00070603229604999668</v>
+        <v>2.2294010395177517e-06</v>
       </c>
       <c r="N23">
-        <v>0.00021311126627596936</v>
+        <v>0.00028967592560371014</v>
       </c>
       <c r="O23">
-        <v>-0.00055978453092549684</v>
+        <v>-1.5004678771510509e-05</v>
       </c>
       <c r="P23">
-        <v>0.00023788874191294339</v>
+        <v>-0.00017165198668459938</v>
       </c>
       <c r="Q23">
-        <v>0.00017202891810156324</v>
+        <v>-9.2782878564031036e-06</v>
       </c>
       <c r="R23">
-        <v>0.00019322281495221536</v>
+        <v>-5.5637592460253786e-05</v>
       </c>
       <c r="S23">
-        <v>0.00023269591664152887</v>
+        <v>-0.00045639232404741061</v>
       </c>
       <c r="T23">
-        <v>-4.8039857728959051e-05</v>
+        <v>0.00011175747351413279</v>
       </c>
       <c r="U23">
-        <v>8.1435472208752117e-05</v>
+        <v>0.00018766665826012115</v>
       </c>
       <c r="V23">
-        <v>-3.2146153439627473e-05</v>
+        <v>-4.6486864235604449e-05</v>
       </c>
       <c r="W23">
-        <v>-2.9061194102584237e-06</v>
+        <v>0.0011854608161121075</v>
       </c>
       <c r="X23">
-        <v>0.00055999754122716162</v>
+        <v>0.0019675046712672958</v>
       </c>
       <c r="Y23">
-        <v>-0.00011896751255536836</v>
+        <v>-5.0032931173935835e-06</v>
       </c>
       <c r="Z23">
-        <v>1.0705523611634696e-05</v>
+        <v>-9.7543537993650779e-05</v>
       </c>
       <c r="AA23">
-        <v>-0.00065652666034463764</v>
+        <v>0.0001193353314392587</v>
       </c>
       <c r="AB23">
-        <v>2.789334889637319e-05</v>
+        <v>-0.0001686305716581142</v>
       </c>
       <c r="AC23">
-        <v>3.5985073037304166e-05</v>
+        <v>4.4284720053924211e-06</v>
       </c>
       <c r="AD23">
-        <v>4.7169146713054583e-05</v>
+        <v>0.00015989314681997912</v>
       </c>
       <c r="AE23">
-        <v>5.0652765044222406e-05</v>
+        <v>0.00010592887561970476</v>
       </c>
       <c r="AF23">
-        <v>0.00018495111207299415</v>
+        <v>5.2209263367333951e-05</v>
       </c>
       <c r="AG23">
-        <v>4.7762933084663593e-05</v>
+        <v>8.2708495274138618e-05</v>
       </c>
       <c r="AH23">
-        <v>6.1725593539739814e-05</v>
+        <v>0.00011480472909783975</v>
       </c>
       <c r="AI23">
-        <v>-0.019785567956063371</v>
+        <v>9.9565044679886269e-05</v>
+      </c>
+      <c r="AJ23">
+        <v>0.0032033069023695939</v>
       </c>
     </row>
     <row r="24">
@@ -2876,106 +2948,109 @@
         <v>46</v>
       </c>
       <c r="B24">
-        <v>-0.42708497112317062</v>
+        <v>-0.014271334411095458</v>
       </c>
       <c r="C24">
-        <v>-0.039403594306083645</v>
+        <v>0.0016190650379425339</v>
       </c>
       <c r="D24">
-        <v>-0.00052942195573361646</v>
+        <v>2.7557411350635948e-06</v>
       </c>
       <c r="E24">
-        <v>7.5598983291268453e-06</v>
+        <v>-4.0966235322160223e-09</v>
       </c>
       <c r="F24">
-        <v>-0.00059552817936721694</v>
+        <v>-8.9249421394238526e-05</v>
       </c>
       <c r="G24">
-        <v>-6.578249448698989e-05</v>
+        <v>3.0230494891259063e-06</v>
       </c>
       <c r="H24">
-        <v>-9.4500699416515122e-05</v>
+        <v>-1.2587281779413706e-05</v>
       </c>
       <c r="I24">
-        <v>-0.000254042385207702</v>
+        <v>-5.8344592110820548e-05</v>
       </c>
       <c r="J24">
-        <v>-0.00043014663693432057</v>
+        <v>0.00020320250088897319</v>
       </c>
       <c r="K24">
-        <v>0.00022887317678900478</v>
+        <v>-5.2089042598708478e-06</v>
       </c>
       <c r="L24">
-        <v>0.0009364478418040249</v>
+        <v>-5.8032315052613083e-05</v>
       </c>
       <c r="M24">
-        <v>0.0016025197754252654</v>
+        <v>-0.00068362442644818999</v>
       </c>
       <c r="N24">
-        <v>0.0015295178590606713</v>
+        <v>0.00028383393650210421</v>
       </c>
       <c r="O24">
-        <v>0.0002030203746463498</v>
+        <v>-0.00056476726495756965</v>
       </c>
       <c r="P24">
-        <v>-0.0013197311307299891</v>
+        <v>0.00027468526501003626</v>
       </c>
       <c r="Q24">
-        <v>0.0020020150381360371</v>
+        <v>0.00020875287162149911</v>
       </c>
       <c r="R24">
-        <v>0.0024311774690057636</v>
+        <v>0.00022468899698518369</v>
       </c>
       <c r="S24">
-        <v>0.0027268461161591515</v>
+        <v>0.00026102181448338894</v>
       </c>
       <c r="T24">
-        <v>0.0003182153416565808</v>
+        <v>-1.4717583511966059e-05</v>
       </c>
       <c r="U24">
-        <v>-0.00036163553719518728</v>
+        <v>-0.00014500547791669079</v>
       </c>
       <c r="V24">
-        <v>0.00037101644777601202</v>
+        <v>6.8050259825497273e-05</v>
       </c>
       <c r="W24">
-        <v>-6.0229127312111844e-05</v>
+        <v>-5.2370140322880853e-05</v>
       </c>
       <c r="X24">
-        <v>-0.00011896751255536836</v>
+        <v>-5.0032931173935835e-06</v>
       </c>
       <c r="Y24">
-        <v>0.018890533745811636</v>
+        <v>0.00057957306801175021</v>
       </c>
       <c r="Z24">
-        <v>0.0012046096766609236</v>
+        <v>-0.00011877598157234337</v>
       </c>
       <c r="AA24">
-        <v>-5.3496012578398491e-05</v>
+        <v>1.5670499507701441e-06</v>
       </c>
       <c r="AB24">
-        <v>-7.5460363116073518e-07</v>
+        <v>-0.00067782728624898869</v>
       </c>
       <c r="AC24">
-        <v>-0.00041087233826457743</v>
+        <v>2.8824255623340523e-05</v>
       </c>
       <c r="AD24">
-        <v>-0.00038357456557543482</v>
+        <v>1.304982083655086e-05</v>
       </c>
       <c r="AE24">
-        <v>-0.00099606404171733061</v>
+        <v>3.3948965047882543e-05</v>
       </c>
       <c r="AF24">
-        <v>-0.00057831513560633978</v>
+        <v>3.8346599379767039e-05</v>
       </c>
       <c r="AG24">
-        <v>-0.00088142540502298469</v>
+        <v>0.00018547195669557821</v>
       </c>
       <c r="AH24">
-        <v>-0.00098315835379058757</v>
+        <v>3.1197360787280429e-05</v>
       </c>
       <c r="AI24">
-        <v>0.012859675143308099</v>
+        <v>3.7368271585214684e-05</v>
+      </c>
+      <c r="AJ24">
+        <v>-0.020381158835424879</v>
       </c>
     </row>
     <row r="25">
@@ -2983,106 +3058,109 @@
         <v>47</v>
       </c>
       <c r="B25">
-        <v>0.042696169594707296</v>
+        <v>-0.40423068636914239</v>
       </c>
       <c r="C25">
-        <v>-0.0063408707682034299</v>
+        <v>-0.036502196669909948</v>
       </c>
       <c r="D25">
-        <v>-6.2911593248133908e-05</v>
+        <v>-0.00044795679051351251</v>
       </c>
       <c r="E25">
-        <v>9.5968162963645088e-07</v>
+        <v>6.4749595984658732e-06</v>
       </c>
       <c r="F25">
-        <v>0.00035352782538422556</v>
+        <v>-0.00078604493774756673</v>
       </c>
       <c r="G25">
-        <v>0.00010995260095963966</v>
+        <v>-3.9762688375737099e-05</v>
       </c>
       <c r="H25">
-        <v>0.0002903765424918936</v>
+        <v>-2.5785282258307396e-05</v>
       </c>
       <c r="I25">
-        <v>0.00028627843108514073</v>
+        <v>-0.00016863984768275553</v>
       </c>
       <c r="J25">
-        <v>-4.8485918077898231e-05</v>
+        <v>-0.00042162893040731755</v>
       </c>
       <c r="K25">
-        <v>0.00023670175134485455</v>
+        <v>0.00015690793646992561</v>
       </c>
       <c r="L25">
-        <v>0.00026691023006594674</v>
+        <v>0.00081496363643340482</v>
       </c>
       <c r="M25">
-        <v>0.00043602477581287198</v>
+        <v>0.0014404235926219118</v>
       </c>
       <c r="N25">
-        <v>0.00042056884597566459</v>
+        <v>0.0014164015979874316</v>
       </c>
       <c r="O25">
-        <v>-7.5305778971812196e-05</v>
+        <v>0.00016533698653648356</v>
       </c>
       <c r="P25">
-        <v>0.00028589000806486867</v>
+        <v>-0.0012330503170501729</v>
       </c>
       <c r="Q25">
-        <v>0.0012672959499446077</v>
+        <v>0.0020889980527941578</v>
       </c>
       <c r="R25">
-        <v>0.0015189687489016006</v>
+        <v>0.0024942953067278147</v>
       </c>
       <c r="S25">
-        <v>0.0017974066457881158</v>
+        <v>0.0027588843300405119</v>
       </c>
       <c r="T25">
-        <v>7.3920928790712008e-06</v>
+        <v>0.00013118896940101168</v>
       </c>
       <c r="U25">
-        <v>-0.00019137875722285654</v>
+        <v>0.00055842911266481242</v>
       </c>
       <c r="V25">
-        <v>-4.4882108429737081e-05</v>
+        <v>-0.00026222122066257988</v>
       </c>
       <c r="W25">
-        <v>0.00012372250538632501</v>
+        <v>0.00037810548105388672</v>
       </c>
       <c r="X25">
-        <v>1.0705523611634696e-05</v>
+        <v>-9.7543537993650779e-05</v>
       </c>
       <c r="Y25">
-        <v>0.0012046096766609236</v>
+        <v>-0.00011877598157234337</v>
       </c>
       <c r="Z25">
-        <v>0.0019990452809815181</v>
+        <v>0.018713706618188081</v>
       </c>
       <c r="AA25">
-        <v>-4.3505980810550505e-05</v>
+        <v>0.0012587668854051304</v>
       </c>
       <c r="AB25">
-        <v>1.8466356831338263e-06</v>
+        <v>-5.5047243570886459e-05</v>
       </c>
       <c r="AC25">
-        <v>-0.00045768293996529012</v>
+        <v>-7.2401136930286703e-07</v>
       </c>
       <c r="AD25">
-        <v>-0.00040503652639068593</v>
+        <v>-0.00051506165346824201</v>
       </c>
       <c r="AE25">
-        <v>-0.00043714554398675408</v>
+        <v>-0.00049993377405562443</v>
       </c>
       <c r="AF25">
-        <v>-0.0003680345232809413</v>
+        <v>-0.0010938002976127363</v>
       </c>
       <c r="AG25">
-        <v>-0.00027877858672470618</v>
+        <v>-0.00069309200635041778</v>
       </c>
       <c r="AH25">
-        <v>-0.00045863147275237884</v>
+        <v>-0.00099157759065768639</v>
       </c>
       <c r="AI25">
-        <v>-0.0011966209011909999</v>
+        <v>-0.0010985823354876028</v>
+      </c>
+      <c r="AJ25">
+        <v>0.011457681291717007</v>
       </c>
     </row>
     <row r="26">
@@ -3090,106 +3168,109 @@
         <v>48</v>
       </c>
       <c r="B26">
-        <v>0.071159919382595041</v>
+        <v>0.048616924519544857</v>
       </c>
       <c r="C26">
-        <v>-0.00034062264106876627</v>
+        <v>-0.0067386622581028372</v>
       </c>
       <c r="D26">
-        <v>4.6010239909438644e-05</v>
+        <v>-4.4919305012504005e-05</v>
       </c>
       <c r="E26">
-        <v>-6.2298458975221238e-07</v>
+        <v>6.7845143132435861e-07</v>
       </c>
       <c r="F26">
-        <v>-0.00019073705750968784</v>
+        <v>0.0002541317112012137</v>
       </c>
       <c r="G26">
-        <v>-0.0001160488282910821</v>
+        <v>8.5140332353350612e-05</v>
       </c>
       <c r="H26">
-        <v>-0.00013474179715905477</v>
+        <v>0.00032559139890397937</v>
       </c>
       <c r="I26">
-        <v>1.38021883758499e-05</v>
+        <v>0.000337733709171395</v>
       </c>
       <c r="J26">
-        <v>-0.00040578728455636102</v>
+        <v>-5.1104846317391985e-05</v>
       </c>
       <c r="K26">
-        <v>0.00020889845789145924</v>
+        <v>0.00025335319509769689</v>
       </c>
       <c r="L26">
-        <v>3.9509382272978969e-06</v>
+        <v>0.00028145696276422947</v>
       </c>
       <c r="M26">
-        <v>0.0005563956985397446</v>
+        <v>0.00043404234164555553</v>
       </c>
       <c r="N26">
-        <v>-0.00074013702914473879</v>
+        <v>0.0004236524433265164</v>
       </c>
       <c r="O26">
-        <v>0.00096850812848046225</v>
+        <v>-0.00010190239538112656</v>
       </c>
       <c r="P26">
-        <v>-0.0002948472675332063</v>
+        <v>0.00029866345080838911</v>
       </c>
       <c r="Q26">
-        <v>-6.0846605364108051e-05</v>
+        <v>0.0013545005116211185</v>
       </c>
       <c r="R26">
-        <v>-0.00024942500821564925</v>
+        <v>0.0015822343450867596</v>
       </c>
       <c r="S26">
-        <v>-0.00017428270326453211</v>
+        <v>0.0018856896139226563</v>
       </c>
       <c r="T26">
-        <v>9.2430186825136315e-07</v>
+        <v>3.743680288836106e-05</v>
       </c>
       <c r="U26">
-        <v>-0.00012226737999189669</v>
+        <v>6.1583968604455062e-05</v>
       </c>
       <c r="V26">
-        <v>5.6183570867147405e-05</v>
+        <v>-0.00025066735290521513</v>
       </c>
       <c r="W26">
-        <v>-0.00015947517016320082</v>
+        <v>-5.7858137315815661e-05</v>
       </c>
       <c r="X26">
-        <v>-0.00065652666034463764</v>
+        <v>0.0001193353314392587</v>
       </c>
       <c r="Y26">
-        <v>-5.3496012578398491e-05</v>
+        <v>1.5670499507701441e-06</v>
       </c>
       <c r="Z26">
-        <v>-4.3505980810550505e-05</v>
+        <v>0.0012587668854051304</v>
       </c>
       <c r="AA26">
-        <v>0.002176809857307773</v>
+        <v>0.0020695832731355114</v>
       </c>
       <c r="AB26">
-        <v>-7.2257821613665649e-05</v>
+        <v>-3.1910120652461557e-05</v>
       </c>
       <c r="AC26">
-        <v>8.9628372583182639e-05</v>
+        <v>1.4156553197245368e-06</v>
       </c>
       <c r="AD26">
-        <v>7.2220706308261454e-05</v>
+        <v>-0.00056890703141835664</v>
       </c>
       <c r="AE26">
-        <v>8.0023146107070916e-05</v>
+        <v>-0.00051280710073887828</v>
       </c>
       <c r="AF26">
-        <v>-0.00012200891346675607</v>
+        <v>-0.00053940517113822432</v>
       </c>
       <c r="AG26">
-        <v>0.00020671392982635596</v>
+        <v>-0.00047135732603801423</v>
       </c>
       <c r="AH26">
-        <v>0.00013464482304841778</v>
+        <v>-0.00039505552640802986</v>
       </c>
       <c r="AI26">
-        <v>0.010414752190208749</v>
+        <v>-0.00058835849405848963</v>
+      </c>
+      <c r="AJ26">
+        <v>-0.0012038743058375313</v>
       </c>
     </row>
     <row r="27">
@@ -3197,106 +3278,109 @@
         <v>49</v>
       </c>
       <c r="B27">
-        <v>-0.0024210025108538339</v>
+        <v>0.069288069196599814</v>
       </c>
       <c r="C27">
-        <v>5.2232044968119652e-05</v>
+        <v>0.00061525010395119262</v>
       </c>
       <c r="D27">
-        <v>-1.1521360416434775e-06</v>
+        <v>5.0034921853884043e-05</v>
       </c>
       <c r="E27">
-        <v>1.6337636712074235e-08</v>
+        <v>-6.4226139312095949e-07</v>
       </c>
       <c r="F27">
-        <v>3.7792907982159979e-06</v>
+        <v>-6.2917903985659773e-05</v>
       </c>
       <c r="G27">
-        <v>3.6596137237276949e-06</v>
+        <v>-4.8323662136001699e-05</v>
       </c>
       <c r="H27">
-        <v>4.2256210295629065e-06</v>
+        <v>-8.9351585151747903e-05</v>
       </c>
       <c r="I27">
-        <v>-5.7753898192840214e-07</v>
+        <v>7.1281580288184987e-05</v>
       </c>
       <c r="J27">
-        <v>1.4950737462750193e-05</v>
+        <v>-0.00044264654520438434</v>
       </c>
       <c r="K27">
-        <v>-5.842763345124245e-06</v>
+        <v>0.00021272869895610613</v>
       </c>
       <c r="L27">
-        <v>-1.657848064615374e-06</v>
+        <v>-3.8646629756339777e-05</v>
       </c>
       <c r="M27">
-        <v>-2.8122226782190736e-05</v>
+        <v>0.00055623889438208632</v>
       </c>
       <c r="N27">
-        <v>2.4285900913136223e-05</v>
+        <v>-0.00082985883371058337</v>
       </c>
       <c r="O27">
-        <v>-3.9376425907337837e-05</v>
+        <v>0.0010368197386893077</v>
       </c>
       <c r="P27">
-        <v>1.2566200672554834e-05</v>
+        <v>-0.00033334425671132577</v>
       </c>
       <c r="Q27">
-        <v>4.5494006807156369e-06</v>
+        <v>-9.1039749237398476e-05</v>
       </c>
       <c r="R27">
-        <v>1.0288745233226539e-05</v>
+        <v>-0.00030852253138595443</v>
       </c>
       <c r="S27">
-        <v>9.1764553226018826e-06</v>
+        <v>-0.00022172316541170729</v>
       </c>
       <c r="T27">
-        <v>-7.7592997908764342e-07</v>
+        <v>-7.6367605385134772e-05</v>
       </c>
       <c r="U27">
-        <v>5.0793106254111995e-06</v>
+        <v>-3.9207991982039133e-05</v>
       </c>
       <c r="V27">
-        <v>-1.7865352875426029e-06</v>
+        <v>-6.9794394013300044e-05</v>
       </c>
       <c r="W27">
-        <v>4.1972335415238635e-06</v>
+        <v>7.0679743701248729e-05</v>
       </c>
       <c r="X27">
-        <v>2.789334889637319e-05</v>
+        <v>-0.0001686305716581142</v>
       </c>
       <c r="Y27">
-        <v>-7.5460363116073518e-07</v>
+        <v>-0.00067782728624898869</v>
       </c>
       <c r="Z27">
-        <v>1.8466356831338263e-06</v>
+        <v>-5.5047243570886459e-05</v>
       </c>
       <c r="AA27">
-        <v>-7.2257821613665649e-05</v>
+        <v>-3.1910120652461557e-05</v>
       </c>
       <c r="AB27">
-        <v>2.5124558729526775e-06</v>
+        <v>0.0022413230406927208</v>
       </c>
       <c r="AC27">
-        <v>-1.0015881312580902e-06</v>
+        <v>-7.43931405809783e-05</v>
       </c>
       <c r="AD27">
-        <v>-7.3779005177758341e-07</v>
+        <v>0.0001650521923487018</v>
       </c>
       <c r="AE27">
-        <v>-1.1698144284082195e-06</v>
+        <v>0.00011855063277800299</v>
       </c>
       <c r="AF27">
-        <v>6.9740551511446964e-06</v>
+        <v>0.00012986073548623515</v>
       </c>
       <c r="AG27">
-        <v>-4.5026484205747396e-06</v>
+        <v>-0.00010325598946626848</v>
       </c>
       <c r="AH27">
-        <v>-2.4296404935500969e-06</v>
+        <v>0.00026015515822356552</v>
       </c>
       <c r="AI27">
-        <v>-0.00063133969950604941</v>
+        <v>0.00020452690656745003</v>
+      </c>
+      <c r="AJ27">
+        <v>0.010661658610058772</v>
       </c>
     </row>
     <row r="28">
@@ -3304,106 +3388,109 @@
         <v>50</v>
       </c>
       <c r="B28">
-        <v>0.04167503069944499</v>
+        <v>-0.0023646765793139718</v>
       </c>
       <c r="C28">
-        <v>0.013289755297482164</v>
+        <v>1.2232335546196772e-05</v>
       </c>
       <c r="D28">
-        <v>-0.00024188602674922975</v>
+        <v>-1.3201437961548549e-06</v>
       </c>
       <c r="E28">
-        <v>3.6451992819760764e-06</v>
+        <v>1.7554184113501017e-08</v>
       </c>
       <c r="F28">
-        <v>-0.00019699754339597142</v>
+        <v>-6.4020514655219185e-08</v>
       </c>
       <c r="G28">
-        <v>6.8786265495446308e-05</v>
+        <v>1.0138052308726608e-06</v>
       </c>
       <c r="H28">
-        <v>-0.00042780656961566299</v>
+        <v>2.2603731803256394e-06</v>
       </c>
       <c r="I28">
-        <v>-0.000324765342721689</v>
+        <v>-2.7577286006042617e-06</v>
       </c>
       <c r="J28">
-        <v>0.00064035711923646601</v>
+        <v>1.6187036676253573e-05</v>
       </c>
       <c r="K28">
-        <v>-0.00040729115004866496</v>
+        <v>-5.9608906500921002e-06</v>
       </c>
       <c r="L28">
-        <v>-0.00053456493072570437</v>
+        <v>9.1034956044077709e-08</v>
       </c>
       <c r="M28">
-        <v>-0.0027004584629066221</v>
+        <v>-2.7567916788975833e-05</v>
       </c>
       <c r="N28">
-        <v>-0.0031388737448439976</v>
+        <v>2.809492346334829e-05</v>
       </c>
       <c r="O28">
-        <v>0.0029590099578440327</v>
+        <v>-4.1639116238285435e-05</v>
       </c>
       <c r="P28">
-        <v>-0.00042413028890383965</v>
+        <v>1.4322448704067536e-05</v>
       </c>
       <c r="Q28">
-        <v>-0.0007873479153950693</v>
+        <v>6.06305458166338e-06</v>
       </c>
       <c r="R28">
-        <v>-0.0010825205005590996</v>
+        <v>1.2459774472939184e-05</v>
       </c>
       <c r="S28">
-        <v>-0.00093168661198174277</v>
+        <v>1.101674702892644e-05</v>
       </c>
       <c r="T28">
-        <v>-7.8903725190907094e-05</v>
+        <v>2.2401081404480074e-06</v>
       </c>
       <c r="U28">
-        <v>9.1711530249414001e-05</v>
+        <v>-1.5254212943521584e-06</v>
       </c>
       <c r="V28">
-        <v>0.00047686308164666068</v>
+        <v>3.3969857149139277e-06</v>
       </c>
       <c r="W28">
-        <v>0.00011137459986377499</v>
+        <v>-2.5561372439502885e-06</v>
       </c>
       <c r="X28">
-        <v>3.5985073037304166e-05</v>
+        <v>4.4284720053924211e-06</v>
       </c>
       <c r="Y28">
-        <v>-0.00041087233826457743</v>
+        <v>2.8824255623340523e-05</v>
       </c>
       <c r="Z28">
-        <v>-0.00045768293996529012</v>
+        <v>-7.2401136930286703e-07</v>
       </c>
       <c r="AA28">
-        <v>8.9628372583182639e-05</v>
+        <v>1.4156553197245368e-06</v>
       </c>
       <c r="AB28">
-        <v>-1.0015881312580902e-06</v>
+        <v>-7.43931405809783e-05</v>
       </c>
       <c r="AC28">
-        <v>0.011488447682848959</v>
+        <v>2.5874915615877642e-06</v>
       </c>
       <c r="AD28">
-        <v>0.0092046332573593737</v>
+        <v>-3.4299005781044376e-06</v>
       </c>
       <c r="AE28">
-        <v>0.0092047856289361584</v>
+        <v>-2.1653339114356012e-06</v>
       </c>
       <c r="AF28">
-        <v>0.0091423582562104085</v>
+        <v>-2.7739205788346745e-06</v>
       </c>
       <c r="AG28">
-        <v>0.0092088685782350591</v>
+        <v>6.5138796383137779e-06</v>
       </c>
       <c r="AH28">
-        <v>0.0091128549513319682</v>
+        <v>-6.2117989162608364e-06</v>
       </c>
       <c r="AI28">
-        <v>-0.006687039886200237</v>
+        <v>-4.734922682714303e-06</v>
+      </c>
+      <c r="AJ28">
+        <v>-0.00064911355533666792</v>
       </c>
     </row>
     <row r="29">
@@ -3411,106 +3498,109 @@
         <v>51</v>
       </c>
       <c r="B29">
-        <v>0.10310886125724626</v>
+        <v>0.044700567108955258</v>
       </c>
       <c r="C29">
-        <v>0.010614052731393764</v>
+        <v>0.012352768684668003</v>
       </c>
       <c r="D29">
-        <v>-0.00030942367085952556</v>
+        <v>-0.00025913318481369033</v>
       </c>
       <c r="E29">
-        <v>4.4418989474176646e-06</v>
+        <v>3.8559943109072196e-06</v>
       </c>
       <c r="F29">
-        <v>-0.00020824551216924725</v>
+        <v>-0.00026963384057465678</v>
       </c>
       <c r="G29">
-        <v>-0.00036735892814038218</v>
+        <v>-2.722479090172536e-05</v>
       </c>
       <c r="H29">
-        <v>-0.0005574749959784131</v>
+        <v>-0.0005194671027988762</v>
       </c>
       <c r="I29">
-        <v>-0.00057493221463100763</v>
+        <v>-0.00042836153031172719</v>
       </c>
       <c r="J29">
-        <v>0.00026474484208860016</v>
+        <v>0.00071167103031875151</v>
       </c>
       <c r="K29">
-        <v>-0.00027490264218683988</v>
+        <v>-0.0004843125908789755</v>
       </c>
       <c r="L29">
-        <v>-0.00043824622233876957</v>
+        <v>-0.00048968528688025491</v>
       </c>
       <c r="M29">
-        <v>-0.0022746277761699369</v>
+        <v>-0.0027267800837532923</v>
       </c>
       <c r="N29">
-        <v>-0.0028889668244260315</v>
+        <v>-0.0032160436069721549</v>
       </c>
       <c r="O29">
-        <v>0.0029566608918253469</v>
+        <v>0.002879560547387707</v>
       </c>
       <c r="P29">
-        <v>-0.00026961053484948327</v>
+        <v>-0.00044987536369928095</v>
       </c>
       <c r="Q29">
-        <v>-0.00049846813573303046</v>
+        <v>-0.00095422260525676291</v>
       </c>
       <c r="R29">
-        <v>-0.00084236937991497224</v>
+        <v>-0.0013242211544942004</v>
       </c>
       <c r="S29">
-        <v>-0.00077782163662643445</v>
+        <v>-0.0011505919882662924</v>
       </c>
       <c r="T29">
-        <v>-1.0264725569824229e-05</v>
+        <v>0.00013967521508012981</v>
       </c>
       <c r="U29">
-        <v>2.4608333511752902e-05</v>
+        <v>-0.00035916420322860401</v>
       </c>
       <c r="V29">
-        <v>0.00037349392819110722</v>
+        <v>-2.1366953860633368e-05</v>
       </c>
       <c r="W29">
-        <v>7.1193961384888251e-05</v>
+        <v>0.00048877945911205106</v>
       </c>
       <c r="X29">
-        <v>4.7169146713054583e-05</v>
+        <v>0.00015989314681997912</v>
       </c>
       <c r="Y29">
-        <v>-0.00038357456557543482</v>
+        <v>1.304982083655086e-05</v>
       </c>
       <c r="Z29">
-        <v>-0.00040503652639068593</v>
+        <v>-0.00051506165346824201</v>
       </c>
       <c r="AA29">
-        <v>7.2220706308261454e-05</v>
+        <v>-0.00056890703141835664</v>
       </c>
       <c r="AB29">
-        <v>-7.3779005177758341e-07</v>
+        <v>0.0001650521923487018</v>
       </c>
       <c r="AC29">
-        <v>0.0092046332573593737</v>
+        <v>-3.4299005781044376e-06</v>
       </c>
       <c r="AD29">
-        <v>0.010827043862000372</v>
+        <v>0.012068571684063556</v>
       </c>
       <c r="AE29">
-        <v>0.0091974099850577664</v>
+        <v>0.0097215900650027207</v>
       </c>
       <c r="AF29">
-        <v>0.0091023254753601762</v>
+        <v>0.0097098930003031228</v>
       </c>
       <c r="AG29">
-        <v>0.00919674805079858</v>
+        <v>0.0096437636353384065</v>
       </c>
       <c r="AH29">
-        <v>0.0090904353535499072</v>
+        <v>0.0097224714876178626</v>
       </c>
       <c r="AI29">
-        <v>-0.0055250382987592477</v>
+        <v>0.0096175426607269157</v>
+      </c>
+      <c r="AJ29">
+        <v>-0.0062361206629742445</v>
       </c>
     </row>
     <row r="30">
@@ -3518,106 +3608,109 @@
         <v>52</v>
       </c>
       <c r="B30">
-        <v>0.065076006542452658</v>
+        <v>0.10755858213469907</v>
       </c>
       <c r="C30">
-        <v>0.013802604640571599</v>
+        <v>0.0094684639002704241</v>
       </c>
       <c r="D30">
-        <v>-0.00018723769281027642</v>
+        <v>-0.00031972678353795608</v>
       </c>
       <c r="E30">
-        <v>2.7680291872209567e-06</v>
+        <v>4.5446123549131305e-06</v>
       </c>
       <c r="F30">
-        <v>0.00017468720633960488</v>
+        <v>-0.00030229303508072514</v>
       </c>
       <c r="G30">
-        <v>-0.00014678654306091166</v>
+        <v>-0.00050747929637179334</v>
       </c>
       <c r="H30">
-        <v>-0.00017287982960645376</v>
+        <v>-0.00065521853583794254</v>
       </c>
       <c r="I30">
-        <v>-0.0002283139001940937</v>
+        <v>-0.00068299009515571108</v>
       </c>
       <c r="J30">
-        <v>0.00039196167911758251</v>
+        <v>0.0002955191502173873</v>
       </c>
       <c r="K30">
-        <v>-0.00046727857092587012</v>
+        <v>-0.0003101845513583145</v>
       </c>
       <c r="L30">
-        <v>-0.00053827432424176087</v>
+        <v>-0.00038332998564618616</v>
       </c>
       <c r="M30">
-        <v>-0.0026229122312671298</v>
+        <v>-0.0022728772854662006</v>
       </c>
       <c r="N30">
-        <v>-0.0029990878132675714</v>
+        <v>-0.0029662849096437887</v>
       </c>
       <c r="O30">
-        <v>0.0030715942386580044</v>
+        <v>0.0028818244746878227</v>
       </c>
       <c r="P30">
-        <v>0.00011916511678051035</v>
+        <v>-0.00026898932976012358</v>
       </c>
       <c r="Q30">
-        <v>-0.00052890627267357393</v>
+        <v>-0.00064572875638472778</v>
       </c>
       <c r="R30">
-        <v>-0.00087550261182786659</v>
+        <v>-0.0010593619085024497</v>
       </c>
       <c r="S30">
-        <v>-0.00085792086063237144</v>
+        <v>-0.00098074851741361286</v>
       </c>
       <c r="T30">
-        <v>-3.5954064999674292e-05</v>
+        <v>0.00028049044791821147</v>
       </c>
       <c r="U30">
-        <v>9.8761412541536575e-05</v>
+        <v>-0.00017647299743263735</v>
       </c>
       <c r="V30">
-        <v>0.00040157710779500742</v>
+        <v>-0.00012252613807813982</v>
       </c>
       <c r="W30">
-        <v>3.697363353992446e-05</v>
+        <v>0.0003841513413991712</v>
       </c>
       <c r="X30">
-        <v>5.0652765044222406e-05</v>
+        <v>0.00010592887561970476</v>
       </c>
       <c r="Y30">
-        <v>-0.00099606404171733061</v>
+        <v>3.3948965047882543e-05</v>
       </c>
       <c r="Z30">
-        <v>-0.00043714554398675408</v>
+        <v>-0.00049993377405562443</v>
       </c>
       <c r="AA30">
-        <v>8.0023146107070916e-05</v>
+        <v>-0.00051280710073887828</v>
       </c>
       <c r="AB30">
-        <v>-1.1698144284082195e-06</v>
+        <v>0.00011855063277800299</v>
       </c>
       <c r="AC30">
-        <v>0.0092047856289361584</v>
+        <v>-2.1653339114356012e-06</v>
       </c>
       <c r="AD30">
-        <v>0.0091974099850577664</v>
+        <v>0.0097215900650027207</v>
       </c>
       <c r="AE30">
-        <v>0.01133640407994198</v>
+        <v>0.011392037575865812</v>
       </c>
       <c r="AF30">
-        <v>0.0091039339507785165</v>
+        <v>0.0097247084703939168</v>
       </c>
       <c r="AG30">
-        <v>0.0092055352035067713</v>
+        <v>0.0096160185609221287</v>
       </c>
       <c r="AH30">
-        <v>0.0090861998044262111</v>
+        <v>0.0097231164248499993</v>
       </c>
       <c r="AI30">
-        <v>-0.0081355012748429434</v>
+        <v>0.0096054071864162521</v>
+      </c>
+      <c r="AJ30">
+        <v>-0.005416072353583325</v>
       </c>
     </row>
     <row r="31">
@@ -3625,106 +3718,109 @@
         <v>53</v>
       </c>
       <c r="B31">
-        <v>0.063587509141651385</v>
+        <v>0.071389523501868141</v>
       </c>
       <c r="C31">
-        <v>0.013342535415184625</v>
+        <v>0.013109054646122054</v>
       </c>
       <c r="D31">
-        <v>-0.00020488777842849783</v>
+        <v>-0.0001902478692502492</v>
       </c>
       <c r="E31">
-        <v>3.0622265848598892e-06</v>
+        <v>2.8008612660330339e-06</v>
       </c>
       <c r="F31">
-        <v>3.2859136858631732e-05</v>
+        <v>5.1111423175653759e-05</v>
       </c>
       <c r="G31">
-        <v>-0.00037585828223651863</v>
+        <v>-0.00028813322742500536</v>
       </c>
       <c r="H31">
-        <v>-0.00038913928229977746</v>
+        <v>-0.00030694086771507201</v>
       </c>
       <c r="I31">
-        <v>-0.00039250915359423377</v>
+        <v>-0.00036555191390709452</v>
       </c>
       <c r="J31">
-        <v>0.00041074118580697013</v>
+        <v>0.00043743257823449259</v>
       </c>
       <c r="K31">
-        <v>-0.00048629489875235505</v>
+        <v>-0.00050411556076881427</v>
       </c>
       <c r="L31">
-        <v>-0.00054105770059326673</v>
+        <v>-0.00050383865992559848</v>
       </c>
       <c r="M31">
-        <v>-0.0025877187412414633</v>
+        <v>-0.0026334675305861605</v>
       </c>
       <c r="N31">
-        <v>-0.0026889008674822988</v>
+        <v>-0.0030931317431023672</v>
       </c>
       <c r="O31">
-        <v>0.0030454467097911979</v>
+        <v>0.0029994411987923036</v>
       </c>
       <c r="P31">
-        <v>-0.00029816000897347865</v>
+        <v>0.00014406173637961735</v>
       </c>
       <c r="Q31">
-        <v>-0.00060330102428831191</v>
+        <v>-0.00065807909882752743</v>
       </c>
       <c r="R31">
-        <v>-0.00075900176349736844</v>
+        <v>-0.0010565806993199794</v>
       </c>
       <c r="S31">
-        <v>-0.00058126274490196859</v>
+        <v>-0.001045777108736315</v>
       </c>
       <c r="T31">
-        <v>-0.00011167788887903607</v>
+        <v>0.00017423587731126499</v>
       </c>
       <c r="U31">
-        <v>5.9025370231384922e-05</v>
+        <v>-0.00024732176697266772</v>
       </c>
       <c r="V31">
-        <v>0.00017070913422620026</v>
+        <v>2.2211581000094126e-05</v>
       </c>
       <c r="W31">
-        <v>4.2166999705862149e-05</v>
+        <v>0.00041072200204037641</v>
       </c>
       <c r="X31">
-        <v>0.00018495111207299415</v>
+        <v>5.2209263367333951e-05</v>
       </c>
       <c r="Y31">
-        <v>-0.00057831513560633978</v>
+        <v>3.8346599379767039e-05</v>
       </c>
       <c r="Z31">
-        <v>-0.0003680345232809413</v>
+        <v>-0.0010938002976127363</v>
       </c>
       <c r="AA31">
-        <v>-0.00012200891346675607</v>
+        <v>-0.00053940517113822432</v>
       </c>
       <c r="AB31">
-        <v>6.9740551511446964e-06</v>
+        <v>0.00012986073548623515</v>
       </c>
       <c r="AC31">
-        <v>0.0091423582562104085</v>
+        <v>-2.7739205788346745e-06</v>
       </c>
       <c r="AD31">
-        <v>0.0091023254753601762</v>
+        <v>0.0097098930003031228</v>
       </c>
       <c r="AE31">
-        <v>0.0091039339507785165</v>
+        <v>0.0097247084703939168</v>
       </c>
       <c r="AF31">
-        <v>0.01081139296070547</v>
+        <v>0.011889367767367629</v>
       </c>
       <c r="AG31">
-        <v>0.0091199104696842795</v>
+        <v>0.0096119711721066661</v>
       </c>
       <c r="AH31">
-        <v>0.0091178754488955918</v>
+        <v>0.0097257751163770858</v>
       </c>
       <c r="AI31">
-        <v>-0.011965852488803381</v>
+        <v>0.0095946063200273019</v>
+      </c>
+      <c r="AJ31">
+        <v>-0.0081911512967937847</v>
       </c>
     </row>
     <row r="32">
@@ -3732,106 +3828,109 @@
         <v>54</v>
       </c>
       <c r="B32">
-        <v>0.10130930003517388</v>
+        <v>0.068747004319453117</v>
       </c>
       <c r="C32">
-        <v>0.013547676971519824</v>
+        <v>0.011757120176712266</v>
       </c>
       <c r="D32">
-        <v>-0.00018763163193530764</v>
+        <v>-0.0002336475160176453</v>
       </c>
       <c r="E32">
-        <v>2.8186374644986398e-06</v>
+        <v>3.4113027974215341e-06</v>
       </c>
       <c r="F32">
-        <v>0.0004373057883380882</v>
+        <v>-5.3124251327252292e-05</v>
       </c>
       <c r="G32">
-        <v>-0.00035559774632820673</v>
+        <v>-0.00052548304366584198</v>
       </c>
       <c r="H32">
-        <v>-0.00032075966531550093</v>
+        <v>-0.00049800624425511142</v>
       </c>
       <c r="I32">
-        <v>-0.00031641590305528378</v>
+        <v>-0.00051092846576128448</v>
       </c>
       <c r="J32">
-        <v>0.00067096704356365915</v>
+        <v>0.00046058125842611715</v>
       </c>
       <c r="K32">
-        <v>-0.00062927862323973265</v>
+        <v>-0.00055116890330128305</v>
       </c>
       <c r="L32">
-        <v>-0.00054505874245996846</v>
+        <v>-0.00047085365539634855</v>
       </c>
       <c r="M32">
-        <v>-0.0026887852341772166</v>
+        <v>-0.0025787895997136084</v>
       </c>
       <c r="N32">
-        <v>-0.0025676868395537837</v>
+        <v>-0.0026919974458402222</v>
       </c>
       <c r="O32">
-        <v>0.0033657017644494608</v>
+        <v>0.0030099481208004171</v>
       </c>
       <c r="P32">
-        <v>-0.00021161917505449338</v>
+        <v>-0.00028189896236239511</v>
       </c>
       <c r="Q32">
-        <v>-0.000391806544723773</v>
+        <v>-0.00073458664625755351</v>
       </c>
       <c r="R32">
-        <v>-0.00070737302321325323</v>
+        <v>-0.00094538972593384216</v>
       </c>
       <c r="S32">
-        <v>-0.00061193036376472202</v>
+        <v>-0.00074984388122480237</v>
       </c>
       <c r="T32">
-        <v>-7.3799463098876971e-05</v>
+        <v>0.00016484563742359454</v>
       </c>
       <c r="U32">
-        <v>-1.8693498563849566e-05</v>
+        <v>-0.00039414874908908697</v>
       </c>
       <c r="V32">
-        <v>0.00042331984530001208</v>
+        <v>-0.00010151274912743109</v>
       </c>
       <c r="W32">
-        <v>7.0035679735096039e-05</v>
+        <v>0.00017868472712351561</v>
       </c>
       <c r="X32">
-        <v>4.7762933084663593e-05</v>
+        <v>8.2708495274138618e-05</v>
       </c>
       <c r="Y32">
-        <v>-0.00088142540502298469</v>
+        <v>0.00018547195669557821</v>
       </c>
       <c r="Z32">
-        <v>-0.00027877858672470618</v>
+        <v>-0.00069309200635041778</v>
       </c>
       <c r="AA32">
-        <v>0.00020671392982635596</v>
+        <v>-0.00047135732603801423</v>
       </c>
       <c r="AB32">
-        <v>-4.5026484205747396e-06</v>
+        <v>-0.00010325598946626848</v>
       </c>
       <c r="AC32">
-        <v>0.0092088685782350591</v>
+        <v>6.5138796383137779e-06</v>
       </c>
       <c r="AD32">
-        <v>0.00919674805079858</v>
+        <v>0.0096437636353384065</v>
       </c>
       <c r="AE32">
-        <v>0.0092055352035067713</v>
+        <v>0.0096160185609221287</v>
       </c>
       <c r="AF32">
-        <v>0.0091199104696842795</v>
+        <v>0.0096119711721066661</v>
       </c>
       <c r="AG32">
-        <v>0.010157889634619489</v>
+        <v>0.011379592579578133</v>
       </c>
       <c r="AH32">
-        <v>0.0090924111472559868</v>
+        <v>0.0096262184450768336</v>
       </c>
       <c r="AI32">
-        <v>-0.009260388113579654</v>
+        <v>0.0096167344537189774</v>
+      </c>
+      <c r="AJ32">
+        <v>-0.01188327960065598</v>
       </c>
     </row>
     <row r="33">
@@ -3839,106 +3938,109 @@
         <v>55</v>
       </c>
       <c r="B33">
-        <v>0.081128233130826594</v>
+        <v>0.10684803463333821</v>
       </c>
       <c r="C33">
-        <v>0.010977371294658339</v>
+        <v>0.012178381634644971</v>
       </c>
       <c r="D33">
-        <v>-0.00026767623432941926</v>
+        <v>-0.0002131261504103284</v>
       </c>
       <c r="E33">
-        <v>3.9839162319782326e-06</v>
+        <v>3.1354343175727539e-06</v>
       </c>
       <c r="F33">
-        <v>-2.6705380407290868e-05</v>
+        <v>0.00030951872868142938</v>
       </c>
       <c r="G33">
-        <v>-0.00054884068747695913</v>
+        <v>-0.0004638058761665953</v>
       </c>
       <c r="H33">
-        <v>-0.00049815122937303669</v>
+        <v>-0.00039600732195300969</v>
       </c>
       <c r="I33">
-        <v>-0.00059871869722495641</v>
+        <v>-0.00040214909048520708</v>
       </c>
       <c r="J33">
-        <v>0.00026785724039906636</v>
+        <v>0.00070204836502050323</v>
       </c>
       <c r="K33">
-        <v>-0.00042034453788511125</v>
+        <v>-0.00068720238313065441</v>
       </c>
       <c r="L33">
-        <v>-0.00045213393508005024</v>
+        <v>-0.00048319697802431711</v>
       </c>
       <c r="M33">
-        <v>-0.0019966838962494384</v>
+        <v>-0.0026695457881824917</v>
       </c>
       <c r="N33">
-        <v>-0.0024149540736188501</v>
+        <v>-0.0026112751116294107</v>
       </c>
       <c r="O33">
-        <v>0.0038604514672349322</v>
+        <v>0.0033101054896326402</v>
       </c>
       <c r="P33">
-        <v>-0.00038891201818296961</v>
+        <v>-0.00022195308815425895</v>
       </c>
       <c r="Q33">
-        <v>-0.0007169162807663486</v>
+        <v>-0.00052804773378511049</v>
       </c>
       <c r="R33">
-        <v>-0.00086428267837278337</v>
+        <v>-0.00093948473387639757</v>
       </c>
       <c r="S33">
-        <v>-0.00067139522295163641</v>
+        <v>-0.00081647293075966839</v>
       </c>
       <c r="T33">
-        <v>-0.0001718781608681397</v>
+        <v>0.00018156420170203176</v>
       </c>
       <c r="U33">
-        <v>0.00012872899156129742</v>
+        <v>-0.00033894208402273946</v>
       </c>
       <c r="V33">
-        <v>0.00018568745674472096</v>
+        <v>-0.00013961506885963474</v>
       </c>
       <c r="W33">
-        <v>3.7842730000199607e-05</v>
+        <v>0.00044821161996494967</v>
       </c>
       <c r="X33">
-        <v>6.1725593539739814e-05</v>
+        <v>0.00011480472909783975</v>
       </c>
       <c r="Y33">
-        <v>-0.00098315835379058757</v>
+        <v>3.1197360787280429e-05</v>
       </c>
       <c r="Z33">
-        <v>-0.00045863147275237884</v>
+        <v>-0.00099157759065768639</v>
       </c>
       <c r="AA33">
-        <v>0.00013464482304841778</v>
+        <v>-0.00039505552640802986</v>
       </c>
       <c r="AB33">
-        <v>-2.4296404935500969e-06</v>
+        <v>0.00026015515822356552</v>
       </c>
       <c r="AC33">
-        <v>0.0091128549513319682</v>
+        <v>-6.2117989162608364e-06</v>
       </c>
       <c r="AD33">
-        <v>0.0090904353535499072</v>
+        <v>0.0097224714876178626</v>
       </c>
       <c r="AE33">
-        <v>0.0090861998044262111</v>
+        <v>0.0097231164248499993</v>
       </c>
       <c r="AF33">
-        <v>0.0091178754488955918</v>
+        <v>0.0097257751163770858</v>
       </c>
       <c r="AG33">
-        <v>0.0090924111472559868</v>
+        <v>0.0096262184450768336</v>
       </c>
       <c r="AH33">
-        <v>0.010458015613964939</v>
+        <v>0.010697695275255008</v>
       </c>
       <c r="AI33">
-        <v>-0.0072639290218526817</v>
+        <v>0.0095993074569317334</v>
+      </c>
+      <c r="AJ33">
+        <v>-0.0087977500786448875</v>
       </c>
     </row>
     <row r="34">
@@ -3946,106 +4048,219 @@
         <v>56</v>
       </c>
       <c r="B34">
-        <v>-7.5014478557055817</v>
+        <v>0.086775025038209913</v>
       </c>
       <c r="C34">
-        <v>-0.40253927747843399</v>
+        <v>0.009746672677643467</v>
       </c>
       <c r="D34">
-        <v>-0.022425967133208467</v>
+        <v>-0.00028790444598063986</v>
       </c>
       <c r="E34">
-        <v>0.00030522568860010516</v>
+        <v>4.2500031558900272e-06</v>
       </c>
       <c r="F34">
-        <v>-0.061142915903919799</v>
+        <v>-0.00010427112488800572</v>
       </c>
       <c r="G34">
-        <v>-0.07692951241091886</v>
+        <v>-0.00073041362526063414</v>
       </c>
       <c r="H34">
-        <v>-0.072827229016091288</v>
+        <v>-0.00060407156948102947</v>
       </c>
       <c r="I34">
-        <v>-0.074902994544512672</v>
+        <v>-0.00072643168811993564</v>
       </c>
       <c r="J34">
-        <v>-0.016273479518709041</v>
+        <v>0.00032291640328157949</v>
       </c>
       <c r="K34">
-        <v>-0.0028706581611771622</v>
+        <v>-0.00047989350412604924</v>
       </c>
       <c r="L34">
-        <v>0.014770115678727103</v>
+        <v>-0.00039388708121651864</v>
       </c>
       <c r="M34">
-        <v>0.042560118928667803</v>
+        <v>-0.0020049185779722851</v>
       </c>
       <c r="N34">
-        <v>0.002806812868468702</v>
+        <v>-0.0024664750228936597</v>
       </c>
       <c r="O34">
-        <v>0.014040958222916164</v>
+        <v>0.0038467197948812825</v>
       </c>
       <c r="P34">
-        <v>-0.010335785793734951</v>
+        <v>-0.00042738192690495026</v>
       </c>
       <c r="Q34">
-        <v>-0.0066607958970502489</v>
+        <v>-0.00090346517113689567</v>
       </c>
       <c r="R34">
-        <v>-0.0060576403963884546</v>
+        <v>-0.0010926162612756923</v>
       </c>
       <c r="S34">
-        <v>-0.0072893218727677657</v>
+        <v>-0.00090545178776167495</v>
       </c>
       <c r="T34">
-        <v>0.0033492145023693997</v>
+        <v>9.5029596718553206e-05</v>
       </c>
       <c r="U34">
-        <v>5.7900964421969177e-05</v>
+        <v>-0.00049835162210639164</v>
       </c>
       <c r="V34">
-        <v>-0.00083298470338044692</v>
+        <v>-1.9030236020144793e-05</v>
       </c>
       <c r="W34">
-        <v>0.0030784277533595075</v>
+        <v>0.00021368823292435804</v>
       </c>
       <c r="X34">
-        <v>-0.019785567956063371</v>
+        <v>9.9565044679886269e-05</v>
       </c>
       <c r="Y34">
-        <v>0.012859675143308099</v>
+        <v>3.7368271585214684e-05</v>
       </c>
       <c r="Z34">
-        <v>-0.0011966209011909999</v>
+        <v>-0.0010985823354876028</v>
       </c>
       <c r="AA34">
-        <v>0.010414752190208749</v>
+        <v>-0.00058835849405848963</v>
       </c>
       <c r="AB34">
-        <v>-0.00063133969950604941</v>
+        <v>0.00020452690656745003</v>
       </c>
       <c r="AC34">
-        <v>-0.006687039886200237</v>
+        <v>-4.734922682714303e-06</v>
       </c>
       <c r="AD34">
-        <v>-0.0055250382987592477</v>
+        <v>0.0096175426607269157</v>
       </c>
       <c r="AE34">
-        <v>-0.0081355012748429434</v>
+        <v>0.0096054071864162521</v>
       </c>
       <c r="AF34">
-        <v>-0.011965852488803381</v>
+        <v>0.0095946063200273019</v>
       </c>
       <c r="AG34">
-        <v>-0.009260388113579654</v>
+        <v>0.0096167344537189774</v>
       </c>
       <c r="AH34">
-        <v>-0.0072639290218526817</v>
+        <v>0.0095993074569317334</v>
       </c>
       <c r="AI34">
-        <v>1.2804849718497731</v>
+        <v>0.011011498720113538</v>
+      </c>
+      <c r="AJ34">
+        <v>-0.0066657953401909722</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>57</v>
+      </c>
+      <c r="B35">
+        <v>-7.50760868148111</v>
+      </c>
+      <c r="C35">
+        <v>-0.37311892966451871</v>
+      </c>
+      <c r="D35">
+        <v>-0.022249251698617419</v>
+      </c>
+      <c r="E35">
+        <v>0.00030329743687748336</v>
+      </c>
+      <c r="F35">
+        <v>-0.060133749086610844</v>
+      </c>
+      <c r="G35">
+        <v>-0.077140312484265283</v>
+      </c>
+      <c r="H35">
+        <v>-0.073182202790631645</v>
+      </c>
+      <c r="I35">
+        <v>-0.075567392646664261</v>
+      </c>
+      <c r="J35">
+        <v>-0.016078198363168674</v>
+      </c>
+      <c r="K35">
+        <v>-0.0029590583490347162</v>
+      </c>
+      <c r="L35">
+        <v>0.013623117641510661</v>
+      </c>
+      <c r="M35">
+        <v>0.040768146586417725</v>
+      </c>
+      <c r="N35">
+        <v>0.00059993195604187387</v>
+      </c>
+      <c r="O35">
+        <v>0.014009909190098795</v>
+      </c>
+      <c r="P35">
+        <v>-0.012054322743333104</v>
+      </c>
+      <c r="Q35">
+        <v>-0.0082232343440501853</v>
+      </c>
+      <c r="R35">
+        <v>-0.0069895405356792942</v>
+      </c>
+      <c r="S35">
+        <v>-0.008289191437113182</v>
+      </c>
+      <c r="T35">
+        <v>0.0019189591195111224</v>
+      </c>
+      <c r="U35">
+        <v>0.0093144568836014425</v>
+      </c>
+      <c r="V35">
+        <v>0.00074799310333424022</v>
+      </c>
+      <c r="W35">
+        <v>-4.0767698066891114e-05</v>
+      </c>
+      <c r="X35">
+        <v>0.0032033069023695939</v>
+      </c>
+      <c r="Y35">
+        <v>-0.020381158835424879</v>
+      </c>
+      <c r="Z35">
+        <v>0.011457681291717007</v>
+      </c>
+      <c r="AA35">
+        <v>-0.0012038743058375313</v>
+      </c>
+      <c r="AB35">
+        <v>0.010661658610058772</v>
+      </c>
+      <c r="AC35">
+        <v>-0.00064911355533666792</v>
+      </c>
+      <c r="AD35">
+        <v>-0.0062361206629742445</v>
+      </c>
+      <c r="AE35">
+        <v>-0.005416072353583325</v>
+      </c>
+      <c r="AF35">
+        <v>-0.0081911512967937847</v>
+      </c>
+      <c r="AG35">
+        <v>-0.01188327960065598</v>
+      </c>
+      <c r="AH35">
+        <v>-0.0087977500786448875</v>
+      </c>
+      <c r="AI35">
+        <v>-0.0066657953401909722</v>
+      </c>
+      <c r="AJ35">
+        <v>1.3024723570439418</v>
       </c>
     </row>
   </sheetData>

--- a/input/ES/reg_fertility.xlsx
+++ b/input/ES/reg_fertility.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="93" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="89" uniqueCount="57">
   <si>
     <t>Description</t>
   </si>
@@ -140,13 +140,7 @@
     <t>Ydses_c5_Q5_L1</t>
   </si>
   <si>
-    <t>Dnc1_L1</t>
-  </si>
-  <si>
-    <t>Dnc2_plus_L1</t>
-  </si>
-  <si>
-    <t>Dnc02_yes_L1</t>
+    <t>Dnc1_plus_L1</t>
   </si>
   <si>
     <t>Deh_c4_Low</t>
@@ -377,7 +371,7 @@
         <v>14</v>
       </c>
       <c r="B11">
-        <v>0.22583240468467514</v>
+        <v>0.19997614006574704</v>
       </c>
       <c r="C11"/>
       <c r="D11"/>
@@ -385,7 +379,7 @@
         <v>20</v>
       </c>
       <c r="F11">
-        <v>1110.9526961824765</v>
+        <v>986.92273337834104</v>
       </c>
     </row>
     <row r="12">
@@ -401,7 +395,7 @@
         <v>21</v>
       </c>
       <c r="F12">
-        <v>-10038232.588347603</v>
+        <v>-10373475.476540718</v>
       </c>
     </row>
   </sheetData>
@@ -410,7 +404,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AJ35"/>
+  <dimension ref="A1:AH33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -418,7 +412,7 @@
         <v>23</v>
       </c>
       <c r="B1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C1" t="s">
         <v>24</v>
@@ -515,12 +509,6 @@
       </c>
       <c r="AH1" t="s">
         <v>55</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="2">
@@ -528,109 +516,103 @@
         <v>24</v>
       </c>
       <c r="B2">
-        <v>10.28828366904478</v>
+        <v>10.515847533788207</v>
       </c>
       <c r="C2">
-        <v>4.0264820492458382</v>
+        <v>4.240015995882251</v>
       </c>
       <c r="D2">
-        <v>0.016511847314585056</v>
+        <v>0.01611108504742368</v>
       </c>
       <c r="E2">
-        <v>-0.00021891562602621467</v>
+        <v>-0.00021514182647979808</v>
       </c>
       <c r="F2">
-        <v>-0.0019806546731783448</v>
+        <v>-0.00020692929517621139</v>
       </c>
       <c r="G2">
-        <v>0.0069914406088493475</v>
+        <v>0.0070372230117672629</v>
       </c>
       <c r="H2">
-        <v>0.0053225052952228513</v>
+        <v>0.0055955751826003153</v>
       </c>
       <c r="I2">
-        <v>0.0066617728859940939</v>
+        <v>0.0069613367122043912</v>
       </c>
       <c r="J2">
-        <v>0.0068401309091116634</v>
+        <v>0.0081873427953190747</v>
       </c>
       <c r="K2">
-        <v>-0.0044960599519654615</v>
+        <v>-0.005623703683514808</v>
       </c>
       <c r="L2">
-        <v>-0.12910664187354523</v>
+        <v>-0.13776945365271934</v>
       </c>
       <c r="M2">
-        <v>-0.67873172975765528</v>
+        <v>-0.70802261938217781</v>
       </c>
       <c r="N2">
-        <v>-0.78093632353149845</v>
+        <v>-0.81500667558533579</v>
       </c>
       <c r="O2">
-        <v>-0.41699609051896836</v>
+        <v>-0.43968146212347875</v>
       </c>
       <c r="P2">
-        <v>0.009134840529856178</v>
+        <v>0.0084765769885288</v>
       </c>
       <c r="Q2">
-        <v>-0.012497257666346708</v>
+        <v>-0.011069886630613254</v>
       </c>
       <c r="R2">
-        <v>-0.016531622865446738</v>
+        <v>-0.015397025111691727</v>
       </c>
       <c r="S2">
-        <v>-0.021052870742490106</v>
+        <v>-0.019735211642398325</v>
       </c>
       <c r="T2">
-        <v>-0.01403103509017159</v>
+        <v>-0.013098940597170525</v>
       </c>
       <c r="U2">
-        <v>-0.014861015372463846</v>
+        <v>0.0016650801904650944</v>
       </c>
       <c r="V2">
-        <v>0.0051318929565080541</v>
+        <v>-5.6199152141975933e-05</v>
       </c>
       <c r="W2">
-        <v>0.0019271813196352072</v>
+        <v>0.0016080431451250959</v>
       </c>
       <c r="X2">
-        <v>-0.00056765398063500158</v>
+        <v>-0.032269201478047529</v>
       </c>
       <c r="Y2">
-        <v>0.0016190650379425339</v>
+        <v>-0.0059579173972693841</v>
       </c>
       <c r="Z2">
-        <v>-0.036502196669909948</v>
+        <v>0.00048662802986032538</v>
       </c>
       <c r="AA2">
-        <v>-0.0067386622581028372</v>
+        <v>1.5066495573121813e-05</v>
       </c>
       <c r="AB2">
-        <v>0.00061525010395119262</v>
+        <v>0.011669315298583338</v>
       </c>
       <c r="AC2">
-        <v>1.2232335546196772e-05</v>
+        <v>0.0093120988944704608</v>
       </c>
       <c r="AD2">
-        <v>0.012352768684668003</v>
+        <v>0.011556608522671812</v>
       </c>
       <c r="AE2">
-        <v>0.0094684639002704241</v>
+        <v>0.011129939035328051</v>
       </c>
       <c r="AF2">
-        <v>0.013109054646122054</v>
+        <v>0.011635219672043999</v>
       </c>
       <c r="AG2">
-        <v>0.011757120176712266</v>
+        <v>0.0084980468441929885</v>
       </c>
       <c r="AH2">
-        <v>0.012178381634644971</v>
-      </c>
-      <c r="AI2">
-        <v>0.009746672677643467</v>
-      </c>
-      <c r="AJ2">
-        <v>-0.37311892966451871</v>
+        <v>-0.36258931257519111</v>
       </c>
     </row>
     <row r="3">
@@ -638,109 +620,103 @@
         <v>25</v>
       </c>
       <c r="B3">
-        <v>0.3765273314776737</v>
+        <v>0.35241834406855749</v>
       </c>
       <c r="C3">
-        <v>0.016511847314585056</v>
+        <v>0.01611108504742368</v>
       </c>
       <c r="D3">
-        <v>0.0012601148983745845</v>
+        <v>0.0011952662437026661</v>
       </c>
       <c r="E3">
-        <v>-1.750413119638845e-05</v>
+        <v>-1.6591071666588392e-05</v>
       </c>
       <c r="F3">
-        <v>-0.00025903859447572869</v>
+        <v>-1.8044809451327193e-05</v>
       </c>
       <c r="G3">
-        <v>0.00037875841799748199</v>
+        <v>0.00037627105366754357</v>
       </c>
       <c r="H3">
-        <v>0.00019802447148850773</v>
+        <v>0.00016966903073059245</v>
       </c>
       <c r="I3">
-        <v>0.00035183995322166616</v>
+        <v>0.00031388780937911809</v>
       </c>
       <c r="J3">
-        <v>0.0004770352383460663</v>
+        <v>0.00059692610060718254</v>
       </c>
       <c r="K3">
-        <v>2.8523648163845863e-05</v>
+        <v>1.2814391383489734e-05</v>
       </c>
       <c r="L3">
-        <v>-0.00060590155380684484</v>
+        <v>-0.00059934166357366518</v>
       </c>
       <c r="M3">
-        <v>-0.00066020688256818356</v>
+        <v>-0.00077892522074326034</v>
       </c>
       <c r="N3">
-        <v>-0.00019717856783842006</v>
+        <v>-0.00019355037209791738</v>
       </c>
       <c r="O3">
-        <v>0.00010327853045473748</v>
+        <v>9.4577824913589029e-05</v>
       </c>
       <c r="P3">
-        <v>-8.0230439460864545e-05</v>
+        <v>-0.00012089150507065731</v>
       </c>
       <c r="Q3">
-        <v>-0.00030388784763747917</v>
+        <v>-0.00030291784111194701</v>
       </c>
       <c r="R3">
-        <v>-0.00030995834585633819</v>
+        <v>-0.00030019779147664799</v>
       </c>
       <c r="S3">
-        <v>-0.00038970639162901912</v>
+        <v>-0.00035985426572260597</v>
       </c>
       <c r="T3">
-        <v>-3.3615211987328593e-05</v>
+        <v>-0.00014097021510243567</v>
       </c>
       <c r="U3">
-        <v>-0.00011066982474565619</v>
+        <v>-4.1782178571726173e-05</v>
       </c>
       <c r="V3">
-        <v>-0.00023393056887593858</v>
+        <v>-0.00015962069767801569</v>
       </c>
       <c r="W3">
-        <v>-4.0250667569825295e-05</v>
+        <v>6.5072685155403119e-06</v>
       </c>
       <c r="X3">
-        <v>-0.00015939846490364926</v>
+        <v>-0.00030540591246199997</v>
       </c>
       <c r="Y3">
-        <v>2.7557411350635948e-06</v>
+        <v>-8.3116208358555068e-05</v>
       </c>
       <c r="Z3">
-        <v>-0.00044795679051351251</v>
+        <v>3.6733248378944747e-05</v>
       </c>
       <c r="AA3">
-        <v>-4.4919305012504005e-05</v>
+        <v>-8.7558222580175812e-07</v>
       </c>
       <c r="AB3">
-        <v>5.0034921853884043e-05</v>
+        <v>-0.00024564504054930963</v>
       </c>
       <c r="AC3">
-        <v>-1.3201437961548549e-06</v>
+        <v>-0.00031853039605623558</v>
       </c>
       <c r="AD3">
-        <v>-0.00025913318481369033</v>
+        <v>-0.00021165120196874228</v>
       </c>
       <c r="AE3">
-        <v>-0.00031972678353795608</v>
+        <v>-0.00022402289232652598</v>
       </c>
       <c r="AF3">
-        <v>-0.0001902478692502492</v>
+        <v>-0.00021953135582914503</v>
       </c>
       <c r="AG3">
-        <v>-0.0002336475160176453</v>
+        <v>-0.0002806125802082898</v>
       </c>
       <c r="AH3">
-        <v>-0.0002131261504103284</v>
-      </c>
-      <c r="AI3">
-        <v>-0.00028790444598063986</v>
-      </c>
-      <c r="AJ3">
-        <v>-0.022249251698617419</v>
+        <v>-0.021170598116270908</v>
       </c>
     </row>
     <row r="4">
@@ -748,109 +724,103 @@
         <v>26</v>
       </c>
       <c r="B4">
-        <v>-0.0062212832590872276</v>
+        <v>-0.0059108720187595826</v>
       </c>
       <c r="C4">
-        <v>-0.00021891562602621467</v>
+        <v>-0.00021514182647979808</v>
       </c>
       <c r="D4">
-        <v>-1.750413119638845e-05</v>
+        <v>-1.6591071666588392e-05</v>
       </c>
       <c r="E4">
-        <v>2.4584741848218557e-07</v>
+        <v>2.3280966914413128e-07</v>
       </c>
       <c r="F4">
-        <v>3.0440925414201175e-06</v>
+        <v>-1.476177515725085e-07</v>
       </c>
       <c r="G4">
-        <v>-4.8806396285952004e-06</v>
+        <v>-4.8791068988180905e-06</v>
       </c>
       <c r="H4">
-        <v>-2.3491670395210911e-06</v>
+        <v>-1.9577859405120208e-06</v>
       </c>
       <c r="I4">
-        <v>-4.3174216617076317e-06</v>
+        <v>-3.794789556816247e-06</v>
       </c>
       <c r="J4">
-        <v>-5.755835934742876e-06</v>
+        <v>-7.4783443527048237e-06</v>
       </c>
       <c r="K4">
-        <v>-3.2318630677959114e-07</v>
+        <v>-1.8246526846221842e-07</v>
       </c>
       <c r="L4">
-        <v>8.0168792119224057e-06</v>
+        <v>7.9920377602192855e-06</v>
       </c>
       <c r="M4">
-        <v>8.1691724576419637e-06</v>
+        <v>9.9024742619407234e-06</v>
       </c>
       <c r="N4">
-        <v>2.3262631773805615e-06</v>
+        <v>2.407469524371442e-06</v>
       </c>
       <c r="O4">
-        <v>-1.1290501425161248e-06</v>
+        <v>-1.0594273882335729e-06</v>
       </c>
       <c r="P4">
-        <v>1.0375098014718678e-06</v>
+        <v>1.4440561479496067e-06</v>
       </c>
       <c r="Q4">
-        <v>4.3844932218281975e-06</v>
+        <v>4.2973774890061788e-06</v>
       </c>
       <c r="R4">
-        <v>4.3193194425701289e-06</v>
+        <v>4.0917380859755017e-06</v>
       </c>
       <c r="S4">
-        <v>5.2133472251351553e-06</v>
+        <v>4.7051888651030374e-06</v>
       </c>
       <c r="T4">
-        <v>-5.8623768479945204e-07</v>
+        <v>1.1794717028021135e-06</v>
       </c>
       <c r="U4">
-        <v>4.7953007317183202e-07</v>
+        <v>9.4391642560298004e-07</v>
       </c>
       <c r="V4">
-        <v>4.1757462749229513e-06</v>
+        <v>2.2520036553976244e-06</v>
       </c>
       <c r="W4">
-        <v>9.0305587337487751e-07</v>
+        <v>-9.2056503310736378e-08</v>
       </c>
       <c r="X4">
-        <v>2.2494239875276752e-06</v>
+        <v>4.6355025348035996e-06</v>
       </c>
       <c r="Y4">
-        <v>-4.0966235322160223e-09</v>
+        <v>1.3225473832606516e-06</v>
       </c>
       <c r="Z4">
-        <v>6.4749595984658732e-06</v>
+        <v>-4.1025765813888847e-07</v>
       </c>
       <c r="AA4">
-        <v>6.7845143132435861e-07</v>
+        <v>9.2907841078439016e-09</v>
       </c>
       <c r="AB4">
-        <v>-6.4226139312095949e-07</v>
+        <v>3.6119996230524003e-06</v>
       </c>
       <c r="AC4">
-        <v>1.7554184113501017e-08</v>
+        <v>4.521407658426255e-06</v>
       </c>
       <c r="AD4">
-        <v>3.8559943109072196e-06</v>
+        <v>3.02577337755238e-06</v>
       </c>
       <c r="AE4">
-        <v>4.5446123549131305e-06</v>
+        <v>3.222293190110147e-06</v>
       </c>
       <c r="AF4">
-        <v>2.8008612660330339e-06</v>
+        <v>3.20845053578911e-06</v>
       </c>
       <c r="AG4">
-        <v>3.4113027974215341e-06</v>
+        <v>4.0555926569290607e-06</v>
       </c>
       <c r="AH4">
-        <v>3.1354343175727539e-06</v>
-      </c>
-      <c r="AI4">
-        <v>4.2500031558900272e-06</v>
-      </c>
-      <c r="AJ4">
-        <v>0.00030329743687748336</v>
+        <v>0.00028973280263590062</v>
       </c>
     </row>
     <row r="5">
@@ -858,109 +828,103 @@
         <v>27</v>
       </c>
       <c r="B5">
-        <v>0.35718175015469528</v>
+        <v>0.37612682517098228</v>
       </c>
       <c r="C5">
-        <v>-0.0019806546731783448</v>
+        <v>-0.00020692929517621139</v>
       </c>
       <c r="D5">
-        <v>-0.00025903859447572869</v>
+        <v>-1.8044809451327193e-05</v>
       </c>
       <c r="E5">
-        <v>3.0440925414201175e-06</v>
+        <v>-1.476177515725085e-07</v>
       </c>
       <c r="F5">
-        <v>0.11090863563757386</v>
+        <v>0.1137120480760489</v>
       </c>
       <c r="G5">
-        <v>0.070991138447904223</v>
+        <v>0.073816088431366056</v>
       </c>
       <c r="H5">
-        <v>0.07091228232359098</v>
+        <v>0.073752532878685384</v>
       </c>
       <c r="I5">
-        <v>0.07088579238361431</v>
+        <v>0.073739801996409837</v>
       </c>
       <c r="J5">
-        <v>0.00033937413316854036</v>
+        <v>0.00047153055298986002</v>
       </c>
       <c r="K5">
-        <v>-0.00063051999708914341</v>
+        <v>-0.00058709345582229344</v>
       </c>
       <c r="L5">
-        <v>9.7337037995151587e-05</v>
+        <v>1.8687708581544005e-05</v>
       </c>
       <c r="M5">
-        <v>-0.00057109175587347419</v>
+        <v>-0.00056113107343192317</v>
       </c>
       <c r="N5">
-        <v>0.00036570032321804613</v>
+        <v>0.00044863154837154751</v>
       </c>
       <c r="O5">
-        <v>-0.00090412420021965256</v>
+        <v>-0.00075063624897117598</v>
       </c>
       <c r="P5">
-        <v>-0.0011370334412190777</v>
+        <v>-0.0009224012771246598</v>
       </c>
       <c r="Q5">
-        <v>-0.0013232822363664666</v>
+        <v>-0.0010067693676782813</v>
       </c>
       <c r="R5">
-        <v>-0.00095340245750266672</v>
+        <v>-0.00061280762155325325</v>
       </c>
       <c r="S5">
-        <v>-0.00090716218822905342</v>
+        <v>-0.00065226358562266162</v>
       </c>
       <c r="T5">
-        <v>6.7708413812345159e-05</v>
+        <v>0.00014740188177680969</v>
       </c>
       <c r="U5">
-        <v>0.0005884381129871788</v>
+        <v>-0.00054181993430536812</v>
       </c>
       <c r="V5">
-        <v>6.8978488783139752e-05</v>
+        <v>-0.00035002149950409331</v>
       </c>
       <c r="W5">
-        <v>-0.00043960912064326674</v>
+        <v>-7.288933469420944e-05</v>
       </c>
       <c r="X5">
-        <v>-0.00019561891786943827</v>
+        <v>-0.00040337413821841563</v>
       </c>
       <c r="Y5">
-        <v>-8.9249421394238526e-05</v>
+        <v>0.00039030047980599669</v>
       </c>
       <c r="Z5">
-        <v>-0.00078604493774756673</v>
+        <v>-0.00024653283224243539</v>
       </c>
       <c r="AA5">
-        <v>0.0002541317112012137</v>
+        <v>5.0894007085295137e-06</v>
       </c>
       <c r="AB5">
-        <v>-6.2917903985659773e-05</v>
+        <v>-0.00016985680028946959</v>
       </c>
       <c r="AC5">
-        <v>-6.4020514655219185e-08</v>
+        <v>-0.00020646414538039171</v>
       </c>
       <c r="AD5">
-        <v>-0.00026963384057465678</v>
+        <v>0.00016059287110052611</v>
       </c>
       <c r="AE5">
-        <v>-0.00030229303508072514</v>
+        <v>3.7846106246075539e-05</v>
       </c>
       <c r="AF5">
-        <v>5.1111423175653759e-05</v>
+        <v>0.00050141620480266547</v>
       </c>
       <c r="AG5">
-        <v>-5.3124251327252292e-05</v>
+        <v>-3.2885359750559062e-05</v>
       </c>
       <c r="AH5">
-        <v>0.00030951872868142938</v>
-      </c>
-      <c r="AI5">
-        <v>-0.00010427112488800572</v>
-      </c>
-      <c r="AJ5">
-        <v>-0.060133749086610844</v>
+        <v>-0.066803857654206128</v>
       </c>
     </row>
     <row r="6">
@@ -968,109 +932,103 @@
         <v>28</v>
       </c>
       <c r="B6">
-        <v>0.50179381713219884</v>
+        <v>0.49466873786825449</v>
       </c>
       <c r="C6">
-        <v>0.0069914406088493475</v>
+        <v>0.0070372230117672629</v>
       </c>
       <c r="D6">
-        <v>0.00037875841799748199</v>
+        <v>0.00037627105366754357</v>
       </c>
       <c r="E6">
-        <v>-4.8806396285952004e-06</v>
+        <v>-4.8791068988180905e-06</v>
       </c>
       <c r="F6">
-        <v>0.070991138447904223</v>
+        <v>0.073816088431366056</v>
       </c>
       <c r="G6">
-        <v>0.075658980542603005</v>
+        <v>0.078189830002223459</v>
       </c>
       <c r="H6">
-        <v>0.071252633349476957</v>
+        <v>0.074007018613351683</v>
       </c>
       <c r="I6">
-        <v>0.07131270814220203</v>
+        <v>0.074070743660965666</v>
       </c>
       <c r="J6">
-        <v>0.00066850949550915223</v>
+        <v>0.00087294479942255643</v>
       </c>
       <c r="K6">
-        <v>4.6905579984810042e-05</v>
+        <v>-0.00019970369904198648</v>
       </c>
       <c r="L6">
-        <v>-0.00025743881702642441</v>
+        <v>-0.00026694467024333812</v>
       </c>
       <c r="M6">
-        <v>-0.00076439992084379946</v>
+        <v>-0.0010168787682814998</v>
       </c>
       <c r="N6">
-        <v>-0.00016569136548562347</v>
+        <v>6.8387609731421217e-05</v>
       </c>
       <c r="O6">
-        <v>-0.00048266061529286808</v>
+        <v>-0.00047822579272507881</v>
       </c>
       <c r="P6">
-        <v>-0.00046196326867928988</v>
+        <v>-0.00046168686353936783</v>
       </c>
       <c r="Q6">
-        <v>-0.00030498902773365422</v>
+        <v>-0.00029449436082797792</v>
       </c>
       <c r="R6">
-        <v>-0.00037504183842230338</v>
+        <v>-0.00035158522699709448</v>
       </c>
       <c r="S6">
-        <v>-0.00045033030282543019</v>
+        <v>-0.00044961197391116953</v>
       </c>
       <c r="T6">
-        <v>-0.00031849112729133433</v>
+        <v>-0.0002535610447800124</v>
       </c>
       <c r="U6">
-        <v>8.3216341128927729e-05</v>
+        <v>-1.6506347765281315e-05</v>
       </c>
       <c r="V6">
-        <v>0.00012280573773625764</v>
+        <v>-0.00017533811831396337</v>
       </c>
       <c r="W6">
-        <v>-1.9161969688527569e-05</v>
+        <v>5.1181453009620237e-05</v>
       </c>
       <c r="X6">
-        <v>-0.00015887896411250629</v>
+        <v>1.760223585040889e-05</v>
       </c>
       <c r="Y6">
-        <v>3.0230494891259063e-06</v>
+        <v>0.00012808414841085358</v>
       </c>
       <c r="Z6">
-        <v>-3.9762688375737099e-05</v>
+        <v>-0.00014244457499099084</v>
       </c>
       <c r="AA6">
-        <v>8.5140332353350612e-05</v>
+        <v>4.5053079514084313e-06</v>
       </c>
       <c r="AB6">
-        <v>-4.8323662136001699e-05</v>
+        <v>0.00015642228619150433</v>
       </c>
       <c r="AC6">
-        <v>1.0138052308726608e-06</v>
+        <v>-0.00035385824700989721</v>
       </c>
       <c r="AD6">
-        <v>-2.722479090172536e-05</v>
+        <v>-0.0001434442593716001</v>
       </c>
       <c r="AE6">
-        <v>-0.00050747929637179334</v>
+        <v>-0.00031391930185736827</v>
       </c>
       <c r="AF6">
-        <v>-0.00028813322742500536</v>
+        <v>-0.0002725646996366432</v>
       </c>
       <c r="AG6">
-        <v>-0.00052548304366584198</v>
+        <v>-0.00044103218366124686</v>
       </c>
       <c r="AH6">
-        <v>-0.0004638058761665953</v>
-      </c>
-      <c r="AI6">
-        <v>-0.00073041362526063414</v>
-      </c>
-      <c r="AJ6">
-        <v>-0.077140312484265283</v>
+        <v>-0.081315943267908489</v>
       </c>
     </row>
     <row r="7">
@@ -1078,109 +1036,103 @@
         <v>29</v>
       </c>
       <c r="B7">
-        <v>0.79271785610069712</v>
+        <v>0.76982149703512892</v>
       </c>
       <c r="C7">
-        <v>0.0053225052952228513</v>
+        <v>0.0055955751826003153</v>
       </c>
       <c r="D7">
-        <v>0.00019802447148850773</v>
+        <v>0.00016966903073059245</v>
       </c>
       <c r="E7">
-        <v>-2.3491670395210911e-06</v>
+        <v>-1.9577859405120208e-06</v>
       </c>
       <c r="F7">
-        <v>0.07091228232359098</v>
+        <v>0.073752532878685384</v>
       </c>
       <c r="G7">
-        <v>0.071252633349476957</v>
+        <v>0.074007018613351683</v>
       </c>
       <c r="H7">
-        <v>0.071708815946861126</v>
+        <v>0.074383249416556274</v>
       </c>
       <c r="I7">
-        <v>0.071362761722253198</v>
+        <v>0.074048607958348223</v>
       </c>
       <c r="J7">
-        <v>0.00048336547520136733</v>
+        <v>0.00053073019334343857</v>
       </c>
       <c r="K7">
-        <v>-0.00036510867326244867</v>
+        <v>-0.00039322299598373856</v>
       </c>
       <c r="L7">
-        <v>-0.00020253263807616662</v>
+        <v>-0.00022126026738042426</v>
       </c>
       <c r="M7">
-        <v>-0.00056979834011672628</v>
+        <v>-0.00067777479173240958</v>
       </c>
       <c r="N7">
-        <v>0.00022825039166399219</v>
+        <v>0.00021653034063069676</v>
       </c>
       <c r="O7">
-        <v>-0.000874177638921253</v>
+        <v>-0.00085014673877412128</v>
       </c>
       <c r="P7">
-        <v>-0.00013551497840506854</v>
+        <v>-9.40152410778064e-05</v>
       </c>
       <c r="Q7">
-        <v>-0.0002990901207749197</v>
+        <v>-0.0002480864861333712</v>
       </c>
       <c r="R7">
-        <v>-0.00029724317080510702</v>
+        <v>-0.00022617083880805723</v>
       </c>
       <c r="S7">
-        <v>-0.00033049685513933391</v>
+        <v>-0.00030574732097374963</v>
       </c>
       <c r="T7">
-        <v>-0.00029751787683207631</v>
+        <v>-0.00034865526472820096</v>
       </c>
       <c r="U7">
-        <v>-0.00013730376260434607</v>
+        <v>0.00016552346490639885</v>
       </c>
       <c r="V7">
-        <v>-0.00016360283807634671</v>
+        <v>-7.2718959757588769e-05</v>
       </c>
       <c r="W7">
-        <v>0.00013719780070220455</v>
+        <v>3.1917768038736139e-05</v>
       </c>
       <c r="X7">
-        <v>-1.7749614095067395e-05</v>
+        <v>-7.7138937322421969e-06</v>
       </c>
       <c r="Y7">
-        <v>-1.2587281779413706e-05</v>
+        <v>0.00024824168129392032</v>
       </c>
       <c r="Z7">
-        <v>-2.5785282258307396e-05</v>
+        <v>-0.00014225977216264507</v>
       </c>
       <c r="AA7">
-        <v>0.00032559139890397937</v>
+        <v>4.5684027597360857e-06</v>
       </c>
       <c r="AB7">
-        <v>-8.9351585151747903e-05</v>
+        <v>-0.00039945909693223092</v>
       </c>
       <c r="AC7">
-        <v>2.2603731803256394e-06</v>
+        <v>-0.00056135869398860061</v>
       </c>
       <c r="AD7">
-        <v>-0.0005194671027988762</v>
+        <v>-0.00020238311732408143</v>
       </c>
       <c r="AE7">
-        <v>-0.00065521853583794254</v>
+        <v>-0.00038064674756468908</v>
       </c>
       <c r="AF7">
-        <v>-0.00030694086771507201</v>
+        <v>-0.00030069489764898705</v>
       </c>
       <c r="AG7">
-        <v>-0.00049800624425511142</v>
+        <v>-0.00046515734126634234</v>
       </c>
       <c r="AH7">
-        <v>-0.00039600732195300969</v>
-      </c>
-      <c r="AI7">
-        <v>-0.00060407156948102947</v>
-      </c>
-      <c r="AJ7">
-        <v>-0.073182202790631645</v>
+        <v>-0.077015019093668188</v>
       </c>
     </row>
     <row r="8">
@@ -1188,109 +1140,103 @@
         <v>30</v>
       </c>
       <c r="B8">
-        <v>0.87029489645335634</v>
+        <v>0.83673416868466455</v>
       </c>
       <c r="C8">
-        <v>0.0066617728859940939</v>
+        <v>0.0069613367122043912</v>
       </c>
       <c r="D8">
-        <v>0.00035183995322166616</v>
+        <v>0.00031388780937911809</v>
       </c>
       <c r="E8">
-        <v>-4.3174216617076317e-06</v>
+        <v>-3.794789556816247e-06</v>
       </c>
       <c r="F8">
-        <v>0.07088579238361431</v>
+        <v>0.073739801996409837</v>
       </c>
       <c r="G8">
-        <v>0.07131270814220203</v>
+        <v>0.074070743660965666</v>
       </c>
       <c r="H8">
-        <v>0.071362761722253198</v>
+        <v>0.074048607958348223</v>
       </c>
       <c r="I8">
-        <v>0.072459843746936259</v>
+        <v>0.075088960667005045</v>
       </c>
       <c r="J8">
-        <v>0.00048444045465258386</v>
+        <v>0.00053428434696183719</v>
       </c>
       <c r="K8">
-        <v>-0.00038324045358537062</v>
+        <v>-0.00040150124548346544</v>
       </c>
       <c r="L8">
-        <v>-0.00028134456924309298</v>
+        <v>-0.00030233716036841274</v>
       </c>
       <c r="M8">
-        <v>-0.00056589372103480959</v>
+        <v>-0.00067915522606669387</v>
       </c>
       <c r="N8">
-        <v>0.00018671209149849488</v>
+        <v>0.00016021322643307301</v>
       </c>
       <c r="O8">
-        <v>0.00061533691292992021</v>
+        <v>0.0005386296324965123</v>
       </c>
       <c r="P8">
-        <v>-6.7238298140141761e-05</v>
+        <v>-8.5219825710396852e-05</v>
       </c>
       <c r="Q8">
-        <v>-0.00016598741552827784</v>
+        <v>-0.00017881218341874589</v>
       </c>
       <c r="R8">
-        <v>-0.00025988306405460779</v>
+        <v>-0.00022591628028095258</v>
       </c>
       <c r="S8">
-        <v>-0.00025563365540589092</v>
+        <v>-0.00027772011095257565</v>
       </c>
       <c r="T8">
-        <v>-0.00032930967045939619</v>
+        <v>-0.00040632050575220569</v>
       </c>
       <c r="U8">
-        <v>-0.00016425396908717471</v>
+        <v>0.00026829459605286904</v>
       </c>
       <c r="V8">
-        <v>-0.0001847887030670646</v>
+        <v>-0.00022172028224845541</v>
       </c>
       <c r="W8">
-        <v>0.00025257432929338963</v>
+        <v>-1.7059418973709717e-05</v>
       </c>
       <c r="X8">
-        <v>-0.00015263677111317792</v>
+        <v>-0.00012350942431211057</v>
       </c>
       <c r="Y8">
-        <v>-5.8344592110820548e-05</v>
+        <v>0.00023830031689303644</v>
       </c>
       <c r="Z8">
-        <v>-0.00016863984768275553</v>
+        <v>6.6528737997784138e-06</v>
       </c>
       <c r="AA8">
-        <v>0.000337733709171395</v>
+        <v>-2.6375933213137331e-07</v>
       </c>
       <c r="AB8">
-        <v>7.1281580288184987e-05</v>
+        <v>-0.00037047491392783183</v>
       </c>
       <c r="AC8">
-        <v>-2.7577286006042617e-06</v>
+        <v>-0.00064345674696386634</v>
       </c>
       <c r="AD8">
-        <v>-0.00042836153031172719</v>
+        <v>-0.00033534205427362962</v>
       </c>
       <c r="AE8">
-        <v>-0.00068299009515571108</v>
+        <v>-0.00044380178766392775</v>
       </c>
       <c r="AF8">
-        <v>-0.00036555191390709452</v>
+        <v>-0.00038006335863416396</v>
       </c>
       <c r="AG8">
-        <v>-0.00051092846576128448</v>
+        <v>-0.00063210773196284431</v>
       </c>
       <c r="AH8">
-        <v>-0.00040214909048520708</v>
-      </c>
-      <c r="AI8">
-        <v>-0.00072643168811993564</v>
-      </c>
-      <c r="AJ8">
-        <v>-0.075567392646664261</v>
+        <v>-0.07882314570701289</v>
       </c>
     </row>
     <row r="9">
@@ -1298,109 +1244,103 @@
         <v>31</v>
       </c>
       <c r="B9">
-        <v>-1.2288194217681772</v>
+        <v>-1.2007530021167976</v>
       </c>
       <c r="C9">
-        <v>0.0068401309091116634</v>
+        <v>0.0081873427953190747</v>
       </c>
       <c r="D9">
-        <v>0.0004770352383460663</v>
+        <v>0.00059692610060718254</v>
       </c>
       <c r="E9">
-        <v>-5.755835934742876e-06</v>
+        <v>-7.4783443527048237e-06</v>
       </c>
       <c r="F9">
-        <v>0.00033937413316854036</v>
+        <v>0.00047153055298986002</v>
       </c>
       <c r="G9">
-        <v>0.00066850949550915223</v>
+        <v>0.00087294479942255643</v>
       </c>
       <c r="H9">
-        <v>0.00048336547520136733</v>
+        <v>0.00053073019334343857</v>
       </c>
       <c r="I9">
-        <v>0.00048444045465258386</v>
+        <v>0.00053428434696183719</v>
       </c>
       <c r="J9">
-        <v>0.01826703213828787</v>
+        <v>0.018484500737695139</v>
       </c>
       <c r="K9">
-        <v>-0.015322354560187542</v>
+        <v>-0.015356059445280675</v>
       </c>
       <c r="L9">
-        <v>-0.00020147815729475724</v>
+        <v>-0.00024745921634344284</v>
       </c>
       <c r="M9">
-        <v>-0.018358693628204966</v>
+        <v>-0.018585028969250191</v>
       </c>
       <c r="N9">
-        <v>0.015490124812957137</v>
+        <v>0.01548096740582834</v>
       </c>
       <c r="O9">
-        <v>0.00016721877051585664</v>
+        <v>0.00015341306705425779</v>
       </c>
       <c r="P9">
-        <v>-0.00025645949140334901</v>
+        <v>-0.0002700123608154703</v>
       </c>
       <c r="Q9">
-        <v>-0.00024036252563609069</v>
+        <v>-0.00026988983317084893</v>
       </c>
       <c r="R9">
-        <v>6.2522710901730368e-05</v>
+        <v>-2.6897258711414064e-06</v>
       </c>
       <c r="S9">
-        <v>-0.0001319750251310505</v>
+        <v>-0.00020643929048007933</v>
       </c>
       <c r="T9">
-        <v>0.00027584060762993363</v>
+        <v>0.0003197952623685699</v>
       </c>
       <c r="U9">
-        <v>7.7532943543886525e-05</v>
+        <v>0.00039958594920104669</v>
       </c>
       <c r="V9">
-        <v>0.00015610081180726291</v>
+        <v>-1.0699832103621115e-05</v>
       </c>
       <c r="W9">
-        <v>0.00040864141282163187</v>
+        <v>0.00016463975174063692</v>
       </c>
       <c r="X9">
-        <v>5.8354328227125781e-05</v>
+        <v>-0.00049755465146504867</v>
       </c>
       <c r="Y9">
-        <v>0.00020320250088897319</v>
+        <v>-9.3601637833949951e-05</v>
       </c>
       <c r="Z9">
-        <v>-0.00042162893040731755</v>
+        <v>-0.00034397062036804326</v>
       </c>
       <c r="AA9">
-        <v>-5.1104846317391985e-05</v>
+        <v>1.2876648775586087e-05</v>
       </c>
       <c r="AB9">
-        <v>-0.00044264654520438434</v>
+        <v>0.00071217792923998057</v>
       </c>
       <c r="AC9">
-        <v>1.6187036676253573e-05</v>
+        <v>0.00042754744375868466</v>
       </c>
       <c r="AD9">
-        <v>0.00071167103031875151</v>
+        <v>0.00045020322097369847</v>
       </c>
       <c r="AE9">
-        <v>0.0002955191502173873</v>
+        <v>0.00047232607958509493</v>
       </c>
       <c r="AF9">
-        <v>0.00043743257823449259</v>
+        <v>0.00073926803091974643</v>
       </c>
       <c r="AG9">
-        <v>0.00046058125842611715</v>
+        <v>0.00032035556746418982</v>
       </c>
       <c r="AH9">
-        <v>0.00070204836502050323</v>
-      </c>
-      <c r="AI9">
-        <v>0.00032291640328157949</v>
-      </c>
-      <c r="AJ9">
-        <v>-0.016078198363168674</v>
+        <v>-0.017282586500260946</v>
       </c>
     </row>
     <row r="10">
@@ -1408,109 +1348,103 @@
         <v>32</v>
       </c>
       <c r="B10">
-        <v>0.1053999587401252</v>
+        <v>0.11373841313657995</v>
       </c>
       <c r="C10">
-        <v>-0.0044960599519654615</v>
+        <v>-0.005623703683514808</v>
       </c>
       <c r="D10">
-        <v>2.8523648163845863e-05</v>
+        <v>1.2814391383489734e-05</v>
       </c>
       <c r="E10">
-        <v>-3.2318630677959114e-07</v>
+        <v>-1.8246526846221842e-07</v>
       </c>
       <c r="F10">
-        <v>-0.00063051999708914341</v>
+        <v>-0.00058709345582229344</v>
       </c>
       <c r="G10">
-        <v>4.6905579984810042e-05</v>
+        <v>-0.00019970369904198648</v>
       </c>
       <c r="H10">
-        <v>-0.00036510867326244867</v>
+        <v>-0.00039322299598373856</v>
       </c>
       <c r="I10">
-        <v>-0.00038324045358537062</v>
+        <v>-0.00040150124548346544</v>
       </c>
       <c r="J10">
-        <v>-0.015322354560187542</v>
+        <v>-0.015356059445280675</v>
       </c>
       <c r="K10">
-        <v>0.016142930743019788</v>
+        <v>0.01614152893405332</v>
       </c>
       <c r="L10">
-        <v>0.00023917861658259267</v>
+        <v>0.00028926941740979676</v>
       </c>
       <c r="M10">
-        <v>0.015487012597818088</v>
+        <v>0.015500879815222596</v>
       </c>
       <c r="N10">
-        <v>-0.015728458695750677</v>
+        <v>-0.015683039936050736</v>
       </c>
       <c r="O10">
-        <v>1.2557975438453272e-05</v>
+        <v>4.1993163565438039e-05</v>
       </c>
       <c r="P10">
-        <v>0.00059879255969465424</v>
+        <v>0.00061910645648015968</v>
       </c>
       <c r="Q10">
-        <v>0.00084987130572135945</v>
+        <v>0.00067716339737253889</v>
       </c>
       <c r="R10">
-        <v>0.00091244289669354241</v>
+        <v>0.00080641431037031873</v>
       </c>
       <c r="S10">
-        <v>0.0012465220329281651</v>
+        <v>0.0011646863593019877</v>
       </c>
       <c r="T10">
-        <v>0.00044434752343775667</v>
+        <v>0.000671918289173603</v>
       </c>
       <c r="U10">
-        <v>0.0007299781743081771</v>
+        <v>-3.2528764713343387e-05</v>
       </c>
       <c r="V10">
-        <v>8.4228112378104903e-05</v>
+        <v>-0.00022016163600234779</v>
       </c>
       <c r="W10">
-        <v>-7.4718561288690018e-05</v>
+        <v>2.8857038316151438e-05</v>
       </c>
       <c r="X10">
-        <v>-0.00026887173349688135</v>
+        <v>0.00014915694226671431</v>
       </c>
       <c r="Y10">
-        <v>-5.2089042598708478e-06</v>
+        <v>0.00029254062206767806</v>
       </c>
       <c r="Z10">
-        <v>0.00015690793646992561</v>
+        <v>0.0001388385125533476</v>
       </c>
       <c r="AA10">
-        <v>0.00025335319509769689</v>
+        <v>-3.3684937474843812e-06</v>
       </c>
       <c r="AB10">
-        <v>0.00021272869895610613</v>
+        <v>-0.00038290470487288737</v>
       </c>
       <c r="AC10">
-        <v>-5.9608906500921002e-06</v>
+        <v>-0.00036366230063441564</v>
       </c>
       <c r="AD10">
-        <v>-0.0004843125908789755</v>
+        <v>-0.00043116836859690972</v>
       </c>
       <c r="AE10">
-        <v>-0.0003101845513583145</v>
+        <v>-0.00044958721832681777</v>
       </c>
       <c r="AF10">
-        <v>-0.00050411556076881427</v>
+        <v>-0.00060058465149667284</v>
       </c>
       <c r="AG10">
-        <v>-0.00055116890330128305</v>
+        <v>-0.00038123149768843956</v>
       </c>
       <c r="AH10">
-        <v>-0.00068720238313065441</v>
-      </c>
-      <c r="AI10">
-        <v>-0.00047989350412604924</v>
-      </c>
-      <c r="AJ10">
-        <v>-0.0029590583490347162</v>
+        <v>-0.0035227861346936707</v>
       </c>
     </row>
     <row r="11">
@@ -1518,109 +1452,103 @@
         <v>33</v>
       </c>
       <c r="B11">
-        <v>-0.39439438984358721</v>
+        <v>-0.40529698439786377</v>
       </c>
       <c r="C11">
-        <v>-0.12910664187354523</v>
+        <v>-0.13776945365271934</v>
       </c>
       <c r="D11">
-        <v>-0.00060590155380684484</v>
+        <v>-0.00059934166357366518</v>
       </c>
       <c r="E11">
-        <v>8.0168792119224057e-06</v>
+        <v>7.9920377602192855e-06</v>
       </c>
       <c r="F11">
-        <v>9.7337037995151587e-05</v>
+        <v>1.8687708581544005e-05</v>
       </c>
       <c r="G11">
-        <v>-0.00025743881702642441</v>
+        <v>-0.00026694467024333812</v>
       </c>
       <c r="H11">
-        <v>-0.00020253263807616662</v>
+        <v>-0.00022126026738042426</v>
       </c>
       <c r="I11">
-        <v>-0.00028134456924309298</v>
+        <v>-0.00030233716036841274</v>
       </c>
       <c r="J11">
-        <v>-0.00020147815729475724</v>
+        <v>-0.00024745921634344284</v>
       </c>
       <c r="K11">
-        <v>0.00023917861658259267</v>
+        <v>0.00028926941740979676</v>
       </c>
       <c r="L11">
-        <v>0.004466257423477323</v>
+        <v>0.0048132177331745157</v>
       </c>
       <c r="M11">
-        <v>0.01930338745606433</v>
+        <v>0.0204893661481069</v>
       </c>
       <c r="N11">
-        <v>0.02270165458918429</v>
+        <v>0.024061627407633388</v>
       </c>
       <c r="O11">
-        <v>0.010925551780011766</v>
+        <v>0.011957810851731377</v>
       </c>
       <c r="P11">
-        <v>-0.00029330910579033987</v>
+        <v>-0.0002669615893025657</v>
       </c>
       <c r="Q11">
-        <v>0.00050280877392754964</v>
+        <v>0.00045026670964361715</v>
       </c>
       <c r="R11">
-        <v>0.00066389538491095224</v>
+        <v>0.00062556194882018698</v>
       </c>
       <c r="S11">
-        <v>0.00086106661336901613</v>
+        <v>0.00081748089917405215</v>
       </c>
       <c r="T11">
-        <v>0.00063214033868301978</v>
+        <v>0.00059841394189035467</v>
       </c>
       <c r="U11">
-        <v>0.00064658426680226384</v>
+        <v>-2.5109934548148008e-05</v>
       </c>
       <c r="V11">
-        <v>-0.00021087268036293675</v>
+        <v>4.9402463920403868e-05</v>
       </c>
       <c r="W11">
-        <v>-3.4955021206470316e-05</v>
+        <v>-5.7827679329410528e-05</v>
       </c>
       <c r="X11">
-        <v>7.4104563116129593e-05</v>
+        <v>0.00068284151337025777</v>
       </c>
       <c r="Y11">
-        <v>-5.8032315052613083e-05</v>
+        <v>0.00024736821519593028</v>
       </c>
       <c r="Z11">
-        <v>0.00081496363643340482</v>
+        <v>-3.2931098875439019e-05</v>
       </c>
       <c r="AA11">
-        <v>0.00028145696276422947</v>
+        <v>-5.0427762742627762e-08</v>
       </c>
       <c r="AB11">
-        <v>-3.8646629756339777e-05</v>
+        <v>-0.00045901793920607656</v>
       </c>
       <c r="AC11">
-        <v>9.1034956044077709e-08</v>
+        <v>-0.00037471524716061518</v>
       </c>
       <c r="AD11">
-        <v>-0.00048968528688025491</v>
+        <v>-0.00043930252443734503</v>
       </c>
       <c r="AE11">
-        <v>-0.00038332998564618616</v>
+        <v>-0.00044318730877031948</v>
       </c>
       <c r="AF11">
-        <v>-0.00050383865992559848</v>
+        <v>-0.00046133025096959865</v>
       </c>
       <c r="AG11">
-        <v>-0.00047085365539634855</v>
+        <v>-0.00034128993823598179</v>
       </c>
       <c r="AH11">
-        <v>-0.00048319697802431711</v>
-      </c>
-      <c r="AI11">
-        <v>-0.00039388708121651864</v>
-      </c>
-      <c r="AJ11">
-        <v>0.013623117641510661</v>
+        <v>0.013377150530292106</v>
       </c>
     </row>
     <row r="12">
@@ -1628,109 +1556,103 @@
         <v>34</v>
       </c>
       <c r="B12">
-        <v>-0.42703433964403537</v>
+        <v>-0.46222318976341254</v>
       </c>
       <c r="C12">
-        <v>-0.67873172975765528</v>
+        <v>-0.70802261938217781</v>
       </c>
       <c r="D12">
-        <v>-0.00066020688256818356</v>
+        <v>-0.00077892522074326034</v>
       </c>
       <c r="E12">
-        <v>8.1691724576419637e-06</v>
+        <v>9.9024742619407234e-06</v>
       </c>
       <c r="F12">
-        <v>-0.00057109175587347419</v>
+        <v>-0.00056113107343192317</v>
       </c>
       <c r="G12">
-        <v>-0.00076439992084379946</v>
+        <v>-0.0010168787682814998</v>
       </c>
       <c r="H12">
-        <v>-0.00056979834011672628</v>
+        <v>-0.00067777479173240958</v>
       </c>
       <c r="I12">
-        <v>-0.00056589372103480959</v>
+        <v>-0.00067915522606669387</v>
       </c>
       <c r="J12">
-        <v>-0.018358693628204966</v>
+        <v>-0.018585028969250191</v>
       </c>
       <c r="K12">
-        <v>0.015487012597818088</v>
+        <v>0.015500879815222596</v>
       </c>
       <c r="L12">
-        <v>0.01930338745606433</v>
+        <v>0.0204893661481069</v>
       </c>
       <c r="M12">
-        <v>0.32072921119788811</v>
+        <v>0.33153175478886449</v>
       </c>
       <c r="N12">
-        <v>-0.0039080193918140885</v>
+        <v>-0.0080964982751700332</v>
       </c>
       <c r="O12">
-        <v>0.084623594331150673</v>
+        <v>0.086632172158913279</v>
       </c>
       <c r="P12">
-        <v>0.00010427264004039295</v>
+        <v>5.9711410707092736e-05</v>
       </c>
       <c r="Q12">
-        <v>0.00087249091734782505</v>
+        <v>0.0007494912900460574</v>
       </c>
       <c r="R12">
-        <v>0.00092592678077957195</v>
+        <v>0.00085201157484591269</v>
       </c>
       <c r="S12">
-        <v>0.0010688269352444844</v>
+        <v>0.0010122215124289684</v>
       </c>
       <c r="T12">
-        <v>-9.3899970209110686e-05</v>
+        <v>-0.00011383305119957304</v>
       </c>
       <c r="U12">
-        <v>0.00021857877783650536</v>
+        <v>-0.00039373726660202682</v>
       </c>
       <c r="V12">
-        <v>-0.00026539830497367828</v>
+        <v>4.4094374917571545e-05</v>
       </c>
       <c r="W12">
-        <v>-0.00039125422590610692</v>
+        <v>-0.00063684432807057734</v>
       </c>
       <c r="X12">
-        <v>2.2294010395177517e-06</v>
+        <v>0.0013885124989095948</v>
       </c>
       <c r="Y12">
-        <v>-0.00068362442644818999</v>
+        <v>0.00043248833804055125</v>
       </c>
       <c r="Z12">
-        <v>0.0014404235926219118</v>
+        <v>0.00046609412638059025</v>
       </c>
       <c r="AA12">
-        <v>0.00043404234164555553</v>
+        <v>-2.4323467485028259e-05</v>
       </c>
       <c r="AB12">
-        <v>0.00055623889438208632</v>
+        <v>-0.0026261055655612282</v>
       </c>
       <c r="AC12">
-        <v>-2.7567916788975833e-05</v>
+        <v>-0.0022925870260025426</v>
       </c>
       <c r="AD12">
-        <v>-0.0027267800837532923</v>
+        <v>-0.0025008868883404445</v>
       </c>
       <c r="AE12">
-        <v>-0.0022728772854662006</v>
+        <v>-0.0024839548410837669</v>
       </c>
       <c r="AF12">
-        <v>-0.0026334675305861605</v>
+        <v>-0.0026004388808535612</v>
       </c>
       <c r="AG12">
-        <v>-0.0025787895997136084</v>
+        <v>-0.0018835830334096022</v>
       </c>
       <c r="AH12">
-        <v>-0.0026695457881824917</v>
-      </c>
-      <c r="AI12">
-        <v>-0.0020049185779722851</v>
-      </c>
-      <c r="AJ12">
-        <v>0.040768146586417725</v>
+        <v>0.041559630461348647</v>
       </c>
     </row>
     <row r="13">
@@ -1738,109 +1660,103 @@
         <v>35</v>
       </c>
       <c r="B13">
-        <v>-2.0375665761706494</v>
+        <v>-2.0661416857081361</v>
       </c>
       <c r="C13">
-        <v>-0.78093632353149845</v>
+        <v>-0.81500667558533579</v>
       </c>
       <c r="D13">
-        <v>-0.00019717856783842006</v>
+        <v>-0.00019355037209791738</v>
       </c>
       <c r="E13">
-        <v>2.3262631773805615e-06</v>
+        <v>2.407469524371442e-06</v>
       </c>
       <c r="F13">
-        <v>0.00036570032321804613</v>
+        <v>0.00044863154837154751</v>
       </c>
       <c r="G13">
-        <v>-0.00016569136548562347</v>
+        <v>6.8387609731421217e-05</v>
       </c>
       <c r="H13">
-        <v>0.00022825039166399219</v>
+        <v>0.00021653034063069676</v>
       </c>
       <c r="I13">
-        <v>0.00018671209149849488</v>
+        <v>0.00016021322643307301</v>
       </c>
       <c r="J13">
-        <v>0.015490124812957137</v>
+        <v>0.01548096740582834</v>
       </c>
       <c r="K13">
-        <v>-0.015728458695750677</v>
+        <v>-0.015683039936050736</v>
       </c>
       <c r="L13">
-        <v>0.02270165458918429</v>
+        <v>0.024061627407633388</v>
       </c>
       <c r="M13">
-        <v>-0.0039080193918140885</v>
+        <v>-0.0080964982751700332</v>
       </c>
       <c r="N13">
-        <v>0.35907189827393537</v>
+        <v>0.37192797726591703</v>
       </c>
       <c r="O13">
-        <v>0.087468024927459046</v>
+        <v>0.090248017578671069</v>
       </c>
       <c r="P13">
-        <v>-0.0015907037189158693</v>
+        <v>-0.0016610287610983989</v>
       </c>
       <c r="Q13">
-        <v>0.00017763740548221412</v>
+        <v>0.0001348917078898078</v>
       </c>
       <c r="R13">
-        <v>0.00063089198112702323</v>
+        <v>0.00055317271094244814</v>
       </c>
       <c r="S13">
-        <v>0.0004309180960626224</v>
+        <v>0.00035283170207072519</v>
       </c>
       <c r="T13">
-        <v>0.00016979418664173074</v>
+        <v>-7.7464978296643092e-05</v>
       </c>
       <c r="U13">
-        <v>-0.00015313543304103011</v>
+        <v>-8.3716027038679194e-05</v>
       </c>
       <c r="V13">
-        <v>-0.0003581395822996519</v>
+        <v>0.00019735160002684588</v>
       </c>
       <c r="W13">
-        <v>-5.6167694535051629e-05</v>
+        <v>0.00022040829081193948</v>
       </c>
       <c r="X13">
-        <v>0.00028967592560371014</v>
+        <v>0.0012951845302396575</v>
       </c>
       <c r="Y13">
-        <v>0.00028383393650210421</v>
+        <v>0.00031341784529282236</v>
       </c>
       <c r="Z13">
-        <v>0.0014164015979874316</v>
+        <v>-0.00069389130621565296</v>
       </c>
       <c r="AA13">
-        <v>0.0004236524433265164</v>
+        <v>2.3320912100885529e-05</v>
       </c>
       <c r="AB13">
-        <v>-0.00082985883371058337</v>
+        <v>-0.0030487323976331306</v>
       </c>
       <c r="AC13">
-        <v>2.809492346334829e-05</v>
+        <v>-0.0026687566056822982</v>
       </c>
       <c r="AD13">
-        <v>-0.0032160436069721549</v>
+        <v>-0.0028726407174519582</v>
       </c>
       <c r="AE13">
-        <v>-0.0029662849096437887</v>
+        <v>-0.0025704174546667836</v>
       </c>
       <c r="AF13">
-        <v>-0.0030931317431023672</v>
+        <v>-0.0024578886165867041</v>
       </c>
       <c r="AG13">
-        <v>-0.0026919974458402222</v>
+        <v>-0.0022809657235777869</v>
       </c>
       <c r="AH13">
-        <v>-0.0026112751116294107</v>
-      </c>
-      <c r="AI13">
-        <v>-0.0024664750228936597</v>
-      </c>
-      <c r="AJ13">
-        <v>0.00059993195604187387</v>
+        <v>0.0020044561287994264</v>
       </c>
     </row>
     <row r="14">
@@ -1848,109 +1764,103 @@
         <v>36</v>
       </c>
       <c r="B14">
-        <v>-0.14259751298740955</v>
+        <v>-0.16101964864111301</v>
       </c>
       <c r="C14">
-        <v>-0.41699609051896836</v>
+        <v>-0.43968146212347875</v>
       </c>
       <c r="D14">
-        <v>0.00010327853045473748</v>
+        <v>9.4577824913589029e-05</v>
       </c>
       <c r="E14">
-        <v>-1.1290501425161248e-06</v>
+        <v>-1.0594273882335729e-06</v>
       </c>
       <c r="F14">
-        <v>-0.00090412420021965256</v>
+        <v>-0.00075063624897117598</v>
       </c>
       <c r="G14">
-        <v>-0.00048266061529286808</v>
+        <v>-0.00047822579272507881</v>
       </c>
       <c r="H14">
-        <v>-0.000874177638921253</v>
+        <v>-0.00085014673877412128</v>
       </c>
       <c r="I14">
-        <v>0.00061533691292992021</v>
+        <v>0.0005386296324965123</v>
       </c>
       <c r="J14">
-        <v>0.00016721877051585664</v>
+        <v>0.00015341306705425779</v>
       </c>
       <c r="K14">
-        <v>1.2557975438453272e-05</v>
+        <v>4.1993163565438039e-05</v>
       </c>
       <c r="L14">
-        <v>0.010925551780011766</v>
+        <v>0.011957810851731377</v>
       </c>
       <c r="M14">
-        <v>0.084623594331150673</v>
+        <v>0.086632172158913279</v>
       </c>
       <c r="N14">
-        <v>0.087468024927459046</v>
+        <v>0.090248017578671069</v>
       </c>
       <c r="O14">
-        <v>0.20670950888052622</v>
+        <v>0.204092017042798</v>
       </c>
       <c r="P14">
-        <v>-0.0045623256792363676</v>
+        <v>-0.0043655571044304824</v>
       </c>
       <c r="Q14">
-        <v>-0.0014310986859956227</v>
+        <v>-0.0014573927852922592</v>
       </c>
       <c r="R14">
-        <v>-0.0015205795057833492</v>
+        <v>-0.0014780224729584283</v>
       </c>
       <c r="S14">
-        <v>-0.0016614669860702488</v>
+        <v>-0.0015810291775500362</v>
       </c>
       <c r="T14">
-        <v>-0.00010614781652158278</v>
+        <v>-0.00010355399823213708</v>
       </c>
       <c r="U14">
-        <v>-0.00018504432776530262</v>
+        <v>-0.00011259433351014294</v>
       </c>
       <c r="V14">
-        <v>1.8281861557667423e-06</v>
+        <v>-3.8986565854266624e-05</v>
       </c>
       <c r="W14">
-        <v>-0.00015270748867635738</v>
+        <v>-0.00054900620048554093</v>
       </c>
       <c r="X14">
-        <v>-1.5004678771510509e-05</v>
+        <v>0.00015763718436880678</v>
       </c>
       <c r="Y14">
-        <v>-0.00056476726495756965</v>
+        <v>-0.00010149776819968841</v>
       </c>
       <c r="Z14">
-        <v>0.00016533698653648356</v>
+        <v>0.00098211573104755841</v>
       </c>
       <c r="AA14">
-        <v>-0.00010190239538112656</v>
+        <v>-3.957079417718528e-05</v>
       </c>
       <c r="AB14">
-        <v>0.0010368197386893077</v>
+        <v>0.0028812316361511957</v>
       </c>
       <c r="AC14">
-        <v>-4.1639116238285435e-05</v>
+        <v>0.0028976479202354813</v>
       </c>
       <c r="AD14">
-        <v>0.002879560547387707</v>
+        <v>0.0029700886040962141</v>
       </c>
       <c r="AE14">
-        <v>0.0028818244746878227</v>
+        <v>0.0029908182724913985</v>
       </c>
       <c r="AF14">
-        <v>0.0029994411987923036</v>
+        <v>0.0032815311479722285</v>
       </c>
       <c r="AG14">
-        <v>0.0030099481208004171</v>
+        <v>0.0037622027578707571</v>
       </c>
       <c r="AH14">
-        <v>0.0033101054896326402</v>
-      </c>
-      <c r="AI14">
-        <v>0.0038467197948812825</v>
-      </c>
-      <c r="AJ14">
-        <v>0.014009909190098795</v>
+        <v>0.013882268177981702</v>
       </c>
     </row>
     <row r="15">
@@ -1958,109 +1868,103 @@
         <v>37</v>
       </c>
       <c r="B15">
-        <v>-0.096489722387074789</v>
+        <v>-0.098627844075473134</v>
       </c>
       <c r="C15">
-        <v>0.009134840529856178</v>
+        <v>0.0084765769885288</v>
       </c>
       <c r="D15">
-        <v>-8.0230439460864545e-05</v>
+        <v>-0.00012089150507065731</v>
       </c>
       <c r="E15">
-        <v>1.0375098014718678e-06</v>
+        <v>1.4440561479496067e-06</v>
       </c>
       <c r="F15">
-        <v>-0.0011370334412190777</v>
+        <v>-0.0009224012771246598</v>
       </c>
       <c r="G15">
-        <v>-0.00046196326867928988</v>
+        <v>-0.00046168686353936783</v>
       </c>
       <c r="H15">
-        <v>-0.00013551497840506854</v>
+        <v>-9.40152410778064e-05</v>
       </c>
       <c r="I15">
-        <v>-6.7238298140141761e-05</v>
+        <v>-8.5219825710396852e-05</v>
       </c>
       <c r="J15">
-        <v>-0.00025645949140334901</v>
+        <v>-0.0002700123608154703</v>
       </c>
       <c r="K15">
-        <v>0.00059879255969465424</v>
+        <v>0.00061910645648015968</v>
       </c>
       <c r="L15">
-        <v>-0.00029330910579033987</v>
+        <v>-0.0002669615893025657</v>
       </c>
       <c r="M15">
-        <v>0.00010427264004039295</v>
+        <v>5.9711410707092736e-05</v>
       </c>
       <c r="N15">
-        <v>-0.0015907037189158693</v>
+        <v>-0.0016610287610983989</v>
       </c>
       <c r="O15">
-        <v>-0.0045623256792363676</v>
+        <v>-0.0043655571044304824</v>
       </c>
       <c r="P15">
-        <v>0.0095715622421395918</v>
+        <v>0.0092330890247496345</v>
       </c>
       <c r="Q15">
-        <v>0.0042179827040229392</v>
+        <v>0.0039945455025615674</v>
       </c>
       <c r="R15">
-        <v>0.0042767080761080632</v>
+        <v>0.0041043187402648989</v>
       </c>
       <c r="S15">
-        <v>0.0043785573649136956</v>
+        <v>0.0042384465031146011</v>
       </c>
       <c r="T15">
-        <v>0.00027163932199897149</v>
+        <v>0.00030345657268320719</v>
       </c>
       <c r="U15">
-        <v>-5.3730124025124252e-05</v>
+        <v>5.7049003498082509e-05</v>
       </c>
       <c r="V15">
-        <v>0.00019828021468279883</v>
+        <v>-0.00015536018623847544</v>
       </c>
       <c r="W15">
-        <v>4.4097899605850311e-05</v>
+        <v>0.0002391872459332381</v>
       </c>
       <c r="X15">
-        <v>-0.00017165198668459938</v>
+        <v>-0.0013242477547020738</v>
       </c>
       <c r="Y15">
-        <v>0.00027468526501003626</v>
+        <v>0.0002778455905319264</v>
       </c>
       <c r="Z15">
-        <v>-0.0012330503170501729</v>
+        <v>-0.00029568046823951833</v>
       </c>
       <c r="AA15">
-        <v>0.00029866345080838911</v>
+        <v>1.2590339189506892e-05</v>
       </c>
       <c r="AB15">
-        <v>-0.00033334425671132577</v>
+        <v>-0.00045968727641176703</v>
       </c>
       <c r="AC15">
-        <v>1.4322448704067536e-05</v>
+        <v>-0.00027179557375709134</v>
       </c>
       <c r="AD15">
-        <v>-0.00044987536369928095</v>
+        <v>0.00010598239263933545</v>
       </c>
       <c r="AE15">
-        <v>-0.00026898932976012358</v>
+        <v>-0.00032696943565104376</v>
       </c>
       <c r="AF15">
-        <v>0.00014406173637961735</v>
+        <v>-0.00022376872349403915</v>
       </c>
       <c r="AG15">
-        <v>-0.00028189896236239511</v>
+        <v>-0.00042818775307142533</v>
       </c>
       <c r="AH15">
-        <v>-0.00022195308815425895</v>
-      </c>
-      <c r="AI15">
-        <v>-0.00042738192690495026</v>
-      </c>
-      <c r="AJ15">
-        <v>-0.012054322743333104</v>
+        <v>-0.0097388546961620776</v>
       </c>
     </row>
     <row r="16">
@@ -2068,109 +1972,103 @@
         <v>38</v>
       </c>
       <c r="B16">
-        <v>-0.078037203077631678</v>
+        <v>-0.072529481304465598</v>
       </c>
       <c r="C16">
-        <v>-0.012497257666346708</v>
+        <v>-0.011069886630613254</v>
       </c>
       <c r="D16">
-        <v>-0.00030388784763747917</v>
+        <v>-0.00030291784111194701</v>
       </c>
       <c r="E16">
-        <v>4.3844932218281975e-06</v>
+        <v>4.2973774890061788e-06</v>
       </c>
       <c r="F16">
-        <v>-0.0013232822363664666</v>
+        <v>-0.0010067693676782813</v>
       </c>
       <c r="G16">
-        <v>-0.00030498902773365422</v>
+        <v>-0.00029449436082797792</v>
       </c>
       <c r="H16">
-        <v>-0.0002990901207749197</v>
+        <v>-0.0002480864861333712</v>
       </c>
       <c r="I16">
-        <v>-0.00016598741552827784</v>
+        <v>-0.00017881218341874589</v>
       </c>
       <c r="J16">
-        <v>-0.00024036252563609069</v>
+        <v>-0.00026988983317084893</v>
       </c>
       <c r="K16">
-        <v>0.00084987130572135945</v>
+        <v>0.00067716339737253889</v>
       </c>
       <c r="L16">
-        <v>0.00050280877392754964</v>
+        <v>0.00045026670964361715</v>
       </c>
       <c r="M16">
-        <v>0.00087249091734782505</v>
+        <v>0.0007494912900460574</v>
       </c>
       <c r="N16">
-        <v>0.00017763740548221412</v>
+        <v>0.0001348917078898078</v>
       </c>
       <c r="O16">
-        <v>-0.0014310986859956227</v>
+        <v>-0.0014573927852922592</v>
       </c>
       <c r="P16">
-        <v>0.0042179827040229392</v>
+        <v>0.0039945455025615674</v>
       </c>
       <c r="Q16">
-        <v>0.0066427545339064025</v>
+        <v>0.0061030034479267305</v>
       </c>
       <c r="R16">
-        <v>0.0054884559762355513</v>
+        <v>0.0050746002237723855</v>
       </c>
       <c r="S16">
-        <v>0.0056967766446109833</v>
+        <v>0.0052563819092102662</v>
       </c>
       <c r="T16">
-        <v>-0.00018358907131377949</v>
+        <v>-0.00019481431379309337</v>
       </c>
       <c r="U16">
-        <v>-0.00039805674930032772</v>
+        <v>0.00015076568477941364</v>
       </c>
       <c r="V16">
-        <v>0.00012506127557443988</v>
+        <v>-6.8920489185360931e-06</v>
       </c>
       <c r="W16">
-        <v>0.00020451535826646186</v>
+        <v>0.00018897522945516431</v>
       </c>
       <c r="X16">
-        <v>-9.2782878564031036e-06</v>
+        <v>0.0017745833846981121</v>
       </c>
       <c r="Y16">
-        <v>0.00020875287162149911</v>
+        <v>0.0012199917935633295</v>
       </c>
       <c r="Z16">
-        <v>0.0020889980527941578</v>
+        <v>-8.9841526956569752e-05</v>
       </c>
       <c r="AA16">
-        <v>0.0013545005116211185</v>
+        <v>5.548180136588563e-06</v>
       </c>
       <c r="AB16">
-        <v>-9.1039749237398476e-05</v>
+        <v>-0.00082262301103112282</v>
       </c>
       <c r="AC16">
-        <v>6.06305458166338e-06</v>
+        <v>-0.00052171459716753022</v>
       </c>
       <c r="AD16">
-        <v>-0.00095422260525676291</v>
+        <v>-0.00051830315264578643</v>
       </c>
       <c r="AE16">
-        <v>-0.00064572875638472778</v>
+        <v>-0.00061894244418916758</v>
       </c>
       <c r="AF16">
-        <v>-0.00065807909882752743</v>
+        <v>-0.00040826189063267627</v>
       </c>
       <c r="AG16">
-        <v>-0.00073458664625755351</v>
+        <v>-0.00069402566694274422</v>
       </c>
       <c r="AH16">
-        <v>-0.00052804773378511049</v>
-      </c>
-      <c r="AI16">
-        <v>-0.00090346517113689567</v>
-      </c>
-      <c r="AJ16">
-        <v>-0.0082232343440501853</v>
+        <v>-0.0069090507922383911</v>
       </c>
     </row>
     <row r="17">
@@ -2178,109 +2076,103 @@
         <v>39</v>
       </c>
       <c r="B17">
-        <v>-0.17138816476305416</v>
+        <v>-0.12070828633628659</v>
       </c>
       <c r="C17">
-        <v>-0.016531622865446738</v>
+        <v>-0.015397025111691727</v>
       </c>
       <c r="D17">
-        <v>-0.00030995834585633819</v>
+        <v>-0.00030019779147664799</v>
       </c>
       <c r="E17">
-        <v>4.3193194425701289e-06</v>
+        <v>4.0917380859755017e-06</v>
       </c>
       <c r="F17">
-        <v>-0.00095340245750266672</v>
+        <v>-0.00061280762155325325</v>
       </c>
       <c r="G17">
-        <v>-0.00037504183842230338</v>
+        <v>-0.00035158522699709448</v>
       </c>
       <c r="H17">
-        <v>-0.00029724317080510702</v>
+        <v>-0.00022617083880805723</v>
       </c>
       <c r="I17">
-        <v>-0.00025988306405460779</v>
+        <v>-0.00022591628028095258</v>
       </c>
       <c r="J17">
-        <v>6.2522710901730368e-05</v>
+        <v>-2.6897258711414064e-06</v>
       </c>
       <c r="K17">
-        <v>0.00091244289669354241</v>
+        <v>0.00080641431037031873</v>
       </c>
       <c r="L17">
-        <v>0.00066389538491095224</v>
+        <v>0.00062556194882018698</v>
       </c>
       <c r="M17">
-        <v>0.00092592678077957195</v>
+        <v>0.00085201157484591269</v>
       </c>
       <c r="N17">
-        <v>0.00063089198112702323</v>
+        <v>0.00055317271094244814</v>
       </c>
       <c r="O17">
-        <v>-0.0015205795057833492</v>
+        <v>-0.0014780224729584283</v>
       </c>
       <c r="P17">
-        <v>0.0042767080761080632</v>
+        <v>0.0041043187402648989</v>
       </c>
       <c r="Q17">
-        <v>0.0054884559762355513</v>
+        <v>0.0050746002237723855</v>
       </c>
       <c r="R17">
-        <v>0.0066259169428012927</v>
+        <v>0.0062780641590742207</v>
       </c>
       <c r="S17">
-        <v>0.0061152854490815704</v>
+        <v>0.0058134139874173596</v>
       </c>
       <c r="T17">
-        <v>7.4298031779859329e-05</v>
+        <v>8.5481272806033288e-05</v>
       </c>
       <c r="U17">
-        <v>-0.00017839259747063263</v>
+        <v>0.00026399524808004202</v>
       </c>
       <c r="V17">
-        <v>4.9928818852626324e-05</v>
+        <v>-0.00010209489416403326</v>
       </c>
       <c r="W17">
-        <v>0.00029139915720181344</v>
+        <v>0.00021477996882587257</v>
       </c>
       <c r="X17">
-        <v>-5.5637592460253786e-05</v>
+        <v>0.0022252737058726562</v>
       </c>
       <c r="Y17">
-        <v>0.00022468899698518369</v>
+        <v>0.0015051755863642541</v>
       </c>
       <c r="Z17">
-        <v>0.0024942953067278147</v>
+        <v>-0.00025178144410860641</v>
       </c>
       <c r="AA17">
-        <v>0.0015822343450867596</v>
+        <v>1.0730514432312281e-05</v>
       </c>
       <c r="AB17">
-        <v>-0.00030852253138595443</v>
+        <v>-0.00099854614404251045</v>
       </c>
       <c r="AC17">
-        <v>1.2459774472939184e-05</v>
+        <v>-0.00074853017251389343</v>
       </c>
       <c r="AD17">
-        <v>-0.0013242211544942004</v>
+        <v>-0.00075448217619428736</v>
       </c>
       <c r="AE17">
-        <v>-0.0010593619085024497</v>
+        <v>-0.00065051600171892911</v>
       </c>
       <c r="AF17">
-        <v>-0.0010565806993199794</v>
+        <v>-0.00059903924069017807</v>
       </c>
       <c r="AG17">
-        <v>-0.00094538972593384216</v>
+        <v>-0.00073408813033014569</v>
       </c>
       <c r="AH17">
-        <v>-0.00093948473387639757</v>
-      </c>
-      <c r="AI17">
-        <v>-0.0010926162612756923</v>
-      </c>
-      <c r="AJ17">
-        <v>-0.0069895405356792942</v>
+        <v>-0.00710939747701926</v>
       </c>
     </row>
     <row r="18">
@@ -2288,109 +2180,103 @@
         <v>40</v>
       </c>
       <c r="B18">
-        <v>0.0081702981228509337</v>
+        <v>0.069269632984197277</v>
       </c>
       <c r="C18">
-        <v>-0.021052870742490106</v>
+        <v>-0.019735211642398325</v>
       </c>
       <c r="D18">
-        <v>-0.00038970639162901912</v>
+        <v>-0.00035985426572260597</v>
       </c>
       <c r="E18">
-        <v>5.2133472251351553e-06</v>
+        <v>4.7051888651030374e-06</v>
       </c>
       <c r="F18">
-        <v>-0.00090716218822905342</v>
+        <v>-0.00065226358562266162</v>
       </c>
       <c r="G18">
-        <v>-0.00045033030282543019</v>
+        <v>-0.00044961197391116953</v>
       </c>
       <c r="H18">
-        <v>-0.00033049685513933391</v>
+        <v>-0.00030574732097374963</v>
       </c>
       <c r="I18">
-        <v>-0.00025563365540589092</v>
+        <v>-0.00027772011095257565</v>
       </c>
       <c r="J18">
-        <v>-0.0001319750251310505</v>
+        <v>-0.00020643929048007933</v>
       </c>
       <c r="K18">
-        <v>0.0012465220329281651</v>
+        <v>0.0011646863593019877</v>
       </c>
       <c r="L18">
-        <v>0.00086106661336901613</v>
+        <v>0.00081748089917405215</v>
       </c>
       <c r="M18">
-        <v>0.0010688269352444844</v>
+        <v>0.0010122215124289684</v>
       </c>
       <c r="N18">
-        <v>0.0004309180960626224</v>
+        <v>0.00035283170207072519</v>
       </c>
       <c r="O18">
-        <v>-0.0016614669860702488</v>
+        <v>-0.0015810291775500362</v>
       </c>
       <c r="P18">
-        <v>0.0043785573649136956</v>
+        <v>0.0042384465031146011</v>
       </c>
       <c r="Q18">
-        <v>0.0056967766446109833</v>
+        <v>0.0052563819092102662</v>
       </c>
       <c r="R18">
-        <v>0.0061152854490815704</v>
+        <v>0.0058134139874173596</v>
       </c>
       <c r="S18">
-        <v>0.0074479468105875541</v>
+        <v>0.0071378406029240461</v>
       </c>
       <c r="T18">
-        <v>0.00033198545501881909</v>
+        <v>0.00031764445824180611</v>
       </c>
       <c r="U18">
-        <v>5.62391154889445e-05</v>
+        <v>0.00026686805087693366</v>
       </c>
       <c r="V18">
-        <v>-3.4646826263611913e-06</v>
+        <v>-0.00052526018175554589</v>
       </c>
       <c r="W18">
-        <v>0.00030307597494647857</v>
+        <v>0.00026029838797028611</v>
       </c>
       <c r="X18">
-        <v>-0.00045639232404741061</v>
+        <v>0.0024278600141531899</v>
       </c>
       <c r="Y18">
-        <v>0.00026102181448338894</v>
+        <v>0.0017707635632871932</v>
       </c>
       <c r="Z18">
-        <v>0.0027588843300405119</v>
+        <v>-0.00018884798092148826</v>
       </c>
       <c r="AA18">
-        <v>0.0018856896139226563</v>
+        <v>1.0051299016838734e-05</v>
       </c>
       <c r="AB18">
-        <v>-0.00022172316541170729</v>
+        <v>-0.00087393393187449112</v>
       </c>
       <c r="AC18">
-        <v>1.101674702892644e-05</v>
+        <v>-0.00071428463244400855</v>
       </c>
       <c r="AD18">
-        <v>-0.0011505919882662924</v>
+        <v>-0.00075352047261068272</v>
       </c>
       <c r="AE18">
-        <v>-0.00098074851741361286</v>
+        <v>-0.00048825658119277973</v>
       </c>
       <c r="AF18">
-        <v>-0.001045777108736315</v>
+        <v>-0.00051661294328831319</v>
       </c>
       <c r="AG18">
-        <v>-0.00074984388122480237</v>
+        <v>-0.00056074122504027831</v>
       </c>
       <c r="AH18">
-        <v>-0.00081647293075966839</v>
-      </c>
-      <c r="AI18">
-        <v>-0.00090545178776167495</v>
-      </c>
-      <c r="AJ18">
-        <v>-0.008289191437113182</v>
+        <v>-0.008853936156973741</v>
       </c>
     </row>
     <row r="19">
@@ -2398,109 +2284,103 @@
         <v>41</v>
       </c>
       <c r="B19">
-        <v>0.11946047387921112</v>
+        <v>-0.16809579610461567</v>
       </c>
       <c r="C19">
-        <v>-0.01403103509017159</v>
+        <v>-0.013098940597170525</v>
       </c>
       <c r="D19">
-        <v>-3.3615211987328593e-05</v>
+        <v>-0.00014097021510243567</v>
       </c>
       <c r="E19">
-        <v>-5.8623768479945204e-07</v>
+        <v>1.1794717028021135e-06</v>
       </c>
       <c r="F19">
-        <v>6.7708413812345159e-05</v>
+        <v>0.00014740188177680969</v>
       </c>
       <c r="G19">
-        <v>-0.00031849112729133433</v>
+        <v>-0.0002535610447800124</v>
       </c>
       <c r="H19">
-        <v>-0.00029751787683207631</v>
+        <v>-0.00034865526472820096</v>
       </c>
       <c r="I19">
-        <v>-0.00032930967045939619</v>
+        <v>-0.00040632050575220569</v>
       </c>
       <c r="J19">
-        <v>0.00027584060762993363</v>
+        <v>0.0003197952623685699</v>
       </c>
       <c r="K19">
-        <v>0.00044434752343775667</v>
+        <v>0.000671918289173603</v>
       </c>
       <c r="L19">
-        <v>0.00063214033868301978</v>
+        <v>0.00059841394189035467</v>
       </c>
       <c r="M19">
-        <v>-9.3899970209110686e-05</v>
+        <v>-0.00011383305119957304</v>
       </c>
       <c r="N19">
-        <v>0.00016979418664173074</v>
+        <v>-7.7464978296643092e-05</v>
       </c>
       <c r="O19">
-        <v>-0.00010614781652158278</v>
+        <v>-0.00010355399823213708</v>
       </c>
       <c r="P19">
-        <v>0.00027163932199897149</v>
+        <v>0.00030345657268320719</v>
       </c>
       <c r="Q19">
-        <v>-0.00018358907131377949</v>
+        <v>-0.00019481431379309337</v>
       </c>
       <c r="R19">
-        <v>7.4298031779859329e-05</v>
+        <v>8.5481272806033288e-05</v>
       </c>
       <c r="S19">
-        <v>0.00033198545501881909</v>
+        <v>0.00031764445824180611</v>
       </c>
       <c r="T19">
-        <v>0.0022992157998673372</v>
+        <v>0.0018689234455486451</v>
       </c>
       <c r="U19">
-        <v>0.0018358555178688897</v>
+        <v>-0.00014614867480886571</v>
       </c>
       <c r="V19">
-        <v>-0.00098742050538569827</v>
+        <v>7.5206327388149778e-05</v>
       </c>
       <c r="W19">
-        <v>-0.00024728611842767846</v>
+        <v>3.9463308874483605e-07</v>
       </c>
       <c r="X19">
-        <v>0.00011175747351413279</v>
+        <v>5.4726236419990075e-05</v>
       </c>
       <c r="Y19">
-        <v>-1.4717583511966059e-05</v>
+        <v>-8.1935413954318056e-05</v>
       </c>
       <c r="Z19">
-        <v>0.00013118896940101168</v>
+        <v>-0.00011758730114208181</v>
       </c>
       <c r="AA19">
-        <v>3.743680288836106e-05</v>
+        <v>3.664323914570873e-06</v>
       </c>
       <c r="AB19">
-        <v>-7.6367605385134772e-05</v>
+        <v>6.645025935743626e-05</v>
       </c>
       <c r="AC19">
-        <v>2.2401081404480074e-06</v>
+        <v>9.4982883042799113e-05</v>
       </c>
       <c r="AD19">
-        <v>0.00013967521508012981</v>
+        <v>0.00011208318502652575</v>
       </c>
       <c r="AE19">
-        <v>0.00028049044791821147</v>
+        <v>3.7261353926055585e-05</v>
       </c>
       <c r="AF19">
-        <v>0.00017423587731126499</v>
+        <v>2.6016390973115716e-05</v>
       </c>
       <c r="AG19">
-        <v>0.00016484563742359454</v>
+        <v>-2.2260716160656027e-05</v>
       </c>
       <c r="AH19">
-        <v>0.00018156420170203176</v>
-      </c>
-      <c r="AI19">
-        <v>9.5029596718553206e-05</v>
-      </c>
-      <c r="AJ19">
-        <v>0.0019189591195111224</v>
+        <v>0.0032367104063549985</v>
       </c>
     </row>
     <row r="20">
@@ -2508,109 +2388,103 @@
         <v>42</v>
       </c>
       <c r="B20">
-        <v>-0.54566835878240749</v>
+        <v>0.035613081547000811</v>
       </c>
       <c r="C20">
-        <v>-0.014861015372463846</v>
+        <v>0.0016650801904650944</v>
       </c>
       <c r="D20">
-        <v>-0.00011066982474565619</v>
+        <v>-4.1782178571726173e-05</v>
       </c>
       <c r="E20">
-        <v>4.7953007317183202e-07</v>
+        <v>9.4391642560298004e-07</v>
       </c>
       <c r="F20">
-        <v>0.0005884381129871788</v>
+        <v>-0.00054181993430536812</v>
       </c>
       <c r="G20">
-        <v>8.3216341128927729e-05</v>
+        <v>-1.6506347765281315e-05</v>
       </c>
       <c r="H20">
-        <v>-0.00013730376260434607</v>
+        <v>0.00016552346490639885</v>
       </c>
       <c r="I20">
-        <v>-0.00016425396908717471</v>
+        <v>0.00026829459605286904</v>
       </c>
       <c r="J20">
-        <v>7.7532943543886525e-05</v>
+        <v>0.00039958594920104669</v>
       </c>
       <c r="K20">
-        <v>0.0007299781743081771</v>
+        <v>-3.2528764713343387e-05</v>
       </c>
       <c r="L20">
-        <v>0.00064658426680226384</v>
+        <v>-2.5109934548148008e-05</v>
       </c>
       <c r="M20">
-        <v>0.00021857877783650536</v>
+        <v>-0.00039373726660202682</v>
       </c>
       <c r="N20">
-        <v>-0.00015313543304103011</v>
+        <v>-8.3716027038679194e-05</v>
       </c>
       <c r="O20">
-        <v>-0.00018504432776530262</v>
+        <v>-0.00011259433351014294</v>
       </c>
       <c r="P20">
-        <v>-5.3730124025124252e-05</v>
+        <v>5.7049003498082509e-05</v>
       </c>
       <c r="Q20">
-        <v>-0.00039805674930032772</v>
+        <v>0.00015076568477941364</v>
       </c>
       <c r="R20">
-        <v>-0.00017839259747063263</v>
+        <v>0.00026399524808004202</v>
       </c>
       <c r="S20">
-        <v>5.62391154889445e-05</v>
+        <v>0.00026686805087693366</v>
       </c>
       <c r="T20">
-        <v>0.0018358555178688897</v>
+        <v>-0.00014614867480886571</v>
       </c>
       <c r="U20">
-        <v>0.0036844816496023522</v>
+        <v>0.0024940583240956413</v>
       </c>
       <c r="V20">
-        <v>-0.0012724305075856907</v>
+        <v>0.0011568891675466236</v>
       </c>
       <c r="W20">
-        <v>-0.00010225588289816516</v>
+        <v>-3.7219089754078529e-05</v>
       </c>
       <c r="X20">
-        <v>0.00018766665826012115</v>
+        <v>0.00036510788708236941</v>
       </c>
       <c r="Y20">
-        <v>-0.00014500547791669079</v>
+        <v>-6.3409502053079505e-05</v>
       </c>
       <c r="Z20">
-        <v>0.00055842911266481242</v>
+        <v>5.6057497035990255e-05</v>
       </c>
       <c r="AA20">
-        <v>6.1583968604455062e-05</v>
+        <v>-1.96621370947415e-06</v>
       </c>
       <c r="AB20">
-        <v>-3.9207991982039133e-05</v>
+        <v>0.00050552700914892183</v>
       </c>
       <c r="AC20">
-        <v>-1.5254212943521584e-06</v>
+        <v>0.00042573213151548021</v>
       </c>
       <c r="AD20">
-        <v>-0.00035916420322860401</v>
+        <v>0.00042830427275442127</v>
       </c>
       <c r="AE20">
-        <v>-0.00017647299743263735</v>
+        <v>0.00021478218541778069</v>
       </c>
       <c r="AF20">
-        <v>-0.00024732176697266772</v>
+        <v>0.00045758912296677798</v>
       </c>
       <c r="AG20">
-        <v>-0.00039414874908908697</v>
+        <v>0.00024098768507783877</v>
       </c>
       <c r="AH20">
-        <v>-0.00033894208402273946</v>
-      </c>
-      <c r="AI20">
-        <v>-0.00049835162210639164</v>
-      </c>
-      <c r="AJ20">
-        <v>0.0093144568836014425</v>
+        <v>-0.00053169933180413046</v>
       </c>
     </row>
     <row r="21">
@@ -2618,109 +2492,103 @@
         <v>43</v>
       </c>
       <c r="B21">
-        <v>-0.15215207939100622</v>
+        <v>0.037092381339704987</v>
       </c>
       <c r="C21">
-        <v>0.0051318929565080541</v>
+        <v>-5.6199152141975933e-05</v>
       </c>
       <c r="D21">
-        <v>-0.00023393056887593858</v>
+        <v>-0.00015962069767801569</v>
       </c>
       <c r="E21">
-        <v>4.1757462749229513e-06</v>
+        <v>2.2520036553976244e-06</v>
       </c>
       <c r="F21">
-        <v>6.8978488783139752e-05</v>
+        <v>-0.00035002149950409331</v>
       </c>
       <c r="G21">
-        <v>0.00012280573773625764</v>
+        <v>-0.00017533811831396337</v>
       </c>
       <c r="H21">
-        <v>-0.00016360283807634671</v>
+        <v>-7.2718959757588769e-05</v>
       </c>
       <c r="I21">
-        <v>-0.0001847887030670646</v>
+        <v>-0.00022172028224845541</v>
       </c>
       <c r="J21">
-        <v>0.00015610081180726291</v>
+        <v>-1.0699832103621115e-05</v>
       </c>
       <c r="K21">
-        <v>8.4228112378104903e-05</v>
+        <v>-0.00022016163600234779</v>
       </c>
       <c r="L21">
-        <v>-0.00021087268036293675</v>
+        <v>4.9402463920403868e-05</v>
       </c>
       <c r="M21">
-        <v>-0.00026539830497367828</v>
+        <v>4.4094374917571545e-05</v>
       </c>
       <c r="N21">
-        <v>-0.0003581395822996519</v>
+        <v>0.00019735160002684588</v>
       </c>
       <c r="O21">
-        <v>1.8281861557667423e-06</v>
+        <v>-3.8986565854266624e-05</v>
       </c>
       <c r="P21">
-        <v>0.00019828021468279883</v>
+        <v>-0.00015536018623847544</v>
       </c>
       <c r="Q21">
-        <v>0.00012506127557443988</v>
+        <v>-6.8920489185360931e-06</v>
       </c>
       <c r="R21">
-        <v>4.9928818852626324e-05</v>
+        <v>-0.00010209489416403326</v>
       </c>
       <c r="S21">
-        <v>-3.4646826263611913e-06</v>
+        <v>-0.00052526018175554589</v>
       </c>
       <c r="T21">
-        <v>-0.00098742050538569827</v>
+        <v>7.5206327388149778e-05</v>
       </c>
       <c r="U21">
-        <v>-0.0012724305075856907</v>
+        <v>0.0011568891675466236</v>
       </c>
       <c r="V21">
-        <v>0.0023550052516793114</v>
+        <v>0.001932169511026535</v>
       </c>
       <c r="W21">
-        <v>0.00024174397356403472</v>
+        <v>2.6406144713314172e-06</v>
       </c>
       <c r="X21">
-        <v>-4.6486864235604449e-05</v>
+        <v>-9.2567772401032643e-05</v>
       </c>
       <c r="Y21">
-        <v>6.8050259825497273e-05</v>
+        <v>9.5460649865766815e-05</v>
       </c>
       <c r="Z21">
-        <v>-0.00026222122066257988</v>
+        <v>-0.00017584011589499268</v>
       </c>
       <c r="AA21">
-        <v>-0.00025066735290521513</v>
+        <v>4.7707289242354246e-06</v>
       </c>
       <c r="AB21">
-        <v>-6.9794394013300044e-05</v>
+        <v>0.0002016908459738973</v>
       </c>
       <c r="AC21">
-        <v>3.3969857149139277e-06</v>
+        <v>0.00017201689204149903</v>
       </c>
       <c r="AD21">
-        <v>-2.1366953860633368e-05</v>
+        <v>0.0001421529271913635</v>
       </c>
       <c r="AE21">
-        <v>-0.00012252613807813982</v>
+        <v>0.00013420070900054145</v>
       </c>
       <c r="AF21">
-        <v>2.2211581000094126e-05</v>
+        <v>0.00016110968516343461</v>
       </c>
       <c r="AG21">
-        <v>-0.00010151274912743109</v>
+        <v>0.00012674154148888779</v>
       </c>
       <c r="AH21">
-        <v>-0.00013961506885963474</v>
-      </c>
-      <c r="AI21">
-        <v>-1.9030236020144793e-05</v>
-      </c>
-      <c r="AJ21">
-        <v>0.00074799310333424022</v>
+        <v>0.0030223704057939522</v>
       </c>
     </row>
     <row r="22">
@@ -2728,109 +2596,103 @@
         <v>44</v>
       </c>
       <c r="B22">
-        <v>0.067103961185812258</v>
+        <v>-0.0099030909600005598</v>
       </c>
       <c r="C22">
-        <v>0.0019271813196352072</v>
+        <v>0.0016080431451250959</v>
       </c>
       <c r="D22">
-        <v>-4.0250667569825295e-05</v>
+        <v>6.5072685155403119e-06</v>
       </c>
       <c r="E22">
-        <v>9.0305587337487751e-07</v>
+        <v>-9.2056503310736378e-08</v>
       </c>
       <c r="F22">
-        <v>-0.00043960912064326674</v>
+        <v>-7.288933469420944e-05</v>
       </c>
       <c r="G22">
-        <v>-1.9161969688527569e-05</v>
+        <v>5.1181453009620237e-05</v>
       </c>
       <c r="H22">
-        <v>0.00013719780070220455</v>
+        <v>3.1917768038736139e-05</v>
       </c>
       <c r="I22">
-        <v>0.00025257432929338963</v>
+        <v>-1.7059418973709717e-05</v>
       </c>
       <c r="J22">
-        <v>0.00040864141282163187</v>
+        <v>0.00016463975174063692</v>
       </c>
       <c r="K22">
-        <v>-7.4718561288690018e-05</v>
+        <v>2.8857038316151438e-05</v>
       </c>
       <c r="L22">
-        <v>-3.4955021206470316e-05</v>
+        <v>-5.7827679329410528e-05</v>
       </c>
       <c r="M22">
-        <v>-0.00039125422590610692</v>
+        <v>-0.00063684432807057734</v>
       </c>
       <c r="N22">
-        <v>-5.6167694535051629e-05</v>
+        <v>0.00022040829081193948</v>
       </c>
       <c r="O22">
-        <v>-0.00015270748867635738</v>
+        <v>-0.00054900620048554093</v>
       </c>
       <c r="P22">
-        <v>4.4097899605850311e-05</v>
+        <v>0.0002391872459332381</v>
       </c>
       <c r="Q22">
-        <v>0.00020451535826646186</v>
+        <v>0.00018897522945516431</v>
       </c>
       <c r="R22">
-        <v>0.00029139915720181344</v>
+        <v>0.00021477996882587257</v>
       </c>
       <c r="S22">
-        <v>0.00030307597494647857</v>
+        <v>0.00026029838797028611</v>
       </c>
       <c r="T22">
-        <v>-0.00024728611842767846</v>
+        <v>3.9463308874483605e-07</v>
       </c>
       <c r="U22">
-        <v>-0.00010225588289816516</v>
+        <v>-3.7219089754078529e-05</v>
       </c>
       <c r="V22">
-        <v>0.00024174397356403472</v>
+        <v>2.6406144713314172e-06</v>
       </c>
       <c r="W22">
-        <v>0.002554766016668166</v>
+        <v>0.00054921167416463056</v>
       </c>
       <c r="X22">
-        <v>0.0011854608161121075</v>
+        <v>-8.0412807542977938e-05</v>
       </c>
       <c r="Y22">
-        <v>-5.2370140322880853e-05</v>
+        <v>1.8381481716825323e-05</v>
       </c>
       <c r="Z22">
-        <v>0.00037810548105388672</v>
+        <v>-0.00063865710451627665</v>
       </c>
       <c r="AA22">
-        <v>-5.7858137315815661e-05</v>
+        <v>2.7212069079289147e-05</v>
       </c>
       <c r="AB22">
-        <v>7.0679743701248729e-05</v>
+        <v>5.1587862265608381e-05</v>
       </c>
       <c r="AC22">
-        <v>-2.5561372439502885e-06</v>
+        <v>7.3722950062074175e-05</v>
       </c>
       <c r="AD22">
-        <v>0.00048877945911205106</v>
+        <v>5.7785619087973896e-05</v>
       </c>
       <c r="AE22">
-        <v>0.0003841513413991712</v>
+        <v>0.00019549899696265187</v>
       </c>
       <c r="AF22">
-        <v>0.00041072200204037641</v>
+        <v>6.6244823720159815e-05</v>
       </c>
       <c r="AG22">
-        <v>0.00017868472712351561</v>
+        <v>7.3715479122188343e-05</v>
       </c>
       <c r="AH22">
-        <v>0.00044821161996494967</v>
-      </c>
-      <c r="AI22">
-        <v>0.00021368823292435804</v>
-      </c>
-      <c r="AJ22">
-        <v>-4.0767698066891114e-05</v>
+        <v>-0.019475396967514984</v>
       </c>
     </row>
     <row r="23">
@@ -2838,109 +2700,103 @@
         <v>45</v>
       </c>
       <c r="B23">
-        <v>0.05943889776774814</v>
+        <v>-0.43500816235308032</v>
       </c>
       <c r="C23">
-        <v>-0.00056765398063500158</v>
+        <v>-0.032269201478047529</v>
       </c>
       <c r="D23">
-        <v>-0.00015939846490364926</v>
+        <v>-0.00030540591246199997</v>
       </c>
       <c r="E23">
-        <v>2.2494239875276752e-06</v>
+        <v>4.6355025348035996e-06</v>
       </c>
       <c r="F23">
-        <v>-0.00019561891786943827</v>
+        <v>-0.00040337413821841563</v>
       </c>
       <c r="G23">
-        <v>-0.00015887896411250629</v>
+        <v>1.760223585040889e-05</v>
       </c>
       <c r="H23">
-        <v>-1.7749614095067395e-05</v>
+        <v>-7.7138937322421969e-06</v>
       </c>
       <c r="I23">
-        <v>-0.00015263677111317792</v>
+        <v>-0.00012350942431211057</v>
       </c>
       <c r="J23">
-        <v>5.8354328227125781e-05</v>
+        <v>-0.00049755465146504867</v>
       </c>
       <c r="K23">
-        <v>-0.00026887173349688135</v>
+        <v>0.00014915694226671431</v>
       </c>
       <c r="L23">
-        <v>7.4104563116129593e-05</v>
+        <v>0.00068284151337025777</v>
       </c>
       <c r="M23">
-        <v>2.2294010395177517e-06</v>
+        <v>0.0013885124989095948</v>
       </c>
       <c r="N23">
-        <v>0.00028967592560371014</v>
+        <v>0.0012951845302396575</v>
       </c>
       <c r="O23">
-        <v>-1.5004678771510509e-05</v>
+        <v>0.00015763718436880678</v>
       </c>
       <c r="P23">
-        <v>-0.00017165198668459938</v>
+        <v>-0.0013242477547020738</v>
       </c>
       <c r="Q23">
-        <v>-9.2782878564031036e-06</v>
+        <v>0.0017745833846981121</v>
       </c>
       <c r="R23">
-        <v>-5.5637592460253786e-05</v>
+        <v>0.0022252737058726562</v>
       </c>
       <c r="S23">
-        <v>-0.00045639232404741061</v>
+        <v>0.0024278600141531899</v>
       </c>
       <c r="T23">
-        <v>0.00011175747351413279</v>
+        <v>5.4726236419990075e-05</v>
       </c>
       <c r="U23">
-        <v>0.00018766665826012115</v>
+        <v>0.00036510788708236941</v>
       </c>
       <c r="V23">
-        <v>-4.6486864235604449e-05</v>
+        <v>-9.2567772401032643e-05</v>
       </c>
       <c r="W23">
-        <v>0.0011854608161121075</v>
+        <v>-8.0412807542977938e-05</v>
       </c>
       <c r="X23">
-        <v>0.0019675046712672958</v>
+        <v>0.017737568902771748</v>
       </c>
       <c r="Y23">
-        <v>-5.0032931173935835e-06</v>
+        <v>0.0012054466459224047</v>
       </c>
       <c r="Z23">
-        <v>-9.7543537993650779e-05</v>
+        <v>-9.3310620380022621e-05</v>
       </c>
       <c r="AA23">
-        <v>0.0001193353314392587</v>
+        <v>1.066321429722824e-06</v>
       </c>
       <c r="AB23">
-        <v>-0.0001686305716581142</v>
+        <v>-0.00042154444577330828</v>
       </c>
       <c r="AC23">
-        <v>4.4284720053924211e-06</v>
+        <v>-0.00045889148939689053</v>
       </c>
       <c r="AD23">
-        <v>0.00015989314681997912</v>
+        <v>-0.00093216137665201333</v>
       </c>
       <c r="AE23">
-        <v>0.00010592887561970476</v>
+        <v>-0.000535734576038574</v>
       </c>
       <c r="AF23">
-        <v>5.2209263367333951e-05</v>
+        <v>-0.00082034134132648231</v>
       </c>
       <c r="AG23">
-        <v>8.2708495274138618e-05</v>
+        <v>-0.00090854933746912277</v>
       </c>
       <c r="AH23">
-        <v>0.00011480472909783975</v>
-      </c>
-      <c r="AI23">
-        <v>9.9565044679886269e-05</v>
-      </c>
-      <c r="AJ23">
-        <v>0.0032033069023695939</v>
+        <v>0.0075641757878592512</v>
       </c>
     </row>
     <row r="24">
@@ -2948,109 +2804,103 @@
         <v>46</v>
       </c>
       <c r="B24">
-        <v>-0.014271334411095458</v>
+        <v>0.018369751665571279</v>
       </c>
       <c r="C24">
-        <v>0.0016190650379425339</v>
+        <v>-0.0059579173972693841</v>
       </c>
       <c r="D24">
-        <v>2.7557411350635948e-06</v>
+        <v>-8.3116208358555068e-05</v>
       </c>
       <c r="E24">
-        <v>-4.0966235322160223e-09</v>
+        <v>1.3225473832606516e-06</v>
       </c>
       <c r="F24">
-        <v>-8.9249421394238526e-05</v>
+        <v>0.00039030047980599669</v>
       </c>
       <c r="G24">
-        <v>3.0230494891259063e-06</v>
+        <v>0.00012808414841085358</v>
       </c>
       <c r="H24">
-        <v>-1.2587281779413706e-05</v>
+        <v>0.00024824168129392032</v>
       </c>
       <c r="I24">
-        <v>-5.8344592110820548e-05</v>
+        <v>0.00023830031689303644</v>
       </c>
       <c r="J24">
-        <v>0.00020320250088897319</v>
+        <v>-9.3601637833949951e-05</v>
       </c>
       <c r="K24">
-        <v>-5.2089042598708478e-06</v>
+        <v>0.00029254062206767806</v>
       </c>
       <c r="L24">
-        <v>-5.8032315052613083e-05</v>
+        <v>0.00024736821519593028</v>
       </c>
       <c r="M24">
-        <v>-0.00068362442644818999</v>
+        <v>0.00043248833804055125</v>
       </c>
       <c r="N24">
-        <v>0.00028383393650210421</v>
+        <v>0.00031341784529282236</v>
       </c>
       <c r="O24">
-        <v>-0.00056476726495756965</v>
+        <v>-0.00010149776819968841</v>
       </c>
       <c r="P24">
-        <v>0.00027468526501003626</v>
+        <v>0.0002778455905319264</v>
       </c>
       <c r="Q24">
-        <v>0.00020875287162149911</v>
+        <v>0.0012199917935633295</v>
       </c>
       <c r="R24">
-        <v>0.00022468899698518369</v>
+        <v>0.0015051755863642541</v>
       </c>
       <c r="S24">
-        <v>0.00026102181448338894</v>
+        <v>0.0017707635632871932</v>
       </c>
       <c r="T24">
-        <v>-1.4717583511966059e-05</v>
+        <v>-8.1935413954318056e-05</v>
       </c>
       <c r="U24">
-        <v>-0.00014500547791669079</v>
+        <v>-6.3409502053079505e-05</v>
       </c>
       <c r="V24">
-        <v>6.8050259825497273e-05</v>
+        <v>9.5460649865766815e-05</v>
       </c>
       <c r="W24">
-        <v>-5.2370140322880853e-05</v>
+        <v>1.8381481716825323e-05</v>
       </c>
       <c r="X24">
-        <v>-5.0032931173935835e-06</v>
+        <v>0.0012054466459224047</v>
       </c>
       <c r="Y24">
-        <v>0.00057957306801175021</v>
+        <v>0.0019950928486309819</v>
       </c>
       <c r="Z24">
-        <v>-0.00011877598157234337</v>
+        <v>-4.9434243788450474e-05</v>
       </c>
       <c r="AA24">
-        <v>1.5670499507701441e-06</v>
+        <v>2.1334289929138799e-06</v>
       </c>
       <c r="AB24">
-        <v>-0.00067782728624898869</v>
+        <v>-0.00046676977002100585</v>
       </c>
       <c r="AC24">
-        <v>2.8824255623340523e-05</v>
+        <v>-0.00041452496417045907</v>
       </c>
       <c r="AD24">
-        <v>1.304982083655086e-05</v>
+        <v>-0.00043499379737392855</v>
       </c>
       <c r="AE24">
-        <v>3.3948965047882543e-05</v>
+        <v>-0.00037200817909403285</v>
       </c>
       <c r="AF24">
-        <v>3.8346599379767039e-05</v>
+        <v>-0.00029324895776152544</v>
       </c>
       <c r="AG24">
-        <v>0.00018547195669557821</v>
+        <v>-0.00046640270153186405</v>
       </c>
       <c r="AH24">
-        <v>3.1197360787280429e-05</v>
-      </c>
-      <c r="AI24">
-        <v>3.7368271585214684e-05</v>
-      </c>
-      <c r="AJ24">
-        <v>-0.020381158835424879</v>
+        <v>-0.0011281092753429359</v>
       </c>
     </row>
     <row r="25">
@@ -3058,109 +2908,103 @@
         <v>47</v>
       </c>
       <c r="B25">
-        <v>-0.40423068636914239</v>
+        <v>0.066625526127355964</v>
       </c>
       <c r="C25">
-        <v>-0.036502196669909948</v>
+        <v>0.00048662802986032538</v>
       </c>
       <c r="D25">
-        <v>-0.00044795679051351251</v>
+        <v>3.6733248378944747e-05</v>
       </c>
       <c r="E25">
-        <v>6.4749595984658732e-06</v>
+        <v>-4.1025765813888847e-07</v>
       </c>
       <c r="F25">
-        <v>-0.00078604493774756673</v>
+        <v>-0.00024653283224243539</v>
       </c>
       <c r="G25">
-        <v>-3.9762688375737099e-05</v>
+        <v>-0.00014244457499099084</v>
       </c>
       <c r="H25">
-        <v>-2.5785282258307396e-05</v>
+        <v>-0.00014225977216264507</v>
       </c>
       <c r="I25">
-        <v>-0.00016863984768275553</v>
+        <v>6.6528737997784138e-06</v>
       </c>
       <c r="J25">
-        <v>-0.00042162893040731755</v>
+        <v>-0.00034397062036804326</v>
       </c>
       <c r="K25">
-        <v>0.00015690793646992561</v>
+        <v>0.0001388385125533476</v>
       </c>
       <c r="L25">
-        <v>0.00081496363643340482</v>
+        <v>-3.2931098875439019e-05</v>
       </c>
       <c r="M25">
-        <v>0.0014404235926219118</v>
+        <v>0.00046609412638059025</v>
       </c>
       <c r="N25">
-        <v>0.0014164015979874316</v>
+        <v>-0.00069389130621565296</v>
       </c>
       <c r="O25">
-        <v>0.00016533698653648356</v>
+        <v>0.00098211573104755841</v>
       </c>
       <c r="P25">
-        <v>-0.0012330503170501729</v>
+        <v>-0.00029568046823951833</v>
       </c>
       <c r="Q25">
-        <v>0.0020889980527941578</v>
+        <v>-8.9841526956569752e-05</v>
       </c>
       <c r="R25">
-        <v>0.0024942953067278147</v>
+        <v>-0.00025178144410860641</v>
       </c>
       <c r="S25">
-        <v>0.0027588843300405119</v>
+        <v>-0.00018884798092148826</v>
       </c>
       <c r="T25">
-        <v>0.00013118896940101168</v>
+        <v>-0.00011758730114208181</v>
       </c>
       <c r="U25">
-        <v>0.00055842911266481242</v>
+        <v>5.6057497035990255e-05</v>
       </c>
       <c r="V25">
-        <v>-0.00026222122066257988</v>
+        <v>-0.00017584011589499268</v>
       </c>
       <c r="W25">
-        <v>0.00037810548105388672</v>
+        <v>-0.00063865710451627665</v>
       </c>
       <c r="X25">
-        <v>-9.7543537993650779e-05</v>
+        <v>-9.3310620380022621e-05</v>
       </c>
       <c r="Y25">
-        <v>-0.00011877598157234337</v>
+        <v>-4.9434243788450474e-05</v>
       </c>
       <c r="Z25">
-        <v>0.018713706618188081</v>
+        <v>0.0021243728807554085</v>
       </c>
       <c r="AA25">
-        <v>0.0012587668854051304</v>
+        <v>-7.0462181635544513e-05</v>
       </c>
       <c r="AB25">
-        <v>-5.5047243570886459e-05</v>
+        <v>5.9862880477856359e-06</v>
       </c>
       <c r="AC25">
-        <v>-7.2401136930286703e-07</v>
+        <v>-4.0097338006901337e-05</v>
       </c>
       <c r="AD25">
-        <v>-0.00051506165346824201</v>
+        <v>4.6652136056919962e-06</v>
       </c>
       <c r="AE25">
-        <v>-0.00049993377405562443</v>
+        <v>-0.00019765747645679715</v>
       </c>
       <c r="AF25">
-        <v>-0.0010938002976127363</v>
+        <v>0.00010026289581685</v>
       </c>
       <c r="AG25">
-        <v>-0.00069309200635041778</v>
+        <v>5.2245905006457821e-05</v>
       </c>
       <c r="AH25">
-        <v>-0.00099157759065768639</v>
-      </c>
-      <c r="AI25">
-        <v>-0.0010985823354876028</v>
-      </c>
-      <c r="AJ25">
-        <v>0.011457681291717007</v>
+        <v>0.010280790617610136</v>
       </c>
     </row>
     <row r="26">
@@ -3168,109 +3012,103 @@
         <v>48</v>
       </c>
       <c r="B26">
-        <v>0.048616924519544857</v>
+        <v>-0.0022470551232034279</v>
       </c>
       <c r="C26">
-        <v>-0.0067386622581028372</v>
+        <v>1.5066495573121813e-05</v>
       </c>
       <c r="D26">
-        <v>-4.4919305012504005e-05</v>
+        <v>-8.7558222580175812e-07</v>
       </c>
       <c r="E26">
-        <v>6.7845143132435861e-07</v>
+        <v>9.2907841078439016e-09</v>
       </c>
       <c r="F26">
-        <v>0.0002541317112012137</v>
+        <v>5.0894007085295137e-06</v>
       </c>
       <c r="G26">
-        <v>8.5140332353350612e-05</v>
+        <v>4.5053079514084313e-06</v>
       </c>
       <c r="H26">
-        <v>0.00032559139890397937</v>
+        <v>4.5684027597360857e-06</v>
       </c>
       <c r="I26">
-        <v>0.000337733709171395</v>
+        <v>-2.6375933213137331e-07</v>
       </c>
       <c r="J26">
-        <v>-5.1104846317391985e-05</v>
+        <v>1.2876648775586087e-05</v>
       </c>
       <c r="K26">
-        <v>0.00025335319509769689</v>
+        <v>-3.3684937474843812e-06</v>
       </c>
       <c r="L26">
-        <v>0.00028145696276422947</v>
+        <v>-5.0427762742627762e-08</v>
       </c>
       <c r="M26">
-        <v>0.00043404234164555553</v>
+        <v>-2.4323467485028259e-05</v>
       </c>
       <c r="N26">
-        <v>0.0004236524433265164</v>
+        <v>2.3320912100885529e-05</v>
       </c>
       <c r="O26">
-        <v>-0.00010190239538112656</v>
+        <v>-3.957079417718528e-05</v>
       </c>
       <c r="P26">
-        <v>0.00029866345080838911</v>
+        <v>1.2590339189506892e-05</v>
       </c>
       <c r="Q26">
-        <v>0.0013545005116211185</v>
+        <v>5.548180136588563e-06</v>
       </c>
       <c r="R26">
-        <v>0.0015822343450867596</v>
+        <v>1.0730514432312281e-05</v>
       </c>
       <c r="S26">
-        <v>0.0018856896139226563</v>
+        <v>1.0051299016838734e-05</v>
       </c>
       <c r="T26">
-        <v>3.743680288836106e-05</v>
+        <v>3.664323914570873e-06</v>
       </c>
       <c r="U26">
-        <v>6.1583968604455062e-05</v>
+        <v>-1.96621370947415e-06</v>
       </c>
       <c r="V26">
-        <v>-0.00025066735290521513</v>
+        <v>4.7707289242354246e-06</v>
       </c>
       <c r="W26">
-        <v>-5.7858137315815661e-05</v>
+        <v>2.7212069079289147e-05</v>
       </c>
       <c r="X26">
-        <v>0.0001193353314392587</v>
+        <v>1.066321429722824e-06</v>
       </c>
       <c r="Y26">
-        <v>1.5670499507701441e-06</v>
+        <v>2.1334289929138799e-06</v>
       </c>
       <c r="Z26">
-        <v>0.0012587668854051304</v>
+        <v>-7.0462181635544513e-05</v>
       </c>
       <c r="AA26">
-        <v>0.0020695832731355114</v>
+        <v>2.4496871116447411e-06</v>
       </c>
       <c r="AB26">
-        <v>-3.1910120652461557e-05</v>
+        <v>1.4900141191351562e-06</v>
       </c>
       <c r="AC26">
-        <v>1.4156553197245368e-06</v>
+        <v>2.7790952061280375e-06</v>
       </c>
       <c r="AD26">
-        <v>-0.00056890703141835664</v>
+        <v>9.5177450946865624e-07</v>
       </c>
       <c r="AE26">
-        <v>-0.00051280710073887828</v>
+        <v>9.1907320615752168e-06</v>
       </c>
       <c r="AF26">
-        <v>-0.00053940517113822432</v>
+        <v>-1.3244270902406855e-06</v>
       </c>
       <c r="AG26">
-        <v>-0.00047135732603801423</v>
+        <v>-1.3588226509671187e-08</v>
       </c>
       <c r="AH26">
-        <v>-0.00039505552640802986</v>
-      </c>
-      <c r="AI26">
-        <v>-0.00058835849405848963</v>
-      </c>
-      <c r="AJ26">
-        <v>-0.0012038743058375313</v>
+        <v>-0.00062261095181424374</v>
       </c>
     </row>
     <row r="27">
@@ -3278,109 +3116,103 @@
         <v>49</v>
       </c>
       <c r="B27">
-        <v>0.069288069196599814</v>
+        <v>0.04533240985619267</v>
       </c>
       <c r="C27">
-        <v>0.00061525010395119262</v>
+        <v>0.011669315298583338</v>
       </c>
       <c r="D27">
-        <v>5.0034921853884043e-05</v>
+        <v>-0.00024564504054930963</v>
       </c>
       <c r="E27">
-        <v>-6.4226139312095949e-07</v>
+        <v>3.6119996230524003e-06</v>
       </c>
       <c r="F27">
-        <v>-6.2917903985659773e-05</v>
+        <v>-0.00016985680028946959</v>
       </c>
       <c r="G27">
-        <v>-4.8323662136001699e-05</v>
+        <v>0.00015642228619150433</v>
       </c>
       <c r="H27">
-        <v>-8.9351585151747903e-05</v>
+        <v>-0.00039945909693223092</v>
       </c>
       <c r="I27">
-        <v>7.1281580288184987e-05</v>
+        <v>-0.00037047491392783183</v>
       </c>
       <c r="J27">
-        <v>-0.00044264654520438434</v>
+        <v>0.00071217792923998057</v>
       </c>
       <c r="K27">
-        <v>0.00021272869895610613</v>
+        <v>-0.00038290470487288737</v>
       </c>
       <c r="L27">
-        <v>-3.8646629756339777e-05</v>
+        <v>-0.00045901793920607656</v>
       </c>
       <c r="M27">
-        <v>0.00055623889438208632</v>
+        <v>-0.0026261055655612282</v>
       </c>
       <c r="N27">
-        <v>-0.00082985883371058337</v>
+        <v>-0.0030487323976331306</v>
       </c>
       <c r="O27">
-        <v>0.0010368197386893077</v>
+        <v>0.0028812316361511957</v>
       </c>
       <c r="P27">
-        <v>-0.00033334425671132577</v>
+        <v>-0.00045968727641176703</v>
       </c>
       <c r="Q27">
-        <v>-9.1039749237398476e-05</v>
+        <v>-0.00082262301103112282</v>
       </c>
       <c r="R27">
-        <v>-0.00030852253138595443</v>
+        <v>-0.00099854614404251045</v>
       </c>
       <c r="S27">
-        <v>-0.00022172316541170729</v>
+        <v>-0.00087393393187449112</v>
       </c>
       <c r="T27">
-        <v>-7.6367605385134772e-05</v>
+        <v>6.645025935743626e-05</v>
       </c>
       <c r="U27">
-        <v>-3.9207991982039133e-05</v>
+        <v>0.00050552700914892183</v>
       </c>
       <c r="V27">
-        <v>-6.9794394013300044e-05</v>
+        <v>0.0002016908459738973</v>
       </c>
       <c r="W27">
-        <v>7.0679743701248729e-05</v>
+        <v>5.1587862265608381e-05</v>
       </c>
       <c r="X27">
-        <v>-0.0001686305716581142</v>
+        <v>-0.00042154444577330828</v>
       </c>
       <c r="Y27">
-        <v>-0.00067782728624898869</v>
+        <v>-0.00046676977002100585</v>
       </c>
       <c r="Z27">
-        <v>-5.5047243570886459e-05</v>
+        <v>5.9862880477856359e-06</v>
       </c>
       <c r="AA27">
-        <v>-3.1910120652461557e-05</v>
+        <v>1.4900141191351562e-06</v>
       </c>
       <c r="AB27">
-        <v>0.0022413230406927208</v>
+        <v>0.011422137769817538</v>
       </c>
       <c r="AC27">
-        <v>-7.43931405809783e-05</v>
+        <v>0.0091415486302305372</v>
       </c>
       <c r="AD27">
-        <v>0.0001650521923487018</v>
+        <v>0.0091359715857700016</v>
       </c>
       <c r="AE27">
-        <v>0.00011855063277800299</v>
+        <v>0.0090967137103934274</v>
       </c>
       <c r="AF27">
-        <v>0.00012986073548623515</v>
+        <v>0.0091425993837409864</v>
       </c>
       <c r="AG27">
-        <v>-0.00010325598946626848</v>
+        <v>0.009068447884194605</v>
       </c>
       <c r="AH27">
-        <v>0.00026015515822356552</v>
-      </c>
-      <c r="AI27">
-        <v>0.00020452690656745003</v>
-      </c>
-      <c r="AJ27">
-        <v>0.010661658610058772</v>
+        <v>-0.0066034412985453029</v>
       </c>
     </row>
     <row r="28">
@@ -3388,109 +3220,103 @@
         <v>50</v>
       </c>
       <c r="B28">
-        <v>-0.0023646765793139718</v>
+        <v>0.072114429543438482</v>
       </c>
       <c r="C28">
-        <v>1.2232335546196772e-05</v>
+        <v>0.0093120988944704608</v>
       </c>
       <c r="D28">
-        <v>-1.3201437961548549e-06</v>
+        <v>-0.00031853039605623558</v>
       </c>
       <c r="E28">
-        <v>1.7554184113501017e-08</v>
+        <v>4.521407658426255e-06</v>
       </c>
       <c r="F28">
-        <v>-6.4020514655219185e-08</v>
+        <v>-0.00020646414538039171</v>
       </c>
       <c r="G28">
-        <v>1.0138052308726608e-06</v>
+        <v>-0.00035385824700989721</v>
       </c>
       <c r="H28">
-        <v>2.2603731803256394e-06</v>
+        <v>-0.00056135869398860061</v>
       </c>
       <c r="I28">
-        <v>-2.7577286006042617e-06</v>
+        <v>-0.00064345674696386634</v>
       </c>
       <c r="J28">
-        <v>1.6187036676253573e-05</v>
+        <v>0.00042754744375868466</v>
       </c>
       <c r="K28">
-        <v>-5.9608906500921002e-06</v>
+        <v>-0.00036366230063441564</v>
       </c>
       <c r="L28">
-        <v>9.1034956044077709e-08</v>
+        <v>-0.00037471524716061518</v>
       </c>
       <c r="M28">
-        <v>-2.7567916788975833e-05</v>
+        <v>-0.0022925870260025426</v>
       </c>
       <c r="N28">
-        <v>2.809492346334829e-05</v>
+        <v>-0.0026687566056822982</v>
       </c>
       <c r="O28">
-        <v>-4.1639116238285435e-05</v>
+        <v>0.0028976479202354813</v>
       </c>
       <c r="P28">
-        <v>1.4322448704067536e-05</v>
+        <v>-0.00027179557375709134</v>
       </c>
       <c r="Q28">
-        <v>6.06305458166338e-06</v>
+        <v>-0.00052171459716753022</v>
       </c>
       <c r="R28">
-        <v>1.2459774472939184e-05</v>
+        <v>-0.00074853017251389343</v>
       </c>
       <c r="S28">
-        <v>1.101674702892644e-05</v>
+        <v>-0.00071428463244400855</v>
       </c>
       <c r="T28">
-        <v>2.2401081404480074e-06</v>
+        <v>9.4982883042799113e-05</v>
       </c>
       <c r="U28">
-        <v>-1.5254212943521584e-06</v>
+        <v>0.00042573213151548021</v>
       </c>
       <c r="V28">
-        <v>3.3969857149139277e-06</v>
+        <v>0.00017201689204149903</v>
       </c>
       <c r="W28">
-        <v>-2.5561372439502885e-06</v>
+        <v>7.3722950062074175e-05</v>
       </c>
       <c r="X28">
-        <v>4.4284720053924211e-06</v>
+        <v>-0.00045889148939689053</v>
       </c>
       <c r="Y28">
-        <v>2.8824255623340523e-05</v>
+        <v>-0.00041452496417045907</v>
       </c>
       <c r="Z28">
-        <v>-7.2401136930286703e-07</v>
+        <v>-4.0097338006901337e-05</v>
       </c>
       <c r="AA28">
-        <v>1.4156553197245368e-06</v>
+        <v>2.7790952061280375e-06</v>
       </c>
       <c r="AB28">
-        <v>-7.43931405809783e-05</v>
+        <v>0.0091415486302305372</v>
       </c>
       <c r="AC28">
-        <v>2.5874915615877642e-06</v>
+        <v>0.010693229535044455</v>
       </c>
       <c r="AD28">
-        <v>-3.4299005781044376e-06</v>
+        <v>0.0091335269693246391</v>
       </c>
       <c r="AE28">
-        <v>-2.1653339114356012e-06</v>
+        <v>0.0090429552306396516</v>
       </c>
       <c r="AF28">
-        <v>-2.7739205788346745e-06</v>
+        <v>0.0091185106819676592</v>
       </c>
       <c r="AG28">
-        <v>6.5138796383137779e-06</v>
+        <v>0.0090410549465440859</v>
       </c>
       <c r="AH28">
-        <v>-6.2117989162608364e-06</v>
-      </c>
-      <c r="AI28">
-        <v>-4.734922682714303e-06</v>
-      </c>
-      <c r="AJ28">
-        <v>-0.00064911355533666792</v>
+        <v>-0.0056033426702598796</v>
       </c>
     </row>
     <row r="29">
@@ -3498,109 +3324,103 @@
         <v>51</v>
       </c>
       <c r="B29">
-        <v>0.044700567108955258</v>
+        <v>0.037949594235096654</v>
       </c>
       <c r="C29">
-        <v>0.012352768684668003</v>
+        <v>0.011556608522671812</v>
       </c>
       <c r="D29">
-        <v>-0.00025913318481369033</v>
+        <v>-0.00021165120196874228</v>
       </c>
       <c r="E29">
-        <v>3.8559943109072196e-06</v>
+        <v>3.02577337755238e-06</v>
       </c>
       <c r="F29">
-        <v>-0.00026963384057465678</v>
+        <v>0.00016059287110052611</v>
       </c>
       <c r="G29">
-        <v>-2.722479090172536e-05</v>
+        <v>-0.0001434442593716001</v>
       </c>
       <c r="H29">
-        <v>-0.0005194671027988762</v>
+        <v>-0.00020238311732408143</v>
       </c>
       <c r="I29">
-        <v>-0.00042836153031172719</v>
+        <v>-0.00033534205427362962</v>
       </c>
       <c r="J29">
-        <v>0.00071167103031875151</v>
+        <v>0.00045020322097369847</v>
       </c>
       <c r="K29">
-        <v>-0.0004843125908789755</v>
+        <v>-0.00043116836859690972</v>
       </c>
       <c r="L29">
-        <v>-0.00048968528688025491</v>
+        <v>-0.00043930252443734503</v>
       </c>
       <c r="M29">
-        <v>-0.0027267800837532923</v>
+        <v>-0.0025008868883404445</v>
       </c>
       <c r="N29">
-        <v>-0.0032160436069721549</v>
+        <v>-0.0028726407174519582</v>
       </c>
       <c r="O29">
-        <v>0.002879560547387707</v>
+        <v>0.0029700886040962141</v>
       </c>
       <c r="P29">
-        <v>-0.00044987536369928095</v>
+        <v>0.00010598239263933545</v>
       </c>
       <c r="Q29">
-        <v>-0.00095422260525676291</v>
+        <v>-0.00051830315264578643</v>
       </c>
       <c r="R29">
-        <v>-0.0013242211544942004</v>
+        <v>-0.00075448217619428736</v>
       </c>
       <c r="S29">
-        <v>-0.0011505919882662924</v>
+        <v>-0.00075352047261068272</v>
       </c>
       <c r="T29">
-        <v>0.00013967521508012981</v>
+        <v>0.00011208318502652575</v>
       </c>
       <c r="U29">
-        <v>-0.00035916420322860401</v>
+        <v>0.00042830427275442127</v>
       </c>
       <c r="V29">
-        <v>-2.1366953860633368e-05</v>
+        <v>0.0001421529271913635</v>
       </c>
       <c r="W29">
-        <v>0.00048877945911205106</v>
+        <v>5.7785619087973896e-05</v>
       </c>
       <c r="X29">
-        <v>0.00015989314681997912</v>
+        <v>-0.00093216137665201333</v>
       </c>
       <c r="Y29">
-        <v>1.304982083655086e-05</v>
+        <v>-0.00043499379737392855</v>
       </c>
       <c r="Z29">
-        <v>-0.00051506165346824201</v>
+        <v>4.6652136056919962e-06</v>
       </c>
       <c r="AA29">
-        <v>-0.00056890703141835664</v>
+        <v>9.5177450946865624e-07</v>
       </c>
       <c r="AB29">
-        <v>0.0001650521923487018</v>
+        <v>0.0091359715857700016</v>
       </c>
       <c r="AC29">
-        <v>-3.4299005781044376e-06</v>
+        <v>0.0091335269693246391</v>
       </c>
       <c r="AD29">
-        <v>0.012068571684063556</v>
+        <v>0.01119966195248453</v>
       </c>
       <c r="AE29">
-        <v>0.0097215900650027207</v>
+        <v>0.0090459564118697856</v>
       </c>
       <c r="AF29">
-        <v>0.0097098930003031228</v>
+        <v>0.0091306337313925064</v>
       </c>
       <c r="AG29">
-        <v>0.0096437636353384065</v>
+        <v>0.0090359215199643916</v>
       </c>
       <c r="AH29">
-        <v>0.0097224714876178626</v>
-      </c>
-      <c r="AI29">
-        <v>0.0096175426607269157</v>
-      </c>
-      <c r="AJ29">
-        <v>-0.0062361206629742445</v>
+        <v>-0.0073650699599991688</v>
       </c>
     </row>
     <row r="30">
@@ -3608,109 +3428,103 @@
         <v>52</v>
       </c>
       <c r="B30">
-        <v>0.10755858213469907</v>
+        <v>0.051734628474666214</v>
       </c>
       <c r="C30">
-        <v>0.0094684639002704241</v>
+        <v>0.011129939035328051</v>
       </c>
       <c r="D30">
-        <v>-0.00031972678353795608</v>
+        <v>-0.00022402289232652598</v>
       </c>
       <c r="E30">
-        <v>4.5446123549131305e-06</v>
+        <v>3.222293190110147e-06</v>
       </c>
       <c r="F30">
-        <v>-0.00030229303508072514</v>
+        <v>3.7846106246075539e-05</v>
       </c>
       <c r="G30">
-        <v>-0.00050747929637179334</v>
+        <v>-0.00031391930185736827</v>
       </c>
       <c r="H30">
-        <v>-0.00065521853583794254</v>
+        <v>-0.00038064674756468908</v>
       </c>
       <c r="I30">
-        <v>-0.00068299009515571108</v>
+        <v>-0.00044380178766392775</v>
       </c>
       <c r="J30">
-        <v>0.0002955191502173873</v>
+        <v>0.00047232607958509493</v>
       </c>
       <c r="K30">
-        <v>-0.0003101845513583145</v>
+        <v>-0.00044958721832681777</v>
       </c>
       <c r="L30">
-        <v>-0.00038332998564618616</v>
+        <v>-0.00044318730877031948</v>
       </c>
       <c r="M30">
-        <v>-0.0022728772854662006</v>
+        <v>-0.0024839548410837669</v>
       </c>
       <c r="N30">
-        <v>-0.0029662849096437887</v>
+        <v>-0.0025704174546667836</v>
       </c>
       <c r="O30">
-        <v>0.0028818244746878227</v>
+        <v>0.0029908182724913985</v>
       </c>
       <c r="P30">
-        <v>-0.00026898932976012358</v>
+        <v>-0.00032696943565104376</v>
       </c>
       <c r="Q30">
-        <v>-0.00064572875638472778</v>
+        <v>-0.00061894244418916758</v>
       </c>
       <c r="R30">
-        <v>-0.0010593619085024497</v>
+        <v>-0.00065051600171892911</v>
       </c>
       <c r="S30">
-        <v>-0.00098074851741361286</v>
+        <v>-0.00048825658119277973</v>
       </c>
       <c r="T30">
-        <v>0.00028049044791821147</v>
+        <v>3.7261353926055585e-05</v>
       </c>
       <c r="U30">
-        <v>-0.00017647299743263735</v>
+        <v>0.00021478218541778069</v>
       </c>
       <c r="V30">
-        <v>-0.00012252613807813982</v>
+        <v>0.00013420070900054145</v>
       </c>
       <c r="W30">
-        <v>0.0003841513413991712</v>
+        <v>0.00019549899696265187</v>
       </c>
       <c r="X30">
-        <v>0.00010592887561970476</v>
+        <v>-0.000535734576038574</v>
       </c>
       <c r="Y30">
-        <v>3.3948965047882543e-05</v>
+        <v>-0.00037200817909403285</v>
       </c>
       <c r="Z30">
-        <v>-0.00049993377405562443</v>
+        <v>-0.00019765747645679715</v>
       </c>
       <c r="AA30">
-        <v>-0.00051280710073887828</v>
+        <v>9.1907320615752168e-06</v>
       </c>
       <c r="AB30">
-        <v>0.00011855063277800299</v>
+        <v>0.0090967137103934274</v>
       </c>
       <c r="AC30">
-        <v>-2.1653339114356012e-06</v>
+        <v>0.0090429552306396516</v>
       </c>
       <c r="AD30">
-        <v>0.0097215900650027207</v>
+        <v>0.0090459564118697856</v>
       </c>
       <c r="AE30">
-        <v>0.011392037575865812</v>
+        <v>0.010768238261098408</v>
       </c>
       <c r="AF30">
-        <v>0.0097247084703939168</v>
+        <v>0.0090612958917499886</v>
       </c>
       <c r="AG30">
-        <v>0.0096160185609221287</v>
+        <v>0.0090726985327432234</v>
       </c>
       <c r="AH30">
-        <v>0.0097231164248499993</v>
-      </c>
-      <c r="AI30">
-        <v>0.0096054071864162521</v>
-      </c>
-      <c r="AJ30">
-        <v>-0.005416072353583325</v>
+        <v>-0.011478693808120678</v>
       </c>
     </row>
     <row r="31">
@@ -3718,109 +3532,103 @@
         <v>53</v>
       </c>
       <c r="B31">
-        <v>0.071389523501868141</v>
+        <v>0.082226899450854082</v>
       </c>
       <c r="C31">
-        <v>0.013109054646122054</v>
+        <v>0.011635219672043999</v>
       </c>
       <c r="D31">
-        <v>-0.0001902478692502492</v>
+        <v>-0.00021953135582914503</v>
       </c>
       <c r="E31">
-        <v>2.8008612660330339e-06</v>
+        <v>3.20845053578911e-06</v>
       </c>
       <c r="F31">
-        <v>5.1111423175653759e-05</v>
+        <v>0.00050141620480266547</v>
       </c>
       <c r="G31">
-        <v>-0.00028813322742500536</v>
+        <v>-0.0002725646996366432</v>
       </c>
       <c r="H31">
-        <v>-0.00030694086771507201</v>
+        <v>-0.00030069489764898705</v>
       </c>
       <c r="I31">
-        <v>-0.00036555191390709452</v>
+        <v>-0.00038006335863416396</v>
       </c>
       <c r="J31">
-        <v>0.00043743257823449259</v>
+        <v>0.00073926803091974643</v>
       </c>
       <c r="K31">
-        <v>-0.00050411556076881427</v>
+        <v>-0.00060058465149667284</v>
       </c>
       <c r="L31">
-        <v>-0.00050383865992559848</v>
+        <v>-0.00046133025096959865</v>
       </c>
       <c r="M31">
-        <v>-0.0026334675305861605</v>
+        <v>-0.0026004388808535612</v>
       </c>
       <c r="N31">
-        <v>-0.0030931317431023672</v>
+        <v>-0.0024578886165867041</v>
       </c>
       <c r="O31">
-        <v>0.0029994411987923036</v>
+        <v>0.0032815311479722285</v>
       </c>
       <c r="P31">
-        <v>0.00014406173637961735</v>
+        <v>-0.00022376872349403915</v>
       </c>
       <c r="Q31">
-        <v>-0.00065807909882752743</v>
+        <v>-0.00040826189063267627</v>
       </c>
       <c r="R31">
-        <v>-0.0010565806993199794</v>
+        <v>-0.00059903924069017807</v>
       </c>
       <c r="S31">
-        <v>-0.001045777108736315</v>
+        <v>-0.00051661294328831319</v>
       </c>
       <c r="T31">
-        <v>0.00017423587731126499</v>
+        <v>2.6016390973115716e-05</v>
       </c>
       <c r="U31">
-        <v>-0.00024732176697266772</v>
+        <v>0.00045758912296677798</v>
       </c>
       <c r="V31">
-        <v>2.2211581000094126e-05</v>
+        <v>0.00016110968516343461</v>
       </c>
       <c r="W31">
-        <v>0.00041072200204037641</v>
+        <v>6.6244823720159815e-05</v>
       </c>
       <c r="X31">
-        <v>5.2209263367333951e-05</v>
+        <v>-0.00082034134132648231</v>
       </c>
       <c r="Y31">
-        <v>3.8346599379767039e-05</v>
+        <v>-0.00029324895776152544</v>
       </c>
       <c r="Z31">
-        <v>-0.0010938002976127363</v>
+        <v>0.00010026289581685</v>
       </c>
       <c r="AA31">
-        <v>-0.00053940517113822432</v>
+        <v>-1.3244270902406855e-06</v>
       </c>
       <c r="AB31">
-        <v>0.00012986073548623515</v>
+        <v>0.0091425993837409864</v>
       </c>
       <c r="AC31">
-        <v>-2.7739205788346745e-06</v>
+        <v>0.0091185106819676592</v>
       </c>
       <c r="AD31">
-        <v>0.0097098930003031228</v>
+        <v>0.0091306337313925064</v>
       </c>
       <c r="AE31">
-        <v>0.0097247084703939168</v>
+        <v>0.0090612958917499886</v>
       </c>
       <c r="AF31">
-        <v>0.011889367767367629</v>
+        <v>0.010067740176148709</v>
       </c>
       <c r="AG31">
-        <v>0.0096119711721066661</v>
+        <v>0.009043142329530603</v>
       </c>
       <c r="AH31">
-        <v>0.0097257751163770858</v>
-      </c>
-      <c r="AI31">
-        <v>0.0095946063200273019</v>
-      </c>
-      <c r="AJ31">
-        <v>-0.0081911512967937847</v>
+        <v>-0.0086615461631521732</v>
       </c>
     </row>
     <row r="32">
@@ -3828,109 +3636,103 @@
         <v>54</v>
       </c>
       <c r="B32">
-        <v>0.068747004319453117</v>
+        <v>0.06717896714120522</v>
       </c>
       <c r="C32">
-        <v>0.011757120176712266</v>
+        <v>0.0084980468441929885</v>
       </c>
       <c r="D32">
-        <v>-0.0002336475160176453</v>
+        <v>-0.0002806125802082898</v>
       </c>
       <c r="E32">
-        <v>3.4113027974215341e-06</v>
+        <v>4.0555926569290607e-06</v>
       </c>
       <c r="F32">
-        <v>-5.3124251327252292e-05</v>
+        <v>-3.2885359750559062e-05</v>
       </c>
       <c r="G32">
-        <v>-0.00052548304366584198</v>
+        <v>-0.00044103218366124686</v>
       </c>
       <c r="H32">
-        <v>-0.00049800624425511142</v>
+        <v>-0.00046515734126634234</v>
       </c>
       <c r="I32">
-        <v>-0.00051092846576128448</v>
+        <v>-0.00063210773196284431</v>
       </c>
       <c r="J32">
-        <v>0.00046058125842611715</v>
+        <v>0.00032035556746418982</v>
       </c>
       <c r="K32">
-        <v>-0.00055116890330128305</v>
+        <v>-0.00038123149768843956</v>
       </c>
       <c r="L32">
-        <v>-0.00047085365539634855</v>
+        <v>-0.00034128993823598179</v>
       </c>
       <c r="M32">
-        <v>-0.0025787895997136084</v>
+        <v>-0.0018835830334096022</v>
       </c>
       <c r="N32">
-        <v>-0.0026919974458402222</v>
+        <v>-0.0022809657235777869</v>
       </c>
       <c r="O32">
-        <v>0.0030099481208004171</v>
+        <v>0.0037622027578707571</v>
       </c>
       <c r="P32">
-        <v>-0.00028189896236239511</v>
+        <v>-0.00042818775307142533</v>
       </c>
       <c r="Q32">
-        <v>-0.00073458664625755351</v>
+        <v>-0.00069402566694274422</v>
       </c>
       <c r="R32">
-        <v>-0.00094538972593384216</v>
+        <v>-0.00073408813033014569</v>
       </c>
       <c r="S32">
-        <v>-0.00074984388122480237</v>
+        <v>-0.00056074122504027831</v>
       </c>
       <c r="T32">
-        <v>0.00016484563742359454</v>
+        <v>-2.2260716160656027e-05</v>
       </c>
       <c r="U32">
-        <v>-0.00039414874908908697</v>
+        <v>0.00024098768507783877</v>
       </c>
       <c r="V32">
-        <v>-0.00010151274912743109</v>
+        <v>0.00012674154148888779</v>
       </c>
       <c r="W32">
-        <v>0.00017868472712351561</v>
+        <v>7.3715479122188343e-05</v>
       </c>
       <c r="X32">
-        <v>8.2708495274138618e-05</v>
+        <v>-0.00090854933746912277</v>
       </c>
       <c r="Y32">
-        <v>0.00018547195669557821</v>
+        <v>-0.00046640270153186405</v>
       </c>
       <c r="Z32">
-        <v>-0.00069309200635041778</v>
+        <v>5.2245905006457821e-05</v>
       </c>
       <c r="AA32">
-        <v>-0.00047135732603801423</v>
+        <v>-1.3588226509671187e-08</v>
       </c>
       <c r="AB32">
-        <v>-0.00010325598946626848</v>
+        <v>0.009068447884194605</v>
       </c>
       <c r="AC32">
-        <v>6.5138796383137779e-06</v>
+        <v>0.0090410549465440859</v>
       </c>
       <c r="AD32">
-        <v>0.0096437636353384065</v>
+        <v>0.0090359215199643916</v>
       </c>
       <c r="AE32">
-        <v>0.0096160185609221287</v>
+        <v>0.0090726985327432234</v>
       </c>
       <c r="AF32">
-        <v>0.0096119711721066661</v>
+        <v>0.009043142329530603</v>
       </c>
       <c r="AG32">
-        <v>0.011379592579578133</v>
+        <v>0.010399894840673208</v>
       </c>
       <c r="AH32">
-        <v>0.0096262184450768336</v>
-      </c>
-      <c r="AI32">
-        <v>0.0096167344537189774</v>
-      </c>
-      <c r="AJ32">
-        <v>-0.01188327960065598</v>
+        <v>-0.0069313168347205833</v>
       </c>
     </row>
     <row r="33">
@@ -3938,329 +3740,103 @@
         <v>55</v>
       </c>
       <c r="B33">
-        <v>0.10684803463333821</v>
+        <v>-7.1993948228937228</v>
       </c>
       <c r="C33">
-        <v>0.012178381634644971</v>
+        <v>-0.36258931257519111</v>
       </c>
       <c r="D33">
-        <v>-0.0002131261504103284</v>
+        <v>-0.021170598116270908</v>
       </c>
       <c r="E33">
-        <v>3.1354343175727539e-06</v>
+        <v>0.00028973280263590062</v>
       </c>
       <c r="F33">
-        <v>0.00030951872868142938</v>
+        <v>-0.066803857654206128</v>
       </c>
       <c r="G33">
-        <v>-0.0004638058761665953</v>
+        <v>-0.081315943267908489</v>
       </c>
       <c r="H33">
-        <v>-0.00039600732195300969</v>
+        <v>-0.077015019093668188</v>
       </c>
       <c r="I33">
-        <v>-0.00040214909048520708</v>
+        <v>-0.07882314570701289</v>
       </c>
       <c r="J33">
-        <v>0.00070204836502050323</v>
+        <v>-0.017282586500260946</v>
       </c>
       <c r="K33">
-        <v>-0.00068720238313065441</v>
+        <v>-0.0035227861346936707</v>
       </c>
       <c r="L33">
-        <v>-0.00048319697802431711</v>
+        <v>0.013377150530292106</v>
       </c>
       <c r="M33">
-        <v>-0.0026695457881824917</v>
+        <v>0.041559630461348647</v>
       </c>
       <c r="N33">
-        <v>-0.0026112751116294107</v>
+        <v>0.0020044561287994264</v>
       </c>
       <c r="O33">
-        <v>0.0033101054896326402</v>
+        <v>0.013882268177981702</v>
       </c>
       <c r="P33">
-        <v>-0.00022195308815425895</v>
+        <v>-0.0097388546961620776</v>
       </c>
       <c r="Q33">
-        <v>-0.00052804773378511049</v>
+        <v>-0.0069090507922383911</v>
       </c>
       <c r="R33">
-        <v>-0.00093948473387639757</v>
+        <v>-0.00710939747701926</v>
       </c>
       <c r="S33">
-        <v>-0.00081647293075966839</v>
+        <v>-0.008853936156973741</v>
       </c>
       <c r="T33">
-        <v>0.00018156420170203176</v>
+        <v>0.0032367104063549985</v>
       </c>
       <c r="U33">
-        <v>-0.00033894208402273946</v>
+        <v>-0.00053169933180413046</v>
       </c>
       <c r="V33">
-        <v>-0.00013961506885963474</v>
+        <v>0.0030223704057939522</v>
       </c>
       <c r="W33">
-        <v>0.00044821161996494967</v>
+        <v>-0.019475396967514984</v>
       </c>
       <c r="X33">
-        <v>0.00011480472909783975</v>
+        <v>0.0075641757878592512</v>
       </c>
       <c r="Y33">
-        <v>3.1197360787280429e-05</v>
+        <v>-0.0011281092753429359</v>
       </c>
       <c r="Z33">
-        <v>-0.00099157759065768639</v>
+        <v>0.010280790617610136</v>
       </c>
       <c r="AA33">
-        <v>-0.00039505552640802986</v>
+        <v>-0.00062261095181424374</v>
       </c>
       <c r="AB33">
-        <v>0.00026015515822356552</v>
+        <v>-0.0066034412985453029</v>
       </c>
       <c r="AC33">
-        <v>-6.2117989162608364e-06</v>
+        <v>-0.0056033426702598796</v>
       </c>
       <c r="AD33">
-        <v>0.0097224714876178626</v>
+        <v>-0.0073650699599991688</v>
       </c>
       <c r="AE33">
-        <v>0.0097231164248499993</v>
+        <v>-0.011478693808120678</v>
       </c>
       <c r="AF33">
-        <v>0.0097257751163770858</v>
+        <v>-0.0086615461631521732</v>
       </c>
       <c r="AG33">
-        <v>0.0096262184450768336</v>
+        <v>-0.0069313168347205833</v>
       </c>
       <c r="AH33">
-        <v>0.010697695275255008</v>
-      </c>
-      <c r="AI33">
-        <v>0.0095993074569317334</v>
-      </c>
-      <c r="AJ33">
-        <v>-0.0087977500786448875</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>56</v>
-      </c>
-      <c r="B34">
-        <v>0.086775025038209913</v>
-      </c>
-      <c r="C34">
-        <v>0.009746672677643467</v>
-      </c>
-      <c r="D34">
-        <v>-0.00028790444598063986</v>
-      </c>
-      <c r="E34">
-        <v>4.2500031558900272e-06</v>
-      </c>
-      <c r="F34">
-        <v>-0.00010427112488800572</v>
-      </c>
-      <c r="G34">
-        <v>-0.00073041362526063414</v>
-      </c>
-      <c r="H34">
-        <v>-0.00060407156948102947</v>
-      </c>
-      <c r="I34">
-        <v>-0.00072643168811993564</v>
-      </c>
-      <c r="J34">
-        <v>0.00032291640328157949</v>
-      </c>
-      <c r="K34">
-        <v>-0.00047989350412604924</v>
-      </c>
-      <c r="L34">
-        <v>-0.00039388708121651864</v>
-      </c>
-      <c r="M34">
-        <v>-0.0020049185779722851</v>
-      </c>
-      <c r="N34">
-        <v>-0.0024664750228936597</v>
-      </c>
-      <c r="O34">
-        <v>0.0038467197948812825</v>
-      </c>
-      <c r="P34">
-        <v>-0.00042738192690495026</v>
-      </c>
-      <c r="Q34">
-        <v>-0.00090346517113689567</v>
-      </c>
-      <c r="R34">
-        <v>-0.0010926162612756923</v>
-      </c>
-      <c r="S34">
-        <v>-0.00090545178776167495</v>
-      </c>
-      <c r="T34">
-        <v>9.5029596718553206e-05</v>
-      </c>
-      <c r="U34">
-        <v>-0.00049835162210639164</v>
-      </c>
-      <c r="V34">
-        <v>-1.9030236020144793e-05</v>
-      </c>
-      <c r="W34">
-        <v>0.00021368823292435804</v>
-      </c>
-      <c r="X34">
-        <v>9.9565044679886269e-05</v>
-      </c>
-      <c r="Y34">
-        <v>3.7368271585214684e-05</v>
-      </c>
-      <c r="Z34">
-        <v>-0.0010985823354876028</v>
-      </c>
-      <c r="AA34">
-        <v>-0.00058835849405848963</v>
-      </c>
-      <c r="AB34">
-        <v>0.00020452690656745003</v>
-      </c>
-      <c r="AC34">
-        <v>-4.734922682714303e-06</v>
-      </c>
-      <c r="AD34">
-        <v>0.0096175426607269157</v>
-      </c>
-      <c r="AE34">
-        <v>0.0096054071864162521</v>
-      </c>
-      <c r="AF34">
-        <v>0.0095946063200273019</v>
-      </c>
-      <c r="AG34">
-        <v>0.0096167344537189774</v>
-      </c>
-      <c r="AH34">
-        <v>0.0095993074569317334</v>
-      </c>
-      <c r="AI34">
-        <v>0.011011498720113538</v>
-      </c>
-      <c r="AJ34">
-        <v>-0.0066657953401909722</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>57</v>
-      </c>
-      <c r="B35">
-        <v>-7.50760868148111</v>
-      </c>
-      <c r="C35">
-        <v>-0.37311892966451871</v>
-      </c>
-      <c r="D35">
-        <v>-0.022249251698617419</v>
-      </c>
-      <c r="E35">
-        <v>0.00030329743687748336</v>
-      </c>
-      <c r="F35">
-        <v>-0.060133749086610844</v>
-      </c>
-      <c r="G35">
-        <v>-0.077140312484265283</v>
-      </c>
-      <c r="H35">
-        <v>-0.073182202790631645</v>
-      </c>
-      <c r="I35">
-        <v>-0.075567392646664261</v>
-      </c>
-      <c r="J35">
-        <v>-0.016078198363168674</v>
-      </c>
-      <c r="K35">
-        <v>-0.0029590583490347162</v>
-      </c>
-      <c r="L35">
-        <v>0.013623117641510661</v>
-      </c>
-      <c r="M35">
-        <v>0.040768146586417725</v>
-      </c>
-      <c r="N35">
-        <v>0.00059993195604187387</v>
-      </c>
-      <c r="O35">
-        <v>0.014009909190098795</v>
-      </c>
-      <c r="P35">
-        <v>-0.012054322743333104</v>
-      </c>
-      <c r="Q35">
-        <v>-0.0082232343440501853</v>
-      </c>
-      <c r="R35">
-        <v>-0.0069895405356792942</v>
-      </c>
-      <c r="S35">
-        <v>-0.008289191437113182</v>
-      </c>
-      <c r="T35">
-        <v>0.0019189591195111224</v>
-      </c>
-      <c r="U35">
-        <v>0.0093144568836014425</v>
-      </c>
-      <c r="V35">
-        <v>0.00074799310333424022</v>
-      </c>
-      <c r="W35">
-        <v>-4.0767698066891114e-05</v>
-      </c>
-      <c r="X35">
-        <v>0.0032033069023695939</v>
-      </c>
-      <c r="Y35">
-        <v>-0.020381158835424879</v>
-      </c>
-      <c r="Z35">
-        <v>0.011457681291717007</v>
-      </c>
-      <c r="AA35">
-        <v>-0.0012038743058375313</v>
-      </c>
-      <c r="AB35">
-        <v>0.010661658610058772</v>
-      </c>
-      <c r="AC35">
-        <v>-0.00064911355533666792</v>
-      </c>
-      <c r="AD35">
-        <v>-0.0062361206629742445</v>
-      </c>
-      <c r="AE35">
-        <v>-0.005416072353583325</v>
-      </c>
-      <c r="AF35">
-        <v>-0.0081911512967937847</v>
-      </c>
-      <c r="AG35">
-        <v>-0.01188327960065598</v>
-      </c>
-      <c r="AH35">
-        <v>-0.0087977500786448875</v>
-      </c>
-      <c r="AI35">
-        <v>-0.0066657953401909722</v>
-      </c>
-      <c r="AJ35">
-        <v>1.3024723570439418</v>
+        <v>1.249089437116611</v>
       </c>
     </row>
   </sheetData>

--- a/input/ES/reg_fertility.xlsx
+++ b/input/ES/reg_fertility.xlsx
@@ -41,7 +41,7 @@
     <t>Ashley Burdett, Aleksandra Kolndrekaj</t>
   </si>
   <si>
-    <t>15 June 2016 AK</t>
+    <t>07 Oct. 2026 AK</t>
   </si>
   <si>
     <t>Description:</t>
@@ -56,7 +56,7 @@
     <t>Goodnessoffit</t>
   </si>
   <si>
-    <t xml:space="preserve">F1 - Fertility </t>
+    <t>F1 - Have child</t>
   </si>
   <si>
     <t>Pseudo R-squared</t>
@@ -286,7 +286,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -316,85 +316,43 @@
       <c r="F2"/>
     </row>
     <row r="3">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
       <c r="B3"/>
       <c r="C3"/>
       <c r="D3"/>
       <c r="F3"/>
     </row>
     <row r="4">
-      <c r="B4"/>
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <v>0.19997614006574704</v>
+      </c>
       <c r="C4"/>
       <c r="D4"/>
-      <c r="F4"/>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4">
+        <v>986.92273337834104</v>
+      </c>
     </row>
     <row r="5">
-      <c r="B5"/>
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5">
+        <v>63817</v>
+      </c>
       <c r="C5"/>
       <c r="D5"/>
-      <c r="F5"/>
-    </row>
-    <row r="6">
-      <c r="B6"/>
-      <c r="C6"/>
-      <c r="D6"/>
-      <c r="F6"/>
-    </row>
-    <row r="7">
-      <c r="B7"/>
-      <c r="C7"/>
-      <c r="D7"/>
-      <c r="F7"/>
-    </row>
-    <row r="8">
-      <c r="B8"/>
-      <c r="C8"/>
-      <c r="D8"/>
-      <c r="F8"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9"/>
-      <c r="C9"/>
-      <c r="D9"/>
-      <c r="F9"/>
-    </row>
-    <row r="10">
-      <c r="B10"/>
-      <c r="C10"/>
-      <c r="D10"/>
-      <c r="F10"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11">
-        <v>0.19997614006574704</v>
-      </c>
-      <c r="C11"/>
-      <c r="D11"/>
-      <c r="E11" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11">
-        <v>986.92273337834104</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12">
-        <v>63817</v>
-      </c>
-      <c r="C12"/>
-      <c r="D12"/>
-      <c r="E12" t="s">
+      <c r="E5" t="s">
         <v>21</v>
       </c>
-      <c r="F12">
+      <c r="F5">
         <v>-10373475.476540718</v>
       </c>
     </row>
